--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDBDEF5-89CC-49C5-B7D5-6EB5260BA465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B0FBCE-D044-42D9-BBA6-D3C10A1BCD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="411">
   <si>
     <t>CCR</t>
   </si>
@@ -1647,6 +1647,12 @@
   <si>
     <t>76a\b</t>
   </si>
+  <si>
+    <t>Kara hurma (D. lotus)</t>
+  </si>
+  <si>
+    <t>Trabzon hurması (D. Kaki)</t>
+  </si>
 </sst>
 </file>
 
@@ -1656,12 +1662,20 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2059,22 +2073,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2082,62 +2090,53 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2145,50 +2144,59 @@
     <xf numFmtId="164" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2196,8 +2204,14 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2207,7 +2221,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2216,180 +2230,147 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2399,6 +2380,66 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2719,7 +2760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M716"/>
+  <dimension ref="A1:M717"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18.7265625" customWidth="1"/>
@@ -21420,568 +21461,768 @@
       </c>
     </row>
     <row r="689" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A689" s="48">
+      <c r="A689" s="122">
         <v>713</v>
       </c>
-      <c r="B689" s="16">
+      <c r="B689" s="38">
         <v>551</v>
       </c>
-      <c r="C689" s="103">
+      <c r="C689" s="123">
         <v>46290</v>
       </c>
-      <c r="D689" s="16"/>
-      <c r="E689" s="104"/>
-      <c r="F689" s="104"/>
-      <c r="G689" s="105">
+      <c r="D689" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E689" s="126" t="s">
+        <v>369</v>
+      </c>
+      <c r="F689" s="126" t="s">
+        <v>371</v>
+      </c>
+      <c r="G689" s="90">
         <v>41.269660000000002</v>
       </c>
-      <c r="H689" s="105">
+      <c r="H689" s="90">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="690" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A690" s="48">
+      <c r="A690" s="122">
         <v>714</v>
       </c>
-      <c r="B690" s="13">
+      <c r="B690" s="29">
         <v>552</v>
       </c>
-      <c r="C690" s="96">
+      <c r="C690" s="125">
         <v>46290</v>
       </c>
-      <c r="D690" s="13"/>
-      <c r="E690" s="97"/>
-      <c r="F690" s="97"/>
-      <c r="G690" s="98">
+      <c r="D690" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E690" s="124" t="s">
+        <v>333</v>
+      </c>
+      <c r="F690" s="124" t="s">
+        <v>334</v>
+      </c>
+      <c r="G690" s="89">
         <v>41.269660000000002</v>
       </c>
-      <c r="H690" s="98">
+      <c r="H690" s="89">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="691" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A691" s="48">
+      <c r="A691" s="122">
         <v>715</v>
       </c>
-      <c r="B691" s="16">
+      <c r="B691" s="38">
         <v>553</v>
       </c>
-      <c r="C691" s="103">
+      <c r="C691" s="123">
         <v>46290</v>
       </c>
-      <c r="D691" s="16"/>
-      <c r="E691" s="104"/>
-      <c r="F691" s="104"/>
-      <c r="G691" s="105">
+      <c r="D691" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E691" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="F691" s="126" t="s">
+        <v>395</v>
+      </c>
+      <c r="G691" s="90">
         <v>41.269660000000002</v>
       </c>
-      <c r="H691" s="105">
+      <c r="H691" s="90">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="692" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A692" s="48">
+      <c r="A692" s="122">
         <v>716</v>
       </c>
-      <c r="B692" s="13">
+      <c r="B692" s="29">
         <v>554</v>
       </c>
-      <c r="C692" s="96">
+      <c r="C692" s="125">
         <v>46290</v>
       </c>
-      <c r="D692" s="13"/>
-      <c r="E692" s="97"/>
-      <c r="F692" s="97"/>
-      <c r="G692" s="98">
+      <c r="D692" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E692" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="F692" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="G692" s="89">
         <v>41.269660000000002</v>
       </c>
-      <c r="H692" s="98">
+      <c r="H692" s="89">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="693" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A693" s="48">
+      <c r="A693" s="122">
         <v>717</v>
       </c>
-      <c r="B693" s="16">
+      <c r="B693" s="38">
         <v>555</v>
       </c>
-      <c r="C693" s="103">
+      <c r="C693" s="123">
         <v>46290</v>
       </c>
-      <c r="D693" s="16"/>
-      <c r="E693" s="104"/>
-      <c r="F693" s="104"/>
-      <c r="G693" s="105">
+      <c r="D693" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E693" s="126" t="s">
+        <v>329</v>
+      </c>
+      <c r="F693" s="126" t="s">
+        <v>330</v>
+      </c>
+      <c r="G693" s="90">
         <v>41.269660000000002</v>
       </c>
-      <c r="H693" s="105">
+      <c r="H693" s="90">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="694" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A694" s="48">
+      <c r="A694" s="122">
         <v>718</v>
       </c>
-      <c r="B694" s="13">
+      <c r="B694" s="29">
         <v>556</v>
       </c>
-      <c r="C694" s="96">
+      <c r="C694" s="125">
         <v>46290</v>
       </c>
-      <c r="D694" s="13"/>
-      <c r="E694" s="97"/>
-      <c r="F694" s="97"/>
-      <c r="G694" s="98">
+      <c r="D694" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E694" s="124" t="s">
+        <v>391</v>
+      </c>
+      <c r="F694" s="124" t="s">
+        <v>392</v>
+      </c>
+      <c r="G694" s="89">
         <v>41.271999999999998</v>
       </c>
-      <c r="H694" s="98">
+      <c r="H694" s="89">
         <v>41.366070000000001</v>
       </c>
     </row>
     <row r="695" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A695" s="48">
+      <c r="A695" s="122">
         <v>719</v>
       </c>
-      <c r="B695" s="16">
+      <c r="B695" s="38">
         <v>557</v>
       </c>
-      <c r="C695" s="103">
+      <c r="C695" s="123">
         <v>46290</v>
       </c>
-      <c r="D695" s="16"/>
-      <c r="E695" s="104"/>
-      <c r="F695" s="104"/>
-      <c r="G695" s="105">
+      <c r="D695" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E695" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="F695" s="126" t="s">
+        <v>395</v>
+      </c>
+      <c r="G695" s="90">
         <v>41.271999999999998</v>
       </c>
-      <c r="H695" s="105">
+      <c r="H695" s="90">
         <v>41.366070000000001</v>
       </c>
     </row>
     <row r="696" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A696" s="48">
+      <c r="A696" s="122">
         <v>720</v>
       </c>
-      <c r="B696" s="99">
+      <c r="B696" s="127">
         <v>558</v>
       </c>
-      <c r="C696" s="100">
+      <c r="C696" s="128">
         <v>46290</v>
       </c>
-      <c r="D696" s="99"/>
-      <c r="E696" s="101"/>
-      <c r="F696" s="101"/>
-      <c r="G696" s="102">
+      <c r="D696" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="E696" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="F696" s="129" t="s">
+        <v>395</v>
+      </c>
+      <c r="G696" s="130">
         <v>41.312849999999997</v>
       </c>
-      <c r="H696" s="102">
+      <c r="H696" s="130">
         <v>41.295079999999999</v>
       </c>
     </row>
     <row r="697" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A697" s="48">
+      <c r="A697" s="122">
         <v>721</v>
       </c>
-      <c r="B697" s="16">
+      <c r="B697" s="38">
         <v>559</v>
       </c>
-      <c r="C697" s="103">
+      <c r="C697" s="123">
         <v>46290</v>
       </c>
-      <c r="D697" s="16"/>
-      <c r="E697" s="104"/>
-      <c r="F697" s="104"/>
-      <c r="G697" s="105">
+      <c r="D697" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E697" s="126" t="s">
+        <v>331</v>
+      </c>
+      <c r="F697" s="126" t="s">
+        <v>370</v>
+      </c>
+      <c r="G697" s="90">
         <v>41.313079999999999</v>
       </c>
-      <c r="H697" s="105">
+      <c r="H697" s="90">
         <v>41.295029999999997</v>
       </c>
     </row>
     <row r="698" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A698" s="48">
+      <c r="A698" s="122">
         <v>722</v>
       </c>
-      <c r="B698" s="13">
+      <c r="B698" s="29">
         <v>560</v>
       </c>
-      <c r="C698" s="96">
+      <c r="C698" s="125">
         <v>46290</v>
       </c>
-      <c r="D698" s="13"/>
-      <c r="E698" s="97"/>
-      <c r="F698" s="97"/>
-      <c r="G698" s="98">
+      <c r="D698" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E698" s="124" t="s">
+        <v>369</v>
+      </c>
+      <c r="F698" s="124" t="s">
+        <v>371</v>
+      </c>
+      <c r="G698" s="89">
         <v>41.313079999999999</v>
       </c>
-      <c r="H698" s="98">
+      <c r="H698" s="89">
         <v>41.295029999999997</v>
       </c>
     </row>
     <row r="699" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A699" s="48">
+      <c r="A699" s="122">
         <v>723</v>
       </c>
-      <c r="B699" s="16">
+      <c r="B699" s="38">
         <v>561</v>
       </c>
-      <c r="C699" s="103">
+      <c r="C699" s="123">
         <v>46290</v>
       </c>
-      <c r="D699" s="16"/>
-      <c r="E699" s="104"/>
-      <c r="F699" s="104"/>
-      <c r="G699" s="105">
+      <c r="D699" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E699" s="126" t="s">
+        <v>116</v>
+      </c>
+      <c r="F699" s="126" t="s">
+        <v>335</v>
+      </c>
+      <c r="G699" s="90">
         <v>41.31521</v>
       </c>
-      <c r="H699" s="105">
+      <c r="H699" s="90">
         <v>41.300800000000002</v>
       </c>
     </row>
     <row r="700" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A700" s="48">
+      <c r="A700" s="122">
         <v>724</v>
       </c>
-      <c r="B700" s="99">
+      <c r="B700" s="127">
         <v>562</v>
       </c>
-      <c r="C700" s="100">
+      <c r="C700" s="128">
         <v>46290</v>
       </c>
-      <c r="D700" s="99"/>
-      <c r="E700" s="101"/>
-      <c r="F700" s="101"/>
-      <c r="G700" s="102">
+      <c r="D700" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="E700" s="129" t="s">
+        <v>333</v>
+      </c>
+      <c r="F700" s="129" t="s">
+        <v>334</v>
+      </c>
+      <c r="G700" s="130">
         <v>41.314399999999999</v>
       </c>
-      <c r="H700" s="102">
+      <c r="H700" s="130">
         <v>41.383319999999998</v>
       </c>
     </row>
     <row r="701" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A701" s="48">
+      <c r="A701" s="122">
         <v>725</v>
       </c>
-      <c r="B701" s="16">
+      <c r="B701" s="38">
         <v>563</v>
       </c>
-      <c r="C701" s="103">
+      <c r="C701" s="123">
         <v>46290</v>
       </c>
-      <c r="D701" s="16"/>
-      <c r="E701" s="104"/>
-      <c r="F701" s="104"/>
-      <c r="G701" s="105">
+      <c r="D701" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E701" s="126" t="s">
+        <v>331</v>
+      </c>
+      <c r="F701" s="126" t="s">
+        <v>370</v>
+      </c>
+      <c r="G701" s="90">
         <v>41.321469999999998</v>
       </c>
-      <c r="H701" s="105">
+      <c r="H701" s="90">
         <v>41.397590000000001</v>
       </c>
     </row>
     <row r="702" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A702" s="48">
+      <c r="A702" s="122">
         <v>726</v>
       </c>
-      <c r="B702" s="13">
+      <c r="B702" s="29">
         <v>564</v>
       </c>
-      <c r="C702" s="96">
+      <c r="C702" s="125">
         <v>46290</v>
       </c>
-      <c r="D702" s="13"/>
-      <c r="E702" s="97"/>
-      <c r="F702" s="97"/>
-      <c r="G702" s="98">
+      <c r="D702" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E702" s="124" t="s">
+        <v>394</v>
+      </c>
+      <c r="F702" s="124" t="s">
+        <v>395</v>
+      </c>
+      <c r="G702" s="89">
         <v>41.321469999999998</v>
       </c>
-      <c r="H702" s="98">
+      <c r="H702" s="89">
         <v>41.397590000000001</v>
       </c>
     </row>
     <row r="703" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A703" s="48">
+      <c r="A703" s="122">
         <v>727</v>
       </c>
-      <c r="B703" s="16">
+      <c r="B703" s="38">
         <v>565</v>
       </c>
-      <c r="C703" s="103">
+      <c r="C703" s="123">
         <v>46290</v>
       </c>
-      <c r="D703" s="16"/>
-      <c r="E703" s="104"/>
-      <c r="F703" s="104"/>
-      <c r="G703" s="105">
+      <c r="D703" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E703" s="126" t="s">
+        <v>369</v>
+      </c>
+      <c r="F703" s="126" t="s">
+        <v>371</v>
+      </c>
+      <c r="G703" s="90">
         <v>41.32</v>
       </c>
-      <c r="H703" s="105">
+      <c r="H703" s="90">
         <v>41.395359999999997</v>
       </c>
     </row>
     <row r="704" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A704" s="48">
+      <c r="A704" s="122">
         <v>728</v>
       </c>
-      <c r="B704" s="13">
+      <c r="B704" s="29">
         <v>566</v>
       </c>
-      <c r="C704" s="96">
+      <c r="C704" s="125">
         <v>46290</v>
       </c>
-      <c r="D704" s="13"/>
-      <c r="E704" s="97"/>
-      <c r="F704" s="97"/>
-      <c r="G704" s="98">
+      <c r="D704" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E704" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="F704" s="124" t="s">
+        <v>330</v>
+      </c>
+      <c r="G704" s="89">
         <v>41.32</v>
       </c>
-      <c r="H704" s="98">
+      <c r="H704" s="89">
         <v>41.395359999999997</v>
       </c>
     </row>
-    <row r="705" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A705" s="48">
+    <row r="705" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A705" s="122">
         <v>729</v>
       </c>
-      <c r="B705" s="16">
+      <c r="B705" s="38">
         <v>567</v>
       </c>
-      <c r="C705" s="103">
+      <c r="C705" s="123">
         <v>46290</v>
       </c>
-      <c r="D705" s="16"/>
-      <c r="E705" s="104"/>
-      <c r="F705" s="104"/>
-      <c r="G705" s="105">
+      <c r="D705" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E705" s="126" t="s">
+        <v>116</v>
+      </c>
+      <c r="F705" s="126" t="s">
+        <v>335</v>
+      </c>
+      <c r="G705" s="90">
         <v>41.345910000000003</v>
       </c>
-      <c r="H705" s="105">
+      <c r="H705" s="90">
         <v>41.308459999999997</v>
       </c>
     </row>
-    <row r="706" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A706" s="48">
+    <row r="706" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A706" s="122">
         <v>730</v>
       </c>
-      <c r="B706" s="13">
+      <c r="B706" s="29">
         <v>568</v>
       </c>
-      <c r="C706" s="96">
+      <c r="C706" s="125">
         <v>46290</v>
       </c>
-      <c r="D706" s="13"/>
-      <c r="E706" s="97"/>
-      <c r="F706" s="97"/>
-      <c r="G706" s="98">
+      <c r="D706" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E706" s="124" t="s">
+        <v>333</v>
+      </c>
+      <c r="F706" s="124" t="s">
+        <v>334</v>
+      </c>
+      <c r="G706" s="89">
         <v>41.345910000000003</v>
       </c>
-      <c r="H706" s="98">
+      <c r="H706" s="89">
         <v>41.308459999999997</v>
       </c>
     </row>
-    <row r="707" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A707" s="48">
+    <row r="707" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A707" s="122">
         <v>731</v>
       </c>
-      <c r="B707" s="16">
+      <c r="B707" s="38">
         <v>569</v>
       </c>
-      <c r="C707" s="103">
+      <c r="C707" s="123">
         <v>46290</v>
       </c>
-      <c r="D707" s="16"/>
-      <c r="E707" s="104"/>
-      <c r="F707" s="104"/>
-      <c r="G707" s="105">
+      <c r="D707" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E707" s="126" t="s">
+        <v>394</v>
+      </c>
+      <c r="F707" s="126" t="s">
+        <v>395</v>
+      </c>
+      <c r="G707" s="90">
         <v>41.365650000000002</v>
       </c>
-      <c r="H707" s="105">
+      <c r="H707" s="90">
         <v>41.3367</v>
       </c>
     </row>
-    <row r="708" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A708" s="48">
+    <row r="708" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A708" s="122">
         <v>732</v>
       </c>
-      <c r="B708" s="13">
+      <c r="B708" s="29">
         <v>570</v>
       </c>
-      <c r="C708" s="96">
+      <c r="C708" s="125">
         <v>46290</v>
       </c>
-      <c r="D708" s="13"/>
-      <c r="E708" s="97"/>
-      <c r="F708" s="97"/>
-      <c r="G708" s="98">
+      <c r="D708" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E708" s="124" t="s">
+        <v>116</v>
+      </c>
+      <c r="F708" s="124" t="s">
+        <v>335</v>
+      </c>
+      <c r="G708" s="89">
         <v>41.365650000000002</v>
       </c>
-      <c r="H708" s="98">
+      <c r="H708" s="89">
         <v>41.3367</v>
       </c>
     </row>
-    <row r="709" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A709" s="48">
+    <row r="709" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A709" s="122">
         <v>733</v>
       </c>
-      <c r="B709" s="16">
+      <c r="B709" s="38">
         <v>571</v>
       </c>
-      <c r="C709" s="103">
+      <c r="C709" s="123">
         <v>46290</v>
       </c>
-      <c r="D709" s="16"/>
-      <c r="E709" s="104"/>
-      <c r="F709" s="104"/>
-      <c r="G709" s="105">
+      <c r="D709" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E709" s="126" t="s">
+        <v>369</v>
+      </c>
+      <c r="F709" s="126" t="s">
+        <v>371</v>
+      </c>
+      <c r="G709" s="90">
         <v>41.365650000000002</v>
       </c>
-      <c r="H709" s="105">
+      <c r="H709" s="90">
         <v>41.3367</v>
       </c>
     </row>
-    <row r="710" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A710" s="48">
+    <row r="710" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A710" s="122">
         <v>734</v>
       </c>
-      <c r="B710" s="13">
+      <c r="B710" s="29">
         <v>572</v>
       </c>
-      <c r="C710" s="96">
+      <c r="C710" s="125">
         <v>46290</v>
       </c>
-      <c r="D710" s="13"/>
-      <c r="E710" s="97"/>
-      <c r="F710" s="97"/>
-      <c r="G710" s="98">
+      <c r="D710" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E710" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="F710" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="G710" s="89">
         <v>41.365650000000002</v>
       </c>
-      <c r="H710" s="98">
+      <c r="H710" s="89">
         <v>41.3367</v>
       </c>
     </row>
-    <row r="711" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A711" s="48">
+    <row r="711" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A711" s="122">
         <v>735</v>
       </c>
-      <c r="B711" s="16">
+      <c r="B711" s="38">
         <v>573</v>
       </c>
-      <c r="C711" s="103">
+      <c r="C711" s="123">
         <v>46290</v>
       </c>
-      <c r="D711" s="16"/>
-      <c r="E711" s="104"/>
-      <c r="F711" s="104"/>
-      <c r="G711" s="105">
+      <c r="D711" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E711" s="126" t="s">
+        <v>331</v>
+      </c>
+      <c r="F711" s="126" t="s">
+        <v>370</v>
+      </c>
+      <c r="G711" s="90">
         <v>41.361899999999999</v>
       </c>
-      <c r="H711" s="105">
+      <c r="H711" s="90">
         <v>41.397300000000001</v>
       </c>
     </row>
-    <row r="712" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A712" s="48">
+    <row r="712" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A712" s="122">
         <v>736</v>
       </c>
-      <c r="B712" s="99">
+      <c r="B712" s="127">
         <v>574</v>
       </c>
-      <c r="C712" s="100">
+      <c r="C712" s="128">
         <v>46290</v>
       </c>
-      <c r="D712" s="99"/>
-      <c r="E712" s="101"/>
-      <c r="F712" s="101"/>
-      <c r="G712" s="102">
+      <c r="D712" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="E712" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="F712" s="129" t="s">
+        <v>395</v>
+      </c>
+      <c r="G712" s="130">
         <v>41.36036</v>
       </c>
-      <c r="H712" s="102">
+      <c r="H712" s="130">
         <v>41.397559999999999</v>
       </c>
-    </row>
-    <row r="713" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A713" s="48">
+      <c r="J712" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="713" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A713" s="122">
         <v>737</v>
       </c>
-      <c r="B713" s="99">
+      <c r="B713" s="127">
         <v>575</v>
       </c>
-      <c r="C713" s="100">
+      <c r="C713" s="128">
         <v>46290</v>
       </c>
-      <c r="D713" s="99"/>
-      <c r="E713" s="101"/>
-      <c r="F713" s="101"/>
-      <c r="G713" s="102">
-        <v>41.36036</v>
-      </c>
-      <c r="H713" s="102">
-        <v>41.397559999999999</v>
-      </c>
-    </row>
-    <row r="714" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A714" s="48">
+      <c r="D713" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="E713" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="F713" s="129" t="s">
+        <v>395</v>
+      </c>
+      <c r="G713" s="130">
+        <v>41.345950000000002</v>
+      </c>
+      <c r="H713" s="130">
+        <v>41.323419999999999</v>
+      </c>
+      <c r="J713" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="714" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A714" s="122">
         <v>738</v>
       </c>
-      <c r="B714" s="13">
+      <c r="B714" s="29">
         <v>576</v>
       </c>
-      <c r="C714" s="96">
+      <c r="C714" s="125">
         <v>46290</v>
       </c>
-      <c r="D714" s="13"/>
-      <c r="E714" s="97"/>
-      <c r="F714" s="97"/>
-      <c r="G714" s="98">
+      <c r="D714" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E714" s="124" t="s">
+        <v>116</v>
+      </c>
+      <c r="F714" s="124" t="s">
+        <v>335</v>
+      </c>
+      <c r="G714" s="89">
         <v>41.357779999999998</v>
       </c>
-      <c r="H714" s="98">
+      <c r="H714" s="89">
         <v>41.400300000000001</v>
       </c>
     </row>
-    <row r="715" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A715" s="48">
+    <row r="715" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A715" s="122">
         <v>739</v>
       </c>
-      <c r="B715" s="16">
+      <c r="B715" s="38">
         <v>577</v>
       </c>
-      <c r="C715" s="103">
+      <c r="C715" s="123">
         <v>46290</v>
       </c>
-      <c r="D715" s="16"/>
-      <c r="E715" s="104"/>
-      <c r="F715" s="104"/>
-      <c r="G715" s="105">
+      <c r="D715" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E715" s="126" t="s">
+        <v>369</v>
+      </c>
+      <c r="F715" s="126" t="s">
+        <v>371</v>
+      </c>
+      <c r="G715" s="90">
         <v>41.357089999999999</v>
       </c>
-      <c r="H715" s="105">
+      <c r="H715" s="90">
         <v>41.400820000000003</v>
       </c>
     </row>
-    <row r="716" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A716" s="48">
+    <row r="716" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A716" s="122">
         <v>740</v>
       </c>
-      <c r="B716" s="13">
+      <c r="B716" s="29">
         <v>578</v>
       </c>
-      <c r="C716" s="96">
+      <c r="C716" s="125">
         <v>46290</v>
       </c>
-      <c r="D716" s="13"/>
-      <c r="E716" s="97"/>
-      <c r="F716" s="97"/>
-      <c r="G716" s="98">
+      <c r="D716" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E716" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="F716" s="124" t="s">
+        <v>330</v>
+      </c>
+      <c r="G716" s="89">
         <v>41.380409999999998</v>
       </c>
-      <c r="H716" s="98">
+      <c r="H716" s="89">
         <v>41.401510000000002</v>
+      </c>
+    </row>
+    <row r="717" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A717" s="122">
+        <v>741</v>
+      </c>
+      <c r="B717" s="29">
+        <v>579</v>
+      </c>
+      <c r="C717" s="125">
+        <v>46290</v>
+      </c>
+      <c r="D717" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="E717" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="F717" s="129" t="s">
+        <v>395</v>
+      </c>
+      <c r="G717" s="130">
+        <v>41.324402900000003</v>
+      </c>
+      <c r="H717" s="130">
+        <v>41.396081299999999</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H215" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -21999,38 +22240,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="117" t="s">
+      <c r="B1" s="120" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="114" t="s">
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="117" t="s">
         <v>238</v>
       </c>
-      <c r="F1" s="114"/>
-      <c r="G1" s="115" t="s">
+      <c r="F1" s="117"/>
+      <c r="G1" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
       <c r="K1" s="62"/>
       <c r="L1" s="62"/>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="113" t="s">
         <v>246</v>
       </c>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="56" t="s">
         <v>261</v>
       </c>
       <c r="D2" s="57"/>
-      <c r="E2" s="112" t="s">
+      <c r="E2" s="111" t="s">
         <v>237</v>
       </c>
-      <c r="F2" s="113"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="61" t="s">
         <v>241</v>
       </c>
@@ -22053,15 +22294,15 @@
       <c r="L3" s="60"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="106" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="112" t="s">
+      <c r="C4" s="106"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="111" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="113"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="61" t="s">
         <v>243</v>
       </c>
@@ -22160,11 +22401,11 @@
       <c r="L11" s="60"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="106" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="108"/>
-      <c r="D12" s="109"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="107"/>
       <c r="G12" s="61" t="s">
         <v>249</v>
       </c>
@@ -22184,11 +22425,11 @@
       <c r="L13" s="60"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="108" t="s">
+      <c r="B14" s="106" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="108"/>
-      <c r="D14" s="109"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="107"/>
       <c r="G14" s="61" t="s">
         <v>250</v>
       </c>
@@ -22208,15 +22449,15 @@
       <c r="L15" s="60"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="106" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="110" t="s">
+      <c r="C16" s="106"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="115" t="s">
         <v>251</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="116"/>
       <c r="G16" s="61" t="s">
         <v>252</v>
       </c>
@@ -22239,19 +22480,19 @@
       <c r="L17" s="60"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="106" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="108"/>
-      <c r="D18" s="109"/>
-      <c r="G18" s="119" t="s">
+      <c r="C18" s="106"/>
+      <c r="D18" s="107"/>
+      <c r="G18" s="108" t="s">
         <v>253</v>
       </c>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="121"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="110"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="57"/>
@@ -22263,23 +22504,23 @@
       <c r="L19" s="60"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="108" t="s">
+      <c r="B20" s="106" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="108"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="112" t="s">
+      <c r="C20" s="106"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="111" t="s">
         <v>255</v>
       </c>
-      <c r="F20" s="113"/>
-      <c r="G20" s="119" t="s">
+      <c r="F20" s="112"/>
+      <c r="G20" s="108" t="s">
         <v>254</v>
       </c>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="121"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="110"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="57"/>
@@ -22291,11 +22532,11 @@
       <c r="L21" s="60"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C22" s="108"/>
-      <c r="D22" s="109"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="107"/>
       <c r="G22" s="61" t="s">
         <v>256</v>
       </c>
@@ -22315,11 +22556,11 @@
       <c r="L23" s="60"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="108"/>
-      <c r="D24" s="109"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="107"/>
       <c r="G24" s="61"/>
       <c r="H24" s="60"/>
       <c r="I24" s="60"/>
@@ -22331,11 +22572,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="108"/>
-      <c r="D25" s="109"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="107"/>
       <c r="G25" s="61"/>
       <c r="H25" s="60"/>
       <c r="I25" s="60"/>
@@ -22421,14 +22662,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B14:D14"/>
@@ -22440,6 +22673,14 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B0FBCE-D044-42D9-BBA6-D3C10A1BCD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BCD146-E416-42C1-BF10-A62D0A054430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="910" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
     <sheet name="harita bilgileri" sheetId="2" r:id="rId2"/>
+    <sheet name="Sayfa2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$H$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sayfa2!$I$1:$I$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sayfa1!$A$135:$I$287</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="417">
   <si>
     <t>CCR</t>
   </si>
@@ -1653,6 +1655,24 @@
   <si>
     <t>Trabzon hurması (D. Kaki)</t>
   </si>
+  <si>
+    <t>Sos.Bilg.Öğrt.</t>
+  </si>
+  <si>
+    <t>Rehb. ve Psiko. Dan.</t>
+  </si>
+  <si>
+    <t>İlköğr. Mat. Öğr.</t>
+  </si>
+  <si>
+    <t>Okul Öncesi Öğrt.</t>
+  </si>
+  <si>
+    <t>Türk. Öğrt</t>
+  </si>
+  <si>
+    <t>BÖLÜM</t>
+  </si>
 </sst>
 </file>
 
@@ -1662,7 +1682,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1836,8 +1856,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3B3A36"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Open Sans"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1949,8 +1989,26 @@
         <fgColor rgb="FFFFF4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B6B6B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCE0FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -2069,11 +2127,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE7E7E7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE7E7E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE7E7E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFE7E7E7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE7E7E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE7E7E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFE7E7E7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE7E7E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE7E7E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE7E7E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFE7E7E7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE7E7E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2366,6 +2505,94 @@
     <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2414,35 +2641,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2760,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M717"/>
+  <dimension ref="A1:M745"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18.7265625" customWidth="1"/>
@@ -20736,19 +20937,19 @@
       <c r="A661" s="48">
         <v>685</v>
       </c>
-      <c r="B661" s="16">
+      <c r="B661" s="133">
         <v>523</v>
       </c>
-      <c r="C661" s="103">
+      <c r="C661" s="134">
         <v>46283</v>
       </c>
-      <c r="D661" s="16" t="s">
+      <c r="D661" s="133" t="s">
         <v>368</v>
       </c>
-      <c r="E661" s="104" t="s">
+      <c r="E661" s="135" t="s">
         <v>369</v>
       </c>
-      <c r="F661" s="104" t="s">
+      <c r="F661" s="135" t="s">
         <v>371</v>
       </c>
       <c r="G661" s="105">
@@ -20892,19 +21093,19 @@
       <c r="A667" s="48">
         <v>691</v>
       </c>
-      <c r="B667" s="16">
+      <c r="B667" s="130">
         <v>529</v>
       </c>
-      <c r="C667" s="103">
+      <c r="C667" s="131">
         <v>46290</v>
       </c>
-      <c r="D667" s="16" t="s">
+      <c r="D667" s="130" t="s">
         <v>368</v>
       </c>
-      <c r="E667" s="104" t="s">
+      <c r="E667" s="132" t="s">
         <v>369</v>
       </c>
-      <c r="F667" s="104" t="s">
+      <c r="F667" s="132" t="s">
         <v>371</v>
       </c>
       <c r="G667" s="105">
@@ -20996,19 +21197,19 @@
       <c r="A671" s="48">
         <v>695</v>
       </c>
-      <c r="B671" s="16">
+      <c r="B671" s="130">
         <v>533</v>
       </c>
-      <c r="C671" s="103">
+      <c r="C671" s="131">
         <v>46290</v>
       </c>
-      <c r="D671" s="16" t="s">
+      <c r="D671" s="130" t="s">
         <v>368</v>
       </c>
-      <c r="E671" s="104" t="s">
+      <c r="E671" s="132" t="s">
         <v>369</v>
       </c>
-      <c r="F671" s="104" t="s">
+      <c r="F671" s="132" t="s">
         <v>371</v>
       </c>
       <c r="G671" s="105">
@@ -21256,19 +21457,19 @@
       <c r="A681" s="48">
         <v>705</v>
       </c>
-      <c r="B681" s="16">
+      <c r="B681" s="130">
         <v>543</v>
       </c>
-      <c r="C681" s="103">
+      <c r="C681" s="131">
         <v>46290</v>
       </c>
-      <c r="D681" s="16" t="s">
+      <c r="D681" s="130" t="s">
         <v>368</v>
       </c>
-      <c r="E681" s="104" t="s">
+      <c r="E681" s="132" t="s">
         <v>369</v>
       </c>
-      <c r="F681" s="104" t="s">
+      <c r="F681" s="132" t="s">
         <v>371</v>
       </c>
       <c r="G681" s="105">
@@ -21461,22 +21662,22 @@
       </c>
     </row>
     <row r="689" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A689" s="122">
+      <c r="A689" s="106">
         <v>713</v>
       </c>
       <c r="B689" s="38">
         <v>551</v>
       </c>
-      <c r="C689" s="123">
+      <c r="C689" s="107">
         <v>46290</v>
       </c>
       <c r="D689" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E689" s="126" t="s">
+      <c r="E689" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="F689" s="126" t="s">
+      <c r="F689" s="110" t="s">
         <v>371</v>
       </c>
       <c r="G689" s="90">
@@ -21487,22 +21688,22 @@
       </c>
     </row>
     <row r="690" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A690" s="122">
+      <c r="A690" s="106">
         <v>714</v>
       </c>
       <c r="B690" s="29">
         <v>552</v>
       </c>
-      <c r="C690" s="125">
+      <c r="C690" s="109">
         <v>46290</v>
       </c>
       <c r="D690" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="E690" s="124" t="s">
+      <c r="E690" s="108" t="s">
         <v>333</v>
       </c>
-      <c r="F690" s="124" t="s">
+      <c r="F690" s="108" t="s">
         <v>334</v>
       </c>
       <c r="G690" s="89">
@@ -21513,22 +21714,22 @@
       </c>
     </row>
     <row r="691" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A691" s="122">
+      <c r="A691" s="106">
         <v>715</v>
       </c>
       <c r="B691" s="38">
         <v>553</v>
       </c>
-      <c r="C691" s="123">
+      <c r="C691" s="107">
         <v>46290</v>
       </c>
       <c r="D691" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E691" s="126" t="s">
+      <c r="E691" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="F691" s="126" t="s">
+      <c r="F691" s="110" t="s">
         <v>395</v>
       </c>
       <c r="G691" s="90">
@@ -21539,22 +21740,22 @@
       </c>
     </row>
     <row r="692" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A692" s="122">
+      <c r="A692" s="106">
         <v>716</v>
       </c>
       <c r="B692" s="29">
         <v>554</v>
       </c>
-      <c r="C692" s="125">
+      <c r="C692" s="109">
         <v>46290</v>
       </c>
       <c r="D692" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E692" s="124" t="s">
+      <c r="E692" s="108" t="s">
         <v>331</v>
       </c>
-      <c r="F692" s="124" t="s">
+      <c r="F692" s="108" t="s">
         <v>370</v>
       </c>
       <c r="G692" s="89">
@@ -21565,22 +21766,22 @@
       </c>
     </row>
     <row r="693" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A693" s="122">
+      <c r="A693" s="106">
         <v>717</v>
       </c>
       <c r="B693" s="38">
         <v>555</v>
       </c>
-      <c r="C693" s="123">
+      <c r="C693" s="107">
         <v>46290</v>
       </c>
       <c r="D693" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="E693" s="126" t="s">
+      <c r="E693" s="110" t="s">
         <v>329</v>
       </c>
-      <c r="F693" s="126" t="s">
+      <c r="F693" s="110" t="s">
         <v>330</v>
       </c>
       <c r="G693" s="90">
@@ -21591,22 +21792,22 @@
       </c>
     </row>
     <row r="694" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A694" s="122">
+      <c r="A694" s="106">
         <v>718</v>
       </c>
       <c r="B694" s="29">
         <v>556</v>
       </c>
-      <c r="C694" s="125">
+      <c r="C694" s="109">
         <v>46290</v>
       </c>
       <c r="D694" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="E694" s="124" t="s">
+      <c r="E694" s="108" t="s">
         <v>391</v>
       </c>
-      <c r="F694" s="124" t="s">
+      <c r="F694" s="108" t="s">
         <v>392</v>
       </c>
       <c r="G694" s="89">
@@ -21617,22 +21818,22 @@
       </c>
     </row>
     <row r="695" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A695" s="122">
+      <c r="A695" s="106">
         <v>719</v>
       </c>
       <c r="B695" s="38">
         <v>557</v>
       </c>
-      <c r="C695" s="123">
+      <c r="C695" s="107">
         <v>46290</v>
       </c>
       <c r="D695" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E695" s="126" t="s">
+      <c r="E695" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="F695" s="126" t="s">
+      <c r="F695" s="110" t="s">
         <v>395</v>
       </c>
       <c r="G695" s="90">
@@ -21643,48 +21844,48 @@
       </c>
     </row>
     <row r="696" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A696" s="122">
+      <c r="A696" s="106">
         <v>720</v>
       </c>
-      <c r="B696" s="127">
+      <c r="B696" s="111">
         <v>558</v>
       </c>
-      <c r="C696" s="128">
+      <c r="C696" s="112">
         <v>46290</v>
       </c>
       <c r="D696" s="99" t="s">
         <v>393</v>
       </c>
-      <c r="E696" s="129" t="s">
+      <c r="E696" s="113" t="s">
         <v>394</v>
       </c>
-      <c r="F696" s="129" t="s">
+      <c r="F696" s="113" t="s">
         <v>395</v>
       </c>
-      <c r="G696" s="130">
+      <c r="G696" s="114">
         <v>41.312849999999997</v>
       </c>
-      <c r="H696" s="130">
+      <c r="H696" s="114">
         <v>41.295079999999999</v>
       </c>
     </row>
     <row r="697" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A697" s="122">
+      <c r="A697" s="106">
         <v>721</v>
       </c>
       <c r="B697" s="38">
         <v>559</v>
       </c>
-      <c r="C697" s="123">
+      <c r="C697" s="107">
         <v>46290</v>
       </c>
       <c r="D697" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E697" s="126" t="s">
+      <c r="E697" s="110" t="s">
         <v>331</v>
       </c>
-      <c r="F697" s="126" t="s">
+      <c r="F697" s="110" t="s">
         <v>370</v>
       </c>
       <c r="G697" s="90">
@@ -21695,22 +21896,22 @@
       </c>
     </row>
     <row r="698" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A698" s="122">
+      <c r="A698" s="106">
         <v>722</v>
       </c>
       <c r="B698" s="29">
         <v>560</v>
       </c>
-      <c r="C698" s="125">
+      <c r="C698" s="109">
         <v>46290</v>
       </c>
       <c r="D698" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="E698" s="124" t="s">
+      <c r="E698" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="F698" s="124" t="s">
+      <c r="F698" s="108" t="s">
         <v>371</v>
       </c>
       <c r="G698" s="89">
@@ -21721,22 +21922,22 @@
       </c>
     </row>
     <row r="699" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A699" s="122">
+      <c r="A699" s="106">
         <v>723</v>
       </c>
       <c r="B699" s="38">
         <v>561</v>
       </c>
-      <c r="C699" s="123">
+      <c r="C699" s="107">
         <v>46290</v>
       </c>
       <c r="D699" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="E699" s="126" t="s">
+      <c r="E699" s="110" t="s">
         <v>116</v>
       </c>
-      <c r="F699" s="126" t="s">
+      <c r="F699" s="110" t="s">
         <v>335</v>
       </c>
       <c r="G699" s="90">
@@ -21747,48 +21948,48 @@
       </c>
     </row>
     <row r="700" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A700" s="122">
+      <c r="A700" s="106">
         <v>724</v>
       </c>
-      <c r="B700" s="127">
+      <c r="B700" s="111">
         <v>562</v>
       </c>
-      <c r="C700" s="128">
+      <c r="C700" s="112">
         <v>46290</v>
       </c>
       <c r="D700" s="99" t="s">
         <v>332</v>
       </c>
-      <c r="E700" s="129" t="s">
+      <c r="E700" s="113" t="s">
         <v>333</v>
       </c>
-      <c r="F700" s="129" t="s">
+      <c r="F700" s="113" t="s">
         <v>334</v>
       </c>
-      <c r="G700" s="130">
+      <c r="G700" s="114">
         <v>41.314399999999999</v>
       </c>
-      <c r="H700" s="130">
+      <c r="H700" s="114">
         <v>41.383319999999998</v>
       </c>
     </row>
     <row r="701" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A701" s="122">
+      <c r="A701" s="106">
         <v>725</v>
       </c>
       <c r="B701" s="38">
         <v>563</v>
       </c>
-      <c r="C701" s="123">
+      <c r="C701" s="107">
         <v>46290</v>
       </c>
       <c r="D701" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E701" s="126" t="s">
+      <c r="E701" s="110" t="s">
         <v>331</v>
       </c>
-      <c r="F701" s="126" t="s">
+      <c r="F701" s="110" t="s">
         <v>370</v>
       </c>
       <c r="G701" s="90">
@@ -21799,22 +22000,22 @@
       </c>
     </row>
     <row r="702" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A702" s="122">
+      <c r="A702" s="106">
         <v>726</v>
       </c>
       <c r="B702" s="29">
         <v>564</v>
       </c>
-      <c r="C702" s="125">
+      <c r="C702" s="109">
         <v>46290</v>
       </c>
       <c r="D702" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="E702" s="124" t="s">
+      <c r="E702" s="108" t="s">
         <v>394</v>
       </c>
-      <c r="F702" s="124" t="s">
+      <c r="F702" s="108" t="s">
         <v>395</v>
       </c>
       <c r="G702" s="89">
@@ -21825,22 +22026,22 @@
       </c>
     </row>
     <row r="703" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A703" s="122">
+      <c r="A703" s="106">
         <v>727</v>
       </c>
       <c r="B703" s="38">
         <v>565</v>
       </c>
-      <c r="C703" s="123">
+      <c r="C703" s="107">
         <v>46290</v>
       </c>
       <c r="D703" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E703" s="126" t="s">
+      <c r="E703" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="F703" s="126" t="s">
+      <c r="F703" s="110" t="s">
         <v>371</v>
       </c>
       <c r="G703" s="90">
@@ -21851,22 +22052,22 @@
       </c>
     </row>
     <row r="704" spans="1:8" ht="16" x14ac:dyDescent="0.35">
-      <c r="A704" s="122">
+      <c r="A704" s="106">
         <v>728</v>
       </c>
       <c r="B704" s="29">
         <v>566</v>
       </c>
-      <c r="C704" s="125">
+      <c r="C704" s="109">
         <v>46290</v>
       </c>
       <c r="D704" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="E704" s="124" t="s">
+      <c r="E704" s="108" t="s">
         <v>329</v>
       </c>
-      <c r="F704" s="124" t="s">
+      <c r="F704" s="108" t="s">
         <v>330</v>
       </c>
       <c r="G704" s="89">
@@ -21877,22 +22078,22 @@
       </c>
     </row>
     <row r="705" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A705" s="122">
+      <c r="A705" s="106">
         <v>729</v>
       </c>
       <c r="B705" s="38">
         <v>567</v>
       </c>
-      <c r="C705" s="123">
+      <c r="C705" s="107">
         <v>46290</v>
       </c>
       <c r="D705" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="E705" s="126" t="s">
+      <c r="E705" s="110" t="s">
         <v>116</v>
       </c>
-      <c r="F705" s="126" t="s">
+      <c r="F705" s="110" t="s">
         <v>335</v>
       </c>
       <c r="G705" s="90">
@@ -21903,22 +22104,22 @@
       </c>
     </row>
     <row r="706" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A706" s="122">
+      <c r="A706" s="106">
         <v>730</v>
       </c>
       <c r="B706" s="29">
         <v>568</v>
       </c>
-      <c r="C706" s="125">
+      <c r="C706" s="109">
         <v>46290</v>
       </c>
       <c r="D706" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="E706" s="124" t="s">
+      <c r="E706" s="108" t="s">
         <v>333</v>
       </c>
-      <c r="F706" s="124" t="s">
+      <c r="F706" s="108" t="s">
         <v>334</v>
       </c>
       <c r="G706" s="89">
@@ -21929,22 +22130,22 @@
       </c>
     </row>
     <row r="707" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A707" s="122">
+      <c r="A707" s="106">
         <v>731</v>
       </c>
       <c r="B707" s="38">
         <v>569</v>
       </c>
-      <c r="C707" s="123">
+      <c r="C707" s="107">
         <v>46290</v>
       </c>
       <c r="D707" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E707" s="126" t="s">
+      <c r="E707" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="F707" s="126" t="s">
+      <c r="F707" s="110" t="s">
         <v>395</v>
       </c>
       <c r="G707" s="90">
@@ -21955,22 +22156,22 @@
       </c>
     </row>
     <row r="708" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A708" s="122">
+      <c r="A708" s="106">
         <v>732</v>
       </c>
       <c r="B708" s="29">
         <v>570</v>
       </c>
-      <c r="C708" s="125">
+      <c r="C708" s="109">
         <v>46290</v>
       </c>
       <c r="D708" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E708" s="124" t="s">
+      <c r="E708" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="F708" s="124" t="s">
+      <c r="F708" s="108" t="s">
         <v>335</v>
       </c>
       <c r="G708" s="89">
@@ -21981,22 +22182,22 @@
       </c>
     </row>
     <row r="709" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A709" s="122">
+      <c r="A709" s="106">
         <v>733</v>
       </c>
       <c r="B709" s="38">
         <v>571</v>
       </c>
-      <c r="C709" s="123">
+      <c r="C709" s="107">
         <v>46290</v>
       </c>
       <c r="D709" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E709" s="126" t="s">
+      <c r="E709" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="F709" s="126" t="s">
+      <c r="F709" s="110" t="s">
         <v>371</v>
       </c>
       <c r="G709" s="90">
@@ -22007,22 +22208,22 @@
       </c>
     </row>
     <row r="710" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A710" s="122">
+      <c r="A710" s="106">
         <v>734</v>
       </c>
       <c r="B710" s="29">
         <v>572</v>
       </c>
-      <c r="C710" s="125">
+      <c r="C710" s="109">
         <v>46290</v>
       </c>
       <c r="D710" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E710" s="124" t="s">
+      <c r="E710" s="108" t="s">
         <v>331</v>
       </c>
-      <c r="F710" s="124" t="s">
+      <c r="F710" s="108" t="s">
         <v>370</v>
       </c>
       <c r="G710" s="89">
@@ -22033,22 +22234,22 @@
       </c>
     </row>
     <row r="711" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A711" s="122">
+      <c r="A711" s="106">
         <v>735</v>
       </c>
       <c r="B711" s="38">
         <v>573</v>
       </c>
-      <c r="C711" s="123">
+      <c r="C711" s="107">
         <v>46290</v>
       </c>
       <c r="D711" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E711" s="126" t="s">
+      <c r="E711" s="110" t="s">
         <v>331</v>
       </c>
-      <c r="F711" s="126" t="s">
+      <c r="F711" s="110" t="s">
         <v>370</v>
       </c>
       <c r="G711" s="90">
@@ -22059,28 +22260,28 @@
       </c>
     </row>
     <row r="712" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A712" s="122">
+      <c r="A712" s="106">
         <v>736</v>
       </c>
-      <c r="B712" s="127">
+      <c r="B712" s="111">
         <v>574</v>
       </c>
-      <c r="C712" s="128">
+      <c r="C712" s="112">
         <v>46290</v>
       </c>
       <c r="D712" s="99" t="s">
         <v>393</v>
       </c>
-      <c r="E712" s="129" t="s">
+      <c r="E712" s="113" t="s">
         <v>394</v>
       </c>
-      <c r="F712" s="129" t="s">
+      <c r="F712" s="113" t="s">
         <v>395</v>
       </c>
-      <c r="G712" s="130">
+      <c r="G712" s="114">
         <v>41.36036</v>
       </c>
-      <c r="H712" s="130">
+      <c r="H712" s="114">
         <v>41.397559999999999</v>
       </c>
       <c r="J712" t="s">
@@ -22088,28 +22289,28 @@
       </c>
     </row>
     <row r="713" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A713" s="122">
+      <c r="A713" s="106">
         <v>737</v>
       </c>
-      <c r="B713" s="127">
+      <c r="B713" s="111">
         <v>575</v>
       </c>
-      <c r="C713" s="128">
+      <c r="C713" s="112">
         <v>46290</v>
       </c>
       <c r="D713" s="99" t="s">
         <v>393</v>
       </c>
-      <c r="E713" s="129" t="s">
+      <c r="E713" s="113" t="s">
         <v>394</v>
       </c>
-      <c r="F713" s="129" t="s">
+      <c r="F713" s="113" t="s">
         <v>395</v>
       </c>
-      <c r="G713" s="130">
+      <c r="G713" s="114">
         <v>41.345950000000002</v>
       </c>
-      <c r="H713" s="130">
+      <c r="H713" s="114">
         <v>41.323419999999999</v>
       </c>
       <c r="J713" t="s">
@@ -22117,22 +22318,22 @@
       </c>
     </row>
     <row r="714" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A714" s="122">
+      <c r="A714" s="106">
         <v>738</v>
       </c>
       <c r="B714" s="29">
         <v>576</v>
       </c>
-      <c r="C714" s="125">
+      <c r="C714" s="109">
         <v>46290</v>
       </c>
       <c r="D714" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E714" s="124" t="s">
+      <c r="E714" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="F714" s="124" t="s">
+      <c r="F714" s="108" t="s">
         <v>335</v>
       </c>
       <c r="G714" s="89">
@@ -22143,22 +22344,22 @@
       </c>
     </row>
     <row r="715" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A715" s="122">
+      <c r="A715" s="106">
         <v>739</v>
       </c>
       <c r="B715" s="38">
         <v>577</v>
       </c>
-      <c r="C715" s="123">
+      <c r="C715" s="107">
         <v>46290</v>
       </c>
       <c r="D715" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="E715" s="126" t="s">
+      <c r="E715" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="F715" s="126" t="s">
+      <c r="F715" s="110" t="s">
         <v>371</v>
       </c>
       <c r="G715" s="90">
@@ -22169,22 +22370,22 @@
       </c>
     </row>
     <row r="716" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A716" s="122">
+      <c r="A716" s="106">
         <v>740</v>
       </c>
       <c r="B716" s="29">
         <v>578</v>
       </c>
-      <c r="C716" s="125">
+      <c r="C716" s="109">
         <v>46290</v>
       </c>
       <c r="D716" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="E716" s="124" t="s">
+      <c r="E716" s="108" t="s">
         <v>329</v>
       </c>
-      <c r="F716" s="124" t="s">
+      <c r="F716" s="108" t="s">
         <v>330</v>
       </c>
       <c r="G716" s="89">
@@ -22195,29 +22396,757 @@
       </c>
     </row>
     <row r="717" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A717" s="122">
+      <c r="A717" s="106">
         <v>741</v>
       </c>
       <c r="B717" s="29">
         <v>579</v>
       </c>
-      <c r="C717" s="125">
+      <c r="C717" s="109">
         <v>46290</v>
       </c>
       <c r="D717" s="99" t="s">
         <v>393</v>
       </c>
-      <c r="E717" s="129" t="s">
+      <c r="E717" s="113" t="s">
         <v>394</v>
       </c>
-      <c r="F717" s="129" t="s">
+      <c r="F717" s="113" t="s">
         <v>395</v>
       </c>
-      <c r="G717" s="130">
+      <c r="G717" s="114">
         <v>41.324402900000003</v>
       </c>
-      <c r="H717" s="130">
+      <c r="H717" s="114">
         <v>41.396081299999999</v>
+      </c>
+    </row>
+    <row r="718" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A718" s="106">
+        <v>742</v>
+      </c>
+      <c r="B718" s="13">
+        <v>580</v>
+      </c>
+      <c r="C718" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D718" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E718" s="97" t="s">
+        <v>329</v>
+      </c>
+      <c r="F718" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="G718" s="98">
+        <v>41.253059999999998</v>
+      </c>
+      <c r="H718" s="98">
+        <v>41.586469999999998</v>
+      </c>
+    </row>
+    <row r="719" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A719" s="106">
+        <v>743</v>
+      </c>
+      <c r="B719" s="16">
+        <v>581</v>
+      </c>
+      <c r="C719" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D719" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E719" s="104" t="s">
+        <v>369</v>
+      </c>
+      <c r="F719" s="104" t="s">
+        <v>371</v>
+      </c>
+      <c r="G719" s="105">
+        <v>41.252519999999997</v>
+      </c>
+      <c r="H719" s="105">
+        <v>41.585479999999997</v>
+      </c>
+    </row>
+    <row r="720" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A720" s="106">
+        <v>744</v>
+      </c>
+      <c r="B720" s="13">
+        <v>582</v>
+      </c>
+      <c r="C720" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D720" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E720" s="97" t="s">
+        <v>388</v>
+      </c>
+      <c r="F720" s="97" t="s">
+        <v>322</v>
+      </c>
+      <c r="G720" s="98">
+        <v>41.253059999999998</v>
+      </c>
+      <c r="H720" s="98">
+        <v>41.586469999999998</v>
+      </c>
+    </row>
+    <row r="721" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A721" s="106">
+        <v>745</v>
+      </c>
+      <c r="B721" s="16">
+        <v>583</v>
+      </c>
+      <c r="C721" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D721" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E721" s="104" t="s">
+        <v>333</v>
+      </c>
+      <c r="F721" s="104" t="s">
+        <v>334</v>
+      </c>
+      <c r="G721" s="105">
+        <v>41.257829999999998</v>
+      </c>
+      <c r="H721" s="105">
+        <v>41.586599999999997</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A722" s="106">
+        <v>746</v>
+      </c>
+      <c r="B722" s="99">
+        <v>584</v>
+      </c>
+      <c r="C722" s="100">
+        <v>46300</v>
+      </c>
+      <c r="D722" s="99" t="s">
+        <v>325</v>
+      </c>
+      <c r="E722" s="101" t="s">
+        <v>326</v>
+      </c>
+      <c r="F722" s="101" t="s">
+        <v>327</v>
+      </c>
+      <c r="G722" s="102">
+        <v>41.256659999999997</v>
+      </c>
+      <c r="H722" s="102">
+        <v>41.588830000000002</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A723" s="106">
+        <v>747</v>
+      </c>
+      <c r="B723" s="16">
+        <v>585</v>
+      </c>
+      <c r="C723" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D723" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="E723" s="104" t="s">
+        <v>337</v>
+      </c>
+      <c r="F723" s="104" t="s">
+        <v>338</v>
+      </c>
+      <c r="G723" s="105">
+        <v>41.256659999999997</v>
+      </c>
+      <c r="H723" s="105">
+        <v>41.588830000000002</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A724" s="106">
+        <v>748</v>
+      </c>
+      <c r="B724" s="99">
+        <v>586</v>
+      </c>
+      <c r="C724" s="100">
+        <v>46300</v>
+      </c>
+      <c r="D724" s="99" t="s">
+        <v>323</v>
+      </c>
+      <c r="E724" s="101" t="s">
+        <v>324</v>
+      </c>
+      <c r="F724" s="101" t="s">
+        <v>389</v>
+      </c>
+      <c r="G724" s="102">
+        <v>41.257460000000002</v>
+      </c>
+      <c r="H724" s="102">
+        <v>41.592829999999999</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A725" s="106">
+        <v>749</v>
+      </c>
+      <c r="B725" s="16">
+        <v>587</v>
+      </c>
+      <c r="C725" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D725" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E725" s="104" t="s">
+        <v>397</v>
+      </c>
+      <c r="F725" s="104" t="s">
+        <v>398</v>
+      </c>
+      <c r="G725" s="105">
+        <v>41.257460000000002</v>
+      </c>
+      <c r="H725" s="105">
+        <v>41.592829999999999</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A726" s="106">
+        <v>750</v>
+      </c>
+      <c r="B726" s="99">
+        <v>588</v>
+      </c>
+      <c r="C726" s="100">
+        <v>46300</v>
+      </c>
+      <c r="D726" s="99" t="s">
+        <v>390</v>
+      </c>
+      <c r="E726" s="101" t="s">
+        <v>391</v>
+      </c>
+      <c r="F726" s="101" t="s">
+        <v>392</v>
+      </c>
+      <c r="G726" s="102">
+        <v>41.25423</v>
+      </c>
+      <c r="H726" s="102">
+        <v>41.56662</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A727" s="106">
+        <v>751</v>
+      </c>
+      <c r="B727" s="16">
+        <v>589</v>
+      </c>
+      <c r="C727" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D727" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="E727" s="104" t="s">
+        <v>394</v>
+      </c>
+      <c r="F727" s="104" t="s">
+        <v>395</v>
+      </c>
+      <c r="G727" s="105">
+        <v>41.298110000000001</v>
+      </c>
+      <c r="H727" s="105">
+        <v>41.539209999999997</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A728" s="106">
+        <v>752</v>
+      </c>
+      <c r="B728" s="13">
+        <v>590</v>
+      </c>
+      <c r="C728" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D728" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E728" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="F728" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="G728" s="98">
+        <v>41.29768</v>
+      </c>
+      <c r="H728" s="98">
+        <v>41.538629999999998</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A729" s="106">
+        <v>753</v>
+      </c>
+      <c r="B729" s="16">
+        <v>591</v>
+      </c>
+      <c r="C729" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D729" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E729" s="104" t="s">
+        <v>388</v>
+      </c>
+      <c r="F729" s="104" t="s">
+        <v>322</v>
+      </c>
+      <c r="G729" s="105">
+        <v>41.296669999999999</v>
+      </c>
+      <c r="H729" s="105">
+        <v>41.537660000000002</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A730" s="106">
+        <v>754</v>
+      </c>
+      <c r="B730" s="99">
+        <v>592</v>
+      </c>
+      <c r="C730" s="100">
+        <v>46300</v>
+      </c>
+      <c r="D730" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="E730" s="101" t="s">
+        <v>333</v>
+      </c>
+      <c r="F730" s="101" t="s">
+        <v>334</v>
+      </c>
+      <c r="G730" s="102">
+        <v>41.296599999999998</v>
+      </c>
+      <c r="H730" s="102">
+        <v>41.537649999999999</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A731" s="106">
+        <v>755</v>
+      </c>
+      <c r="B731" s="16">
+        <v>593</v>
+      </c>
+      <c r="C731" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D731" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E731" s="104" t="s">
+        <v>329</v>
+      </c>
+      <c r="F731" s="104" t="s">
+        <v>330</v>
+      </c>
+      <c r="G731" s="105">
+        <v>41.295099999999998</v>
+      </c>
+      <c r="H731" s="105">
+        <v>41.537939999999999</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A732" s="106">
+        <v>756</v>
+      </c>
+      <c r="B732" s="13">
+        <v>594</v>
+      </c>
+      <c r="C732" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D732" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E732" s="97" t="s">
+        <v>394</v>
+      </c>
+      <c r="F732" s="97" t="s">
+        <v>395</v>
+      </c>
+      <c r="G732" s="98">
+        <v>41.296909999999997</v>
+      </c>
+      <c r="H732" s="98">
+        <v>41.559269999999998</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A733" s="106">
+        <v>757</v>
+      </c>
+      <c r="B733" s="16">
+        <v>595</v>
+      </c>
+      <c r="C733" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D733" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E733" s="104" t="s">
+        <v>369</v>
+      </c>
+      <c r="F733" s="104" t="s">
+        <v>371</v>
+      </c>
+      <c r="G733" s="105">
+        <v>41.294460000000001</v>
+      </c>
+      <c r="H733" s="105">
+        <v>41.56662</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A734" s="106">
+        <v>758</v>
+      </c>
+      <c r="B734" s="13">
+        <v>596</v>
+      </c>
+      <c r="C734" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D734" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E734" s="97" t="s">
+        <v>369</v>
+      </c>
+      <c r="F734" s="97" t="s">
+        <v>371</v>
+      </c>
+      <c r="G734" s="98">
+        <v>41.26099</v>
+      </c>
+      <c r="H734" s="98">
+        <v>41.545209999999997</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A735" s="106">
+        <v>759</v>
+      </c>
+      <c r="B735" s="16">
+        <v>597</v>
+      </c>
+      <c r="C735" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D735" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E735" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="F735" s="104" t="s">
+        <v>335</v>
+      </c>
+      <c r="G735" s="105">
+        <v>41.26099</v>
+      </c>
+      <c r="H735" s="105">
+        <v>41.545209999999997</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A736" s="106">
+        <v>760</v>
+      </c>
+      <c r="B736" s="13">
+        <v>598</v>
+      </c>
+      <c r="C736" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D736" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E736" s="97" t="s">
+        <v>331</v>
+      </c>
+      <c r="F736" s="97" t="s">
+        <v>370</v>
+      </c>
+      <c r="G736" s="98">
+        <v>41.26099</v>
+      </c>
+      <c r="H736" s="98">
+        <v>41.545209999999997</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A737" s="106">
+        <v>761</v>
+      </c>
+      <c r="B737" s="16">
+        <v>599</v>
+      </c>
+      <c r="C737" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D737" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E737" s="104" t="s">
+        <v>329</v>
+      </c>
+      <c r="F737" s="104" t="s">
+        <v>330</v>
+      </c>
+      <c r="G737" s="105">
+        <v>41.26099</v>
+      </c>
+      <c r="H737" s="105">
+        <v>41.545209999999997</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A738" s="106">
+        <v>762</v>
+      </c>
+      <c r="B738" s="13">
+        <v>600</v>
+      </c>
+      <c r="C738" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D738" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E738" s="97" t="s">
+        <v>324</v>
+      </c>
+      <c r="F738" s="97" t="s">
+        <v>389</v>
+      </c>
+      <c r="G738" s="98">
+        <v>41.26099</v>
+      </c>
+      <c r="H738" s="98">
+        <v>41.545209999999997</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A739" s="106">
+        <v>763</v>
+      </c>
+      <c r="B739" s="16">
+        <v>601</v>
+      </c>
+      <c r="C739" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D739" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E739" s="104" t="s">
+        <v>388</v>
+      </c>
+      <c r="F739" s="104" t="s">
+        <v>322</v>
+      </c>
+      <c r="G739" s="105">
+        <v>41.263240000000003</v>
+      </c>
+      <c r="H739" s="105">
+        <v>41.54468</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A740" s="106">
+        <v>764</v>
+      </c>
+      <c r="B740" s="13">
+        <v>602</v>
+      </c>
+      <c r="C740" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D740" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E740" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="F740" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="G740" s="98">
+        <v>41.263240000000003</v>
+      </c>
+      <c r="H740" s="98">
+        <v>41.54468</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A741" s="106">
+        <v>765</v>
+      </c>
+      <c r="B741" s="99">
+        <v>603</v>
+      </c>
+      <c r="C741" s="100">
+        <v>46300</v>
+      </c>
+      <c r="D741" s="99" t="s">
+        <v>393</v>
+      </c>
+      <c r="E741" s="101" t="s">
+        <v>394</v>
+      </c>
+      <c r="F741" s="101" t="s">
+        <v>395</v>
+      </c>
+      <c r="G741" s="102">
+        <v>41.26793</v>
+      </c>
+      <c r="H741" s="102">
+        <v>41.548389999999998</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A742" s="106">
+        <v>766</v>
+      </c>
+      <c r="B742" s="13">
+        <v>604</v>
+      </c>
+      <c r="C742" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D742" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E742" s="97" t="s">
+        <v>333</v>
+      </c>
+      <c r="F742" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="G742" s="98">
+        <v>41.26793</v>
+      </c>
+      <c r="H742" s="98">
+        <v>41.548389999999998</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A743" s="106">
+        <v>767</v>
+      </c>
+      <c r="B743" s="16">
+        <v>605</v>
+      </c>
+      <c r="C743" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D743" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E743" s="104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F743" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="G743" s="105">
+        <v>41.27948</v>
+      </c>
+      <c r="H743" s="105">
+        <v>41.55856</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A744" s="106">
+        <v>768</v>
+      </c>
+      <c r="B744" s="13">
+        <v>606</v>
+      </c>
+      <c r="C744" s="96">
+        <v>46300</v>
+      </c>
+      <c r="D744" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E744" s="97" t="s">
+        <v>394</v>
+      </c>
+      <c r="F744" s="97" t="s">
+        <v>395</v>
+      </c>
+      <c r="G744" s="98">
+        <v>41.27948</v>
+      </c>
+      <c r="H744" s="98">
+        <v>41.55856</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A745" s="106">
+        <v>769</v>
+      </c>
+      <c r="B745" s="16">
+        <v>607</v>
+      </c>
+      <c r="C745" s="103">
+        <v>46300</v>
+      </c>
+      <c r="D745" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="E745" s="104" t="s">
+        <v>337</v>
+      </c>
+      <c r="F745" s="104" t="s">
+        <v>338</v>
+      </c>
+      <c r="G745" s="105">
+        <v>41.280389999999997</v>
+      </c>
+      <c r="H745" s="105">
+        <v>41.561770000000003</v>
       </c>
     </row>
   </sheetData>
@@ -22240,38 +23169,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="150" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="117" t="s">
+      <c r="C1" s="150"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="147" t="s">
         <v>238</v>
       </c>
-      <c r="F1" s="117"/>
-      <c r="G1" s="118" t="s">
+      <c r="F1" s="147"/>
+      <c r="G1" s="148" t="s">
         <v>239</v>
       </c>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
       <c r="K1" s="62"/>
       <c r="L1" s="62"/>
-      <c r="M1" s="113" t="s">
+      <c r="M1" s="143" t="s">
         <v>246</v>
       </c>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="56" t="s">
         <v>261</v>
       </c>
       <c r="D2" s="57"/>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="141" t="s">
         <v>237</v>
       </c>
-      <c r="F2" s="112"/>
+      <c r="F2" s="142"/>
       <c r="G2" s="61" t="s">
         <v>241</v>
       </c>
@@ -22294,15 +23223,15 @@
       <c r="L3" s="60"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="136" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="111" t="s">
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="141" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="142"/>
       <c r="G4" s="61" t="s">
         <v>243</v>
       </c>
@@ -22401,11 +23330,11 @@
       <c r="L11" s="60"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="136" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="107"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="137"/>
       <c r="G12" s="61" t="s">
         <v>249</v>
       </c>
@@ -22425,11 +23354,11 @@
       <c r="L13" s="60"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="106" t="s">
+      <c r="B14" s="136" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="107"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="137"/>
       <c r="G14" s="61" t="s">
         <v>250</v>
       </c>
@@ -22449,15 +23378,15 @@
       <c r="L15" s="60"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="136" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="115" t="s">
+      <c r="C16" s="136"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="145" t="s">
         <v>251</v>
       </c>
-      <c r="F16" s="116"/>
+      <c r="F16" s="146"/>
       <c r="G16" s="61" t="s">
         <v>252</v>
       </c>
@@ -22480,19 +23409,19 @@
       <c r="L17" s="60"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="107"/>
-      <c r="G18" s="108" t="s">
+      <c r="C18" s="136"/>
+      <c r="D18" s="137"/>
+      <c r="G18" s="138" t="s">
         <v>253</v>
       </c>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="110"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="140"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="57"/>
@@ -22504,23 +23433,23 @@
       <c r="L19" s="60"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="106" t="s">
+      <c r="B20" s="136" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="106"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="111" t="s">
+      <c r="C20" s="136"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="141" t="s">
         <v>255</v>
       </c>
-      <c r="F20" s="112"/>
-      <c r="G20" s="108" t="s">
+      <c r="F20" s="142"/>
+      <c r="G20" s="138" t="s">
         <v>254</v>
       </c>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="110"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="140"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="57"/>
@@ -22532,11 +23461,11 @@
       <c r="L21" s="60"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="136" t="s">
         <v>268</v>
       </c>
-      <c r="C22" s="106"/>
-      <c r="D22" s="107"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
       <c r="G22" s="61" t="s">
         <v>256</v>
       </c>
@@ -22556,11 +23485,11 @@
       <c r="L23" s="60"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="106" t="s">
+      <c r="B24" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="106"/>
-      <c r="D24" s="107"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="137"/>
       <c r="G24" s="61"/>
       <c r="H24" s="60"/>
       <c r="I24" s="60"/>
@@ -22572,11 +23501,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="106" t="s">
+      <c r="B25" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="106"/>
-      <c r="D25" s="107"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137"/>
       <c r="G25" s="61"/>
       <c r="H25" s="60"/>
       <c r="I25" s="60"/>
@@ -22685,4 +23614,551 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC08E385-7096-4F5B-AACD-9DFB3906EA65}">
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="32.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="122"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="122"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="123" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="122"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="115"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="122"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="122"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="123" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="122"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="123" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="122"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="123" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="122"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="115"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="122"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="122"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="122"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="122"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="122"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="122"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="122"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="122"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="122"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="123" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="122"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="122"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="122"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="115"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="122"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="124"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="125" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="122"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="122"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="122"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="122"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="122"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="122"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="122"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="123" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="122"/>
+      <c r="B31" s="116"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="123" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="122"/>
+      <c r="B32" s="116"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="123" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="122"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="115"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="123" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="122"/>
+      <c r="B34" s="116"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="115"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="122"/>
+      <c r="B35" s="116"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="115"/>
+      <c r="G35" s="115"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="122"/>
+      <c r="B36" s="116"/>
+      <c r="C36" s="115"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="122"/>
+      <c r="B37" s="116"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="115"/>
+      <c r="E37" s="115"/>
+      <c r="F37" s="115"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="122"/>
+      <c r="B38" s="116"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="115"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="115"/>
+      <c r="H38" s="115"/>
+      <c r="I38" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="122"/>
+      <c r="B39" s="116"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="115"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="115"/>
+      <c r="H39" s="115"/>
+      <c r="I39" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="122"/>
+      <c r="B40" s="116"/>
+      <c r="C40" s="115"/>
+      <c r="D40" s="115"/>
+      <c r="E40" s="115"/>
+      <c r="F40" s="115"/>
+      <c r="G40" s="115"/>
+      <c r="H40" s="115"/>
+      <c r="I40" s="123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="126"/>
+      <c r="B41" s="127"/>
+      <c r="C41" s="128"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="128"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="128"/>
+      <c r="I41" s="129" t="s">
+        <v>412</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="I1:I41" xr:uid="{AC08E385-7096-4F5B-AACD-9DFB3906EA65}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E163D791-3C20-4CD6-AB2B-18D400D6B471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3D8C58-BB93-4D0D-B535-F51BCC3D4442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="540" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1010" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -3253,10 +3253,10 @@
         <v>104</v>
       </c>
       <c r="G16" s="22">
-        <v>41.250160000000001</v>
+        <v>41.382539999999999</v>
       </c>
       <c r="H16" s="22">
-        <v>41.119022999999999</v>
+        <v>41.513060000000003</v>
       </c>
       <c r="J16">
         <v>8</v>

--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\BitkiHaritası_SS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFE26DD-2F50-4BC2-9357-19B873C7A751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33FC34-613E-4BAE-B1FA-5CCD151C1A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2760" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -2527,38 +2527,30 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2575,7 +2567,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3945,10 +3945,10 @@
         <v>102</v>
       </c>
       <c r="G36" s="22">
-        <v>41.168770000000002</v>
+        <v>41.115839999999999</v>
       </c>
       <c r="H36" s="22">
-        <v>41.339165999999999</v>
+        <v>41.611510000000003</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -6692,10 +6692,10 @@
         <v>406</v>
       </c>
       <c r="G130" s="25">
-        <v>41.154060000000001</v>
+        <v>41.136189999999999</v>
       </c>
       <c r="H130" s="25">
-        <v>41.353259999999999</v>
+        <v>41.545990000000003</v>
       </c>
       <c r="J130" t="s">
         <v>406</v>
@@ -6721,10 +6721,10 @@
         <v>102</v>
       </c>
       <c r="G131" s="26">
-        <v>41.154060000000001</v>
+        <v>41.168590000000002</v>
       </c>
       <c r="H131" s="26">
-        <v>41.353259999999999</v>
+        <v>41.487879999999997</v>
       </c>
       <c r="J131">
         <v>5</v>
@@ -6750,10 +6750,10 @@
         <v>333</v>
       </c>
       <c r="G132" s="25">
-        <v>41.15372</v>
+        <v>41.185119999999998</v>
       </c>
       <c r="H132" s="25">
-        <v>41.35445</v>
+        <v>41.486020000000003</v>
       </c>
       <c r="J132">
         <v>21</v>
@@ -6779,10 +6779,10 @@
         <v>408</v>
       </c>
       <c r="G133" s="26">
-        <v>41.173789999999997</v>
+        <v>41.235610000000001</v>
       </c>
       <c r="H133" s="26">
-        <v>41.34778</v>
+        <v>41.449300000000001</v>
       </c>
       <c r="J133" t="s">
         <v>405</v>
@@ -6808,10 +6808,10 @@
         <v>406</v>
       </c>
       <c r="G134" s="25">
-        <v>41.172330000000002</v>
+        <v>41.193390000000001</v>
       </c>
       <c r="H134" s="25">
-        <v>41.341079999999998</v>
+        <v>41.384360000000001</v>
       </c>
       <c r="J134" t="s">
         <v>406</v>
@@ -10482,7 +10482,7 @@
       <c r="H260" s="33">
         <v>41.897970000000001</v>
       </c>
-      <c r="K260" s="135"/>
+      <c r="K260" s="119"/>
     </row>
     <row r="261" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A261">
@@ -14006,10 +14006,10 @@
         <v>311</v>
       </c>
       <c r="G395" s="87">
-        <v>41.478020000000001</v>
+        <v>41.468580000000003</v>
       </c>
       <c r="H395" s="87">
-        <v>41.893880000000003</v>
+        <v>41.909739999999999</v>
       </c>
     </row>
     <row r="396" spans="1:8" ht="16" x14ac:dyDescent="0.35">
@@ -23551,38 +23551,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="131" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="130" t="s">
+      <c r="C1" s="131"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="128" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="130"/>
-      <c r="G1" s="131" t="s">
+      <c r="F1" s="128"/>
+      <c r="G1" s="129" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
-      <c r="M1" s="126" t="s">
+      <c r="M1" s="120" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="55" t="s">
         <v>260</v>
       </c>
       <c r="D2" s="56"/>
-      <c r="E2" s="124" t="s">
+      <c r="E2" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="125"/>
+      <c r="F2" s="127"/>
       <c r="G2" s="60" t="s">
         <v>240</v>
       </c>
@@ -23605,15 +23605,15 @@
       <c r="L3" s="59"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="122" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="124" t="s">
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="125"/>
+      <c r="F4" s="127"/>
       <c r="G4" s="60" t="s">
         <v>242</v>
       </c>
@@ -23712,11 +23712,11 @@
       <c r="L11" s="59"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="119" t="s">
+      <c r="B12" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="119"/>
-      <c r="D12" s="120"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="123"/>
       <c r="G12" s="60" t="s">
         <v>248</v>
       </c>
@@ -23736,11 +23736,11 @@
       <c r="L13" s="59"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="122" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="120"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="123"/>
       <c r="G14" s="60" t="s">
         <v>249</v>
       </c>
@@ -23760,15 +23760,15 @@
       <c r="L15" s="59"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="119" t="s">
+      <c r="B16" s="122" t="s">
         <v>265</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="128" t="s">
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="129"/>
+      <c r="F16" s="125"/>
       <c r="G16" s="60" t="s">
         <v>251</v>
       </c>
@@ -23791,19 +23791,19 @@
       <c r="L17" s="59"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="120"/>
-      <c r="G18" s="121" t="s">
+      <c r="C18" s="122"/>
+      <c r="D18" s="123"/>
+      <c r="G18" s="133" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="123"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="135"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="56"/>
@@ -23815,23 +23815,23 @@
       <c r="L19" s="59"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="122" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="119"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="124" t="s">
+      <c r="C20" s="122"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="126" t="s">
         <v>254</v>
       </c>
-      <c r="F20" s="125"/>
-      <c r="G20" s="121" t="s">
+      <c r="F20" s="127"/>
+      <c r="G20" s="133" t="s">
         <v>253</v>
       </c>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="123"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="135"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="56"/>
@@ -23843,11 +23843,11 @@
       <c r="L21" s="59"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="122" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="120"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="123"/>
       <c r="G22" s="60" t="s">
         <v>255</v>
       </c>
@@ -23867,11 +23867,11 @@
       <c r="L23" s="59"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="120"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="123"/>
       <c r="G24" s="60"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
@@ -23883,11 +23883,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="119" t="s">
+      <c r="B25" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="120"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="123"/>
       <c r="G25" s="60"/>
       <c r="H25" s="59"/>
       <c r="I25" s="59"/>
@@ -23973,6 +23973,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B14:D14"/>
@@ -23984,14 +23992,6 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\BitkiHaritası_SS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33FC34-613E-4BAE-B1FA-5CCD151C1A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B026068A-8818-4387-A809-80C1F7AD1595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2760" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1010" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -2528,29 +2528,38 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2566,15 +2575,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4090,10 +4090,10 @@
         <v>102</v>
       </c>
       <c r="G41" s="23">
-        <v>41.154060000000001</v>
+        <v>41.069540000000003</v>
       </c>
       <c r="H41" s="23">
-        <v>41.353265999999998</v>
+        <v>41.507890000000003</v>
       </c>
       <c r="J41">
         <v>5</v>
@@ -23551,38 +23551,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="134" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="131"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="128" t="s">
+      <c r="C1" s="134"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="131" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="129" t="s">
+      <c r="F1" s="131"/>
+      <c r="G1" s="132" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
-      <c r="M1" s="120" t="s">
+      <c r="M1" s="127" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="55" t="s">
         <v>260</v>
       </c>
       <c r="D2" s="56"/>
-      <c r="E2" s="126" t="s">
+      <c r="E2" s="125" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="127"/>
+      <c r="F2" s="126"/>
       <c r="G2" s="60" t="s">
         <v>240</v>
       </c>
@@ -23605,15 +23605,15 @@
       <c r="L3" s="59"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="120" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="126" t="s">
+      <c r="C4" s="120"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="125" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="127"/>
+      <c r="F4" s="126"/>
       <c r="G4" s="60" t="s">
         <v>242</v>
       </c>
@@ -23712,11 +23712,11 @@
       <c r="L11" s="59"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="122"/>
-      <c r="D12" s="123"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="121"/>
       <c r="G12" s="60" t="s">
         <v>248</v>
       </c>
@@ -23736,11 +23736,11 @@
       <c r="L13" s="59"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="120" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="122"/>
-      <c r="D14" s="123"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121"/>
       <c r="G14" s="60" t="s">
         <v>249</v>
       </c>
@@ -23760,15 +23760,15 @@
       <c r="L15" s="59"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="120" t="s">
         <v>265</v>
       </c>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124" t="s">
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="125"/>
+      <c r="F16" s="130"/>
       <c r="G16" s="60" t="s">
         <v>251</v>
       </c>
@@ -23791,19 +23791,19 @@
       <c r="L17" s="59"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="120" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="122"/>
-      <c r="D18" s="123"/>
-      <c r="G18" s="133" t="s">
+      <c r="C18" s="120"/>
+      <c r="D18" s="121"/>
+      <c r="G18" s="122" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="135"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="124"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="56"/>
@@ -23815,23 +23815,23 @@
       <c r="L19" s="59"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="120" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="122"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="126" t="s">
+      <c r="C20" s="120"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="125" t="s">
         <v>254</v>
       </c>
-      <c r="F20" s="127"/>
-      <c r="G20" s="133" t="s">
+      <c r="F20" s="126"/>
+      <c r="G20" s="122" t="s">
         <v>253</v>
       </c>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="135"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="124"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="56"/>
@@ -23843,11 +23843,11 @@
       <c r="L21" s="59"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="120" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="122"/>
-      <c r="D22" s="123"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
       <c r="G22" s="60" t="s">
         <v>255</v>
       </c>
@@ -23867,11 +23867,11 @@
       <c r="L23" s="59"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="122"/>
-      <c r="D24" s="123"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="121"/>
       <c r="G24" s="60"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
@@ -23883,11 +23883,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="122"/>
-      <c r="D25" s="123"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
       <c r="G25" s="60"/>
       <c r="H25" s="59"/>
       <c r="I25" s="59"/>
@@ -23973,14 +23973,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B14:D14"/>
@@ -23992,6 +23984,14 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B026068A-8818-4387-A809-80C1F7AD1595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F5680F-6767-41A0-B25F-C91017354263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="1010" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="harita bilgileri" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$H$752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$H$749</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sayfa1!$A$135:$I$287</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="447">
   <si>
     <t>CCR</t>
   </si>
@@ -1603,9 +1603,6 @@
     <t>Prunus spp.</t>
   </si>
   <si>
-    <t>Kiraz/Erik</t>
-  </si>
-  <si>
     <t>495</t>
   </si>
   <si>
@@ -1649,9 +1646,6 @@
   </si>
   <si>
     <t>Diospyros kaki</t>
-  </si>
-  <si>
-    <t>Sarı Erik</t>
   </si>
   <si>
     <t>Prunus avium</t>
@@ -2193,7 +2187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2528,38 +2522,29 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2575,6 +2560,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2895,15 +2892,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M752"/>
+  <dimension ref="A1:M749"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
     <col min="2" max="2" width="9.7265625" customWidth="1"/>
     <col min="3" max="3" width="13.1796875" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" customWidth="1"/>
-    <col min="5" max="5" width="30.54296875" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="19.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" customWidth="1"/>
     <col min="10" max="10" width="21.90625" customWidth="1"/>
@@ -3922,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -4418,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -4972,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="M71" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -5294,7 +5291,7 @@
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -5601,10 +5598,10 @@
         <v>391</v>
       </c>
       <c r="E93" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="F93" s="18" t="s">
         <v>407</v>
-      </c>
-      <c r="F93" s="18" t="s">
-        <v>408</v>
       </c>
       <c r="G93" s="26">
         <v>41.250160000000001</v>
@@ -5613,10 +5610,10 @@
         <v>41.79027</v>
       </c>
       <c r="J93" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5630,10 +5627,10 @@
         <v>391</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G94" s="26">
         <v>41.250109999999999</v>
@@ -5642,7 +5639,7 @@
         <v>41.784930000000003</v>
       </c>
       <c r="J94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5717,10 +5714,10 @@
         <v>391</v>
       </c>
       <c r="E97" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="F97" s="18" t="s">
         <v>407</v>
-      </c>
-      <c r="F97" s="18" t="s">
-        <v>408</v>
       </c>
       <c r="G97" s="26">
         <v>41.274000000000001</v>
@@ -5729,10 +5726,10 @@
         <v>41.782550000000001</v>
       </c>
       <c r="J97" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5746,10 +5743,10 @@
         <v>391</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G98" s="25">
         <v>41.278060000000004</v>
@@ -5758,7 +5755,7 @@
         <v>41.783859999999997</v>
       </c>
       <c r="J98" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -5978,10 +5975,10 @@
         <v>391</v>
       </c>
       <c r="E106" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="F106" s="15" t="s">
         <v>407</v>
-      </c>
-      <c r="F106" s="15" t="s">
-        <v>408</v>
       </c>
       <c r="G106" s="25">
         <v>41.377160000000003</v>
@@ -5990,10 +5987,10 @@
         <v>41.610999999999997</v>
       </c>
       <c r="J106" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6007,10 +6004,10 @@
         <v>391</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F107" s="18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G107" s="26">
         <v>41.372219000000001</v>
@@ -6019,10 +6016,10 @@
         <v>41.612439000000002</v>
       </c>
       <c r="J107" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M107" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -6257,7 +6254,7 @@
         <v>2</v>
       </c>
       <c r="M115" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -6347,7 +6344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6361,10 +6358,10 @@
         <v>391</v>
       </c>
       <c r="E119" s="18" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F119" s="18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G119" s="26">
         <v>41.059890000000003</v>
@@ -6373,7 +6370,7 @@
         <v>42.064419999999998</v>
       </c>
       <c r="J119" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6419,10 +6416,10 @@
         <v>391</v>
       </c>
       <c r="E121" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="F121" s="18" t="s">
         <v>407</v>
-      </c>
-      <c r="F121" s="18" t="s">
-        <v>408</v>
       </c>
       <c r="G121" s="26">
         <v>41.066740000000003</v>
@@ -6431,10 +6428,10 @@
         <v>42.073189999999997</v>
       </c>
       <c r="J121" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6448,10 +6445,10 @@
         <v>391</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G122" s="25">
         <v>41.067259999999997</v>
@@ -6460,7 +6457,7 @@
         <v>42.071959999999997</v>
       </c>
       <c r="J122" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -6579,10 +6576,10 @@
         <v>18</v>
       </c>
       <c r="M126" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6628,10 +6625,10 @@
         <v>391</v>
       </c>
       <c r="E128" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="F128" s="65" t="s">
         <v>407</v>
-      </c>
-      <c r="F128" s="65" t="s">
-        <v>408</v>
       </c>
       <c r="G128" s="25">
         <v>41.168770000000002</v>
@@ -6640,7 +6637,7 @@
         <v>41.379159999999999</v>
       </c>
       <c r="J128" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="16" x14ac:dyDescent="0.35">
@@ -6672,7 +6669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6686,10 +6683,10 @@
         <v>391</v>
       </c>
       <c r="E130" s="65" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F130" s="65" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G130" s="25">
         <v>41.136189999999999</v>
@@ -6698,7 +6695,7 @@
         <v>41.545990000000003</v>
       </c>
       <c r="J130" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="16" x14ac:dyDescent="0.35">
@@ -6773,10 +6770,10 @@
         <v>391</v>
       </c>
       <c r="E133" s="69" t="s">
+        <v>406</v>
+      </c>
+      <c r="F133" s="69" t="s">
         <v>407</v>
-      </c>
-      <c r="F133" s="69" t="s">
-        <v>408</v>
       </c>
       <c r="G133" s="26">
         <v>41.235610000000001</v>
@@ -6785,10 +6782,10 @@
         <v>41.449300000000001</v>
       </c>
       <c r="J133" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6802,10 +6799,10 @@
         <v>391</v>
       </c>
       <c r="E134" s="65" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F134" s="65" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G134" s="25">
         <v>41.193390000000001</v>
@@ -6814,7 +6811,7 @@
         <v>41.384360000000001</v>
       </c>
       <c r="J134" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="16" x14ac:dyDescent="0.35">
@@ -8916,8 +8913,8 @@
       <c r="E206" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="F206" s="35" t="s">
-        <v>394</v>
+      <c r="F206" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G206" s="36">
         <v>41.140900000000002</v>
@@ -8974,8 +8971,8 @@
       <c r="E208" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="F208" s="35" t="s">
-        <v>394</v>
+      <c r="F208" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G208" s="36">
         <v>41.140169999999998</v>
@@ -9021,7 +9018,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C210" s="31">
         <v>46179</v>
@@ -9828,7 +9825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>238</v>
       </c>
@@ -9873,8 +9870,8 @@
       <c r="E239" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="F239" s="35" t="s">
-        <v>394</v>
+      <c r="F239" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G239" s="36">
         <v>41.149630000000002</v>
@@ -9886,7 +9883,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>240</v>
       </c>
@@ -10018,8 +10015,8 @@
       <c r="E244" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="F244" s="32" t="s">
-        <v>394</v>
+      <c r="F244" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G244" s="33">
         <v>41.221519999999998</v>
@@ -10031,7 +10028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>245</v>
       </c>
@@ -10179,7 +10176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>250</v>
       </c>
@@ -10253,8 +10250,8 @@
       <c r="E252" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="F252" s="32" t="s">
-        <v>394</v>
+      <c r="F252" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G252" s="33">
         <v>41.25085</v>
@@ -10266,7 +10263,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>253</v>
       </c>
@@ -10353,7 +10350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>256</v>
       </c>
@@ -10405,7 +10402,7 @@
         <v>42.209020000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>258</v>
       </c>
@@ -10484,7 +10481,7 @@
       </c>
       <c r="K260" s="119"/>
     </row>
-    <row r="261" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>261</v>
       </c>
@@ -10536,7 +10533,7 @@
         <v>42.157890000000002</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>263</v>
       </c>
@@ -10692,7 +10689,7 @@
         <v>42.144280000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>269</v>
       </c>
@@ -10744,7 +10741,7 @@
         <v>42.165500000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="16" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" ht="32" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>271</v>
       </c>
@@ -10848,7 +10845,7 @@
         <v>42.178130000000003</v>
       </c>
     </row>
-    <row r="275" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>276</v>
       </c>
@@ -10942,8 +10939,8 @@
       <c r="E278" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="F278" s="35" t="s">
-        <v>394</v>
+      <c r="F278" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G278" s="36">
         <v>41.265230000000003</v>
@@ -10994,8 +10991,8 @@
       <c r="E280" s="35" t="s">
         <v>393</v>
       </c>
-      <c r="F280" s="35" t="s">
-        <v>394</v>
+      <c r="F280" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G280" s="36">
         <v>41.284059999999997</v>
@@ -11082,7 +11079,7 @@
         <v>42.231459999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>285</v>
       </c>
@@ -11576,7 +11573,7 @@
         <v>41.360720000000001</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A303" s="47" t="s">
         <v>167</v>
       </c>
@@ -11592,8 +11589,8 @@
       <c r="E303" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="F303" s="48" t="s">
-        <v>394</v>
+      <c r="F303" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G303" s="48">
         <v>41.323439999999998</v>
@@ -11888,7 +11885,7 @@
         <v>41.663679999999999</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A315" s="47" t="s">
         <v>192</v>
       </c>
@@ -11904,8 +11901,8 @@
       <c r="E315" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="F315" s="48" t="s">
-        <v>394</v>
+      <c r="F315" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G315" s="48">
         <v>40.883429999999997</v>
@@ -12044,7 +12041,7 @@
         <v>41.73959</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A321" s="47" t="s">
         <v>204</v>
       </c>
@@ -12060,8 +12057,8 @@
       <c r="E321" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="F321" s="48" t="s">
-        <v>394</v>
+      <c r="F321" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G321" s="48">
         <v>40.885269999999998</v>
@@ -12356,7 +12353,7 @@
         <v>41.829909999999998</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A333" s="47" t="s">
         <v>228</v>
       </c>
@@ -12372,8 +12369,8 @@
       <c r="E333" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="F333" s="49" t="s">
-        <v>394</v>
+      <c r="F333" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G333" s="48">
         <v>40.998489999999997</v>
@@ -12528,8 +12525,8 @@
       <c r="E339" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F339" s="73" t="s">
-        <v>394</v>
+      <c r="F339" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G339" s="74">
         <v>41.17998</v>
@@ -12658,8 +12655,8 @@
       <c r="E344" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F344" s="77" t="s">
-        <v>394</v>
+      <c r="F344" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G344" s="78">
         <v>41.265340000000002</v>
@@ -12850,7 +12847,7 @@
         <v>42.345939999999999</v>
       </c>
       <c r="J351" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="352" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -12879,7 +12876,7 @@
         <v>42.337038999999997</v>
       </c>
       <c r="M352" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="353" spans="1:9" ht="16" x14ac:dyDescent="0.35">
@@ -12898,8 +12895,8 @@
       <c r="E353" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F353" s="73" t="s">
-        <v>394</v>
+      <c r="F353" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G353" s="74">
         <v>41.27458</v>
@@ -13109,8 +13106,8 @@
       <c r="E361" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F361" s="73" t="s">
-        <v>394</v>
+      <c r="F361" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G361" s="74">
         <v>40.786969999999997</v>
@@ -13135,8 +13132,8 @@
       <c r="E362" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F362" s="77" t="s">
-        <v>394</v>
+      <c r="F362" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G362" s="78">
         <v>40.787550000000003</v>
@@ -13447,8 +13444,8 @@
       <c r="E374" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F374" s="73" t="s">
-        <v>394</v>
+      <c r="F374" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G374" s="74">
         <v>40.982100000000003</v>
@@ -13509,7 +13506,7 @@
         <v>41.39123</v>
       </c>
     </row>
-    <row r="377" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A377" s="47">
         <v>390</v>
       </c>
@@ -13577,8 +13574,8 @@
       <c r="E379" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="F379" s="15" t="s">
-        <v>394</v>
+      <c r="F379" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G379" s="87">
         <v>41.247410000000002</v>
@@ -13587,7 +13584,7 @@
         <v>41.573639999999997</v>
       </c>
       <c r="J379" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="380" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -13607,7 +13604,7 @@
         <v>393</v>
       </c>
       <c r="F380" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G380" s="88">
         <v>41.24062</v>
@@ -13616,10 +13613,10 @@
         <v>41.576425</v>
       </c>
       <c r="J380" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M380" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="381" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -13804,7 +13801,7 @@
         <v>41.566679999999998</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A388" s="47">
         <v>401</v>
       </c>
@@ -13934,7 +13931,7 @@
         <v>41.550060000000002</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A393" s="47">
         <v>406</v>
       </c>
@@ -14133,7 +14130,7 @@
         <v>393</v>
       </c>
       <c r="F400" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G400" s="88">
         <v>41.46322</v>
@@ -14185,7 +14182,7 @@
         <v>393</v>
       </c>
       <c r="F402" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G402" s="88">
         <v>41.39555</v>
@@ -14246,7 +14243,7 @@
         <v>41.676540000000003</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A405" s="47">
         <v>418</v>
       </c>
@@ -14350,7 +14347,7 @@
         <v>41.728430000000003</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A409" s="47">
         <v>422</v>
       </c>
@@ -14402,7 +14399,7 @@
         <v>41.729109999999999</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A411" s="47">
         <v>424</v>
       </c>
@@ -14444,8 +14441,8 @@
       <c r="E412" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F412" s="77" t="s">
-        <v>394</v>
+      <c r="F412" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G412" s="78">
         <v>41.334609999999998</v>
@@ -14480,7 +14477,7 @@
         <v>41.771799999999999</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A414" s="47">
         <v>428</v>
       </c>
@@ -14548,8 +14545,8 @@
       <c r="E416" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F416" s="73" t="s">
-        <v>394</v>
+      <c r="F416" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G416" s="74">
         <v>41.33569</v>
@@ -14558,7 +14555,7 @@
         <v>41.759349999999998</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A417" s="47">
         <v>431</v>
       </c>
@@ -14756,8 +14753,8 @@
       <c r="E424" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F424" s="73" t="s">
-        <v>394</v>
+      <c r="F424" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G424" s="74">
         <v>41.518090000000001</v>
@@ -14818,7 +14815,7 @@
         <v>41.408050000000003</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A427" s="47">
         <v>442</v>
       </c>
@@ -14886,8 +14883,8 @@
       <c r="E429" s="73" t="s">
         <v>393</v>
       </c>
-      <c r="F429" s="73" t="s">
-        <v>394</v>
+      <c r="F429" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G429" s="74">
         <v>41.34281</v>
@@ -14896,7 +14893,7 @@
         <v>41.38409</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A430" s="47">
         <v>445</v>
       </c>
@@ -15000,7 +14997,7 @@
         <v>41.749070000000003</v>
       </c>
     </row>
-    <row r="434" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A434" s="47">
         <v>449</v>
       </c>
@@ -15042,8 +15039,8 @@
       <c r="E435" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F435" s="77" t="s">
-        <v>394</v>
+      <c r="F435" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G435" s="78">
         <v>41.152970000000003</v>
@@ -15130,7 +15127,7 @@
         <v>41.73939</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A439" s="47">
         <v>456</v>
       </c>
@@ -15224,8 +15221,8 @@
       <c r="E442" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F442" s="77" t="s">
-        <v>394</v>
+      <c r="F442" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G442" s="78">
         <v>41.163409999999999</v>
@@ -15234,7 +15231,7 @@
         <v>41.79392</v>
       </c>
     </row>
-    <row r="443" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A443" s="47">
         <v>460</v>
       </c>
@@ -15286,7 +15283,7 @@
         <v>41.42633</v>
       </c>
     </row>
-    <row r="445" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A445" s="47">
         <v>462</v>
       </c>
@@ -15355,7 +15352,7 @@
         <v>393</v>
       </c>
       <c r="F447" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G447" s="88">
         <v>41.330599999999997</v>
@@ -15442,7 +15439,7 @@
         <v>42.307400000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A451" s="47">
         <v>468</v>
       </c>
@@ -15494,7 +15491,7 @@
         <v>42.169930000000001</v>
       </c>
     </row>
-    <row r="453" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A453" s="47">
         <v>470</v>
       </c>
@@ -15520,7 +15517,7 @@
         <v>42.157170000000001</v>
       </c>
     </row>
-    <row r="454" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A454" s="47">
         <v>471</v>
       </c>
@@ -15640,8 +15637,8 @@
       <c r="E458" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="F458" s="15" t="s">
-        <v>394</v>
+      <c r="F458" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G458" s="87">
         <v>41.043059999999997</v>
@@ -15650,7 +15647,7 @@
         <v>42.092179999999999</v>
       </c>
       <c r="J458" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="459" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -15669,8 +15666,8 @@
       <c r="E459" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="F459" s="15" t="s">
-        <v>394</v>
+      <c r="F459" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G459" s="87">
         <v>41.109133999999997</v>
@@ -15696,7 +15693,7 @@
         <v>393</v>
       </c>
       <c r="F460" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G460" s="88">
         <v>41.035223999999999</v>
@@ -15705,10 +15702,10 @@
         <v>42.096122999999999</v>
       </c>
       <c r="J460" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M460" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="461" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -15740,7 +15737,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="462" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A462" s="47">
         <v>479</v>
       </c>
@@ -15792,7 +15789,7 @@
         <v>42.115789999999997</v>
       </c>
     </row>
-    <row r="464" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A464" s="47">
         <v>482</v>
       </c>
@@ -15887,7 +15884,7 @@
         <v>393</v>
       </c>
       <c r="F467" s="18" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="G467" s="88">
         <v>41.282640000000001</v>
@@ -16026,10 +16023,10 @@
         <v>41.782420000000002</v>
       </c>
       <c r="J472" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M472" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="473" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -16084,7 +16081,7 @@
         <v>41.829590000000003</v>
       </c>
     </row>
-    <row r="475" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A475" s="47">
         <v>494</v>
       </c>
@@ -16214,10 +16211,10 @@
         <v>41.885607</v>
       </c>
       <c r="J479" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M479" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="480" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -16236,8 +16233,8 @@
       <c r="E480" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F480" s="77" t="s">
-        <v>394</v>
+      <c r="F480" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G480" s="78">
         <v>40.927570000000003</v>
@@ -16350,7 +16347,7 @@
         <v>41.870750000000001</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A485" s="47">
         <v>505</v>
       </c>
@@ -16444,8 +16441,8 @@
       <c r="E488" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="F488" s="77" t="s">
-        <v>394</v>
+      <c r="F488" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G488" s="78">
         <v>40.689950000000003</v>
@@ -16610,7 +16607,7 @@
         <v>41.55247</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A495" s="47">
         <v>516</v>
       </c>
@@ -16714,7 +16711,7 @@
         <v>41.460790000000003</v>
       </c>
     </row>
-    <row r="499" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A499" s="47">
         <v>522</v>
       </c>
@@ -16740,7 +16737,7 @@
         <v>41.446530000000003</v>
       </c>
     </row>
-    <row r="500" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A500" s="47">
         <v>523</v>
       </c>
@@ -16844,7 +16841,7 @@
         <v>41.266080000000002</v>
       </c>
     </row>
-    <row r="504" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A504" s="47">
         <v>527</v>
       </c>
@@ -16922,7 +16919,7 @@
         <v>41.855580000000003</v>
       </c>
     </row>
-    <row r="507" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A507" s="47">
         <v>530</v>
       </c>
@@ -16948,7 +16945,7 @@
         <v>41.857210000000002</v>
       </c>
     </row>
-    <row r="508" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A508" s="47">
         <v>531</v>
       </c>
@@ -17052,7 +17049,7 @@
         <v>41.917589999999997</v>
       </c>
     </row>
-    <row r="512" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A512" s="47">
         <v>536</v>
       </c>
@@ -17078,7 +17075,7 @@
         <v>41.831420000000001</v>
       </c>
       <c r="J512" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="513" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -17159,7 +17156,7 @@
         <v>41.86965</v>
       </c>
     </row>
-    <row r="516" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A516" s="47">
         <v>540</v>
       </c>
@@ -17185,7 +17182,7 @@
         <v>41.771599999999999</v>
       </c>
     </row>
-    <row r="517" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A517" s="47">
         <v>541</v>
       </c>
@@ -17211,7 +17208,7 @@
         <v>41.829411</v>
       </c>
       <c r="M517" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="518" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -17266,7 +17263,7 @@
         <v>41.77758</v>
       </c>
       <c r="J519" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="520" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -17295,7 +17292,7 @@
         <v>41.782829999999997</v>
       </c>
       <c r="M520" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="521" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -17376,7 +17373,7 @@
         <v>41.81241</v>
       </c>
     </row>
-    <row r="524" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A524" s="47">
         <v>548</v>
       </c>
@@ -17506,7 +17503,7 @@
         <v>41.763869999999997</v>
       </c>
     </row>
-    <row r="529" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A529" s="47">
         <v>553</v>
       </c>
@@ -17766,7 +17763,7 @@
         <v>41.708759999999998</v>
       </c>
       <c r="J538" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="539" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -17795,10 +17792,10 @@
         <v>41.716400999999998</v>
       </c>
       <c r="J539" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M539" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="540" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18243,7 +18240,7 @@
         <v>42.352069999999998</v>
       </c>
     </row>
-    <row r="557" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A557" s="47">
         <v>581</v>
       </c>
@@ -18347,7 +18344,7 @@
         <v>42.384050000000002</v>
       </c>
     </row>
-    <row r="561" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A561" s="47">
         <v>585</v>
       </c>
@@ -18361,10 +18358,10 @@
         <v>391</v>
       </c>
       <c r="E561" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F561" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G561" s="78">
         <v>41.274520000000003</v>
@@ -18373,7 +18370,7 @@
         <v>42.205869999999997</v>
       </c>
       <c r="J561" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="562" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18416,10 +18413,10 @@
         <v>391</v>
       </c>
       <c r="E563" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="F563" s="77" t="s">
         <v>407</v>
-      </c>
-      <c r="F563" s="77" t="s">
-        <v>408</v>
       </c>
       <c r="G563" s="78">
         <v>41.271867</v>
@@ -18428,10 +18425,10 @@
         <v>42.200944</v>
       </c>
       <c r="J563" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M563" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="564" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18512,7 +18509,7 @@
         <v>41.793317000000002</v>
       </c>
       <c r="M566" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="567" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18541,7 +18538,7 @@
         <v>41.795960000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A568" s="47">
         <v>592</v>
       </c>
@@ -18555,10 +18552,10 @@
         <v>391</v>
       </c>
       <c r="E568" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F568" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G568" s="78">
         <v>41.278060000000004</v>
@@ -18567,7 +18564,7 @@
         <v>41.73386</v>
       </c>
       <c r="J568" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="569" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18596,7 +18593,7 @@
         <v>42.096021</v>
       </c>
       <c r="M569" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="570" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18625,7 +18622,7 @@
         <v>41.788736</v>
       </c>
       <c r="M570" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="571" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18654,7 +18651,7 @@
         <v>41.762746999999997</v>
       </c>
       <c r="M571" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="572" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18671,10 +18668,10 @@
         <v>391</v>
       </c>
       <c r="E572" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="F572" s="77" t="s">
         <v>407</v>
-      </c>
-      <c r="F572" s="77" t="s">
-        <v>408</v>
       </c>
       <c r="G572" s="78">
         <v>41.066740000000003</v>
@@ -18683,7 +18680,7 @@
         <v>42.033189999999998</v>
       </c>
       <c r="J572" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="573" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18700,10 +18697,10 @@
         <v>391</v>
       </c>
       <c r="E573" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="F573" s="73" t="s">
         <v>407</v>
-      </c>
-      <c r="F573" s="73" t="s">
-        <v>408</v>
       </c>
       <c r="G573" s="74">
         <v>41.121699999999997</v>
@@ -18712,7 +18709,7 @@
         <v>41.657719999999998</v>
       </c>
       <c r="J573" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="574" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18767,7 +18764,7 @@
         <v>41.647939999999998</v>
       </c>
     </row>
-    <row r="576" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A576" s="47">
         <v>600</v>
       </c>
@@ -18781,10 +18778,10 @@
         <v>391</v>
       </c>
       <c r="E576" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F576" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G576" s="78">
         <v>41.250160000000001</v>
@@ -18793,7 +18790,7 @@
         <v>41.790230000000001</v>
       </c>
       <c r="J576" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="577" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18810,10 +18807,10 @@
         <v>391</v>
       </c>
       <c r="E577" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="F577" s="73" t="s">
         <v>407</v>
-      </c>
-      <c r="F577" s="73" t="s">
-        <v>408</v>
       </c>
       <c r="G577" s="74">
         <v>41.371212999999997</v>
@@ -18822,10 +18819,10 @@
         <v>41.614167999999999</v>
       </c>
       <c r="J577" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M577" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="578" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18868,10 +18865,10 @@
         <v>391</v>
       </c>
       <c r="E579" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="F579" s="73" t="s">
         <v>407</v>
-      </c>
-      <c r="F579" s="73" t="s">
-        <v>408</v>
       </c>
       <c r="G579" s="74">
         <v>41.156410000000001</v>
@@ -18880,7 +18877,7 @@
         <v>41.51229</v>
       </c>
       <c r="J579" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="580" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18897,10 +18894,10 @@
         <v>391</v>
       </c>
       <c r="E580" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="F580" s="77" t="s">
         <v>407</v>
-      </c>
-      <c r="F580" s="77" t="s">
-        <v>408</v>
       </c>
       <c r="G580" s="78">
         <v>41.253748999999999</v>
@@ -18909,10 +18906,10 @@
         <v>41.800646999999998</v>
       </c>
       <c r="J580" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M580" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="581" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -18941,10 +18938,10 @@
         <v>42.090766000000002</v>
       </c>
       <c r="M581" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="582" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A582" s="47">
         <v>606</v>
       </c>
@@ -18958,10 +18955,10 @@
         <v>391</v>
       </c>
       <c r="E582" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F582" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G582" s="78">
         <v>41.376789000000002</v>
@@ -18970,10 +18967,10 @@
         <v>41.600631999999997</v>
       </c>
       <c r="J582" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M582" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="583" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -19002,7 +18999,7 @@
         <v>42.105010999999998</v>
       </c>
       <c r="M583" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="584" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -19045,10 +19042,10 @@
         <v>391</v>
       </c>
       <c r="E585" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="F585" s="73" t="s">
         <v>407</v>
-      </c>
-      <c r="F585" s="73" t="s">
-        <v>408</v>
       </c>
       <c r="G585" s="74">
         <v>41.279339</v>
@@ -19057,10 +19054,10 @@
         <v>41.780526000000002</v>
       </c>
       <c r="J585" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M585" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="586" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -19089,10 +19086,10 @@
         <v>42.071809999999999</v>
       </c>
       <c r="M586" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="587" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A587" s="47">
         <v>611</v>
       </c>
@@ -19106,10 +19103,10 @@
         <v>391</v>
       </c>
       <c r="E587" s="73" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F587" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G587" s="74">
         <v>41.138249999999999</v>
@@ -19118,7 +19115,7 @@
         <v>41.671950000000002</v>
       </c>
       <c r="J587" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="588" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -19147,7 +19144,7 @@
         <v>41.586190000000002</v>
       </c>
     </row>
-    <row r="589" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A589" s="47">
         <v>613</v>
       </c>
@@ -19161,10 +19158,10 @@
         <v>391</v>
       </c>
       <c r="E589" s="73" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F589" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G589" s="74">
         <v>41.06326</v>
@@ -19173,10 +19170,10 @@
         <v>42.031959999999998</v>
       </c>
       <c r="J589" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="590" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A590" s="47">
         <v>614</v>
       </c>
@@ -19190,10 +19187,10 @@
         <v>391</v>
       </c>
       <c r="E590" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F590" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G590" s="78">
         <v>41.059829999999998</v>
@@ -19202,7 +19199,7 @@
         <v>42.064419999999998</v>
       </c>
       <c r="J590" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="591" spans="1:13" ht="16" x14ac:dyDescent="0.35">
@@ -19231,10 +19228,10 @@
         <v>41.668211999999997</v>
       </c>
       <c r="M591" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="592" spans="1:13" ht="16" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" ht="32" x14ac:dyDescent="0.35">
       <c r="A592" s="47">
         <v>616</v>
       </c>
@@ -19248,10 +19245,10 @@
         <v>391</v>
       </c>
       <c r="E592" s="77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F592" s="77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G592" s="78">
         <v>41.177239999999998</v>
@@ -19260,10 +19257,10 @@
         <v>41.479239999999997</v>
       </c>
       <c r="J592" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="593" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A593" s="47">
         <v>617</v>
       </c>
@@ -19289,7 +19286,7 @@
         <v>41.790230000000001</v>
       </c>
     </row>
-    <row r="594" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A594" s="47">
         <v>618</v>
       </c>
@@ -19315,7 +19312,7 @@
         <v>42.170459999999999</v>
       </c>
     </row>
-    <row r="595" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A595" s="47">
         <v>619</v>
       </c>
@@ -19341,7 +19338,7 @@
         <v>42.170459999999999</v>
       </c>
     </row>
-    <row r="596" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A596" s="47">
         <v>620</v>
       </c>
@@ -19367,7 +19364,7 @@
         <v>42.160739999999997</v>
       </c>
     </row>
-    <row r="597" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A597" s="47">
         <v>621</v>
       </c>
@@ -19393,7 +19390,7 @@
         <v>42.162460000000003</v>
       </c>
     </row>
-    <row r="598" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A598" s="47">
         <v>622</v>
       </c>
@@ -19419,157 +19416,154 @@
         <v>42.162460000000003</v>
       </c>
     </row>
-    <row r="599" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A599" s="47">
-        <v>623</v>
-      </c>
-      <c r="B599" s="75">
-        <v>461</v>
-      </c>
-      <c r="C599" s="76">
+        <v>624</v>
+      </c>
+      <c r="B599" s="71">
+        <v>462</v>
+      </c>
+      <c r="C599" s="72">
         <v>46275</v>
       </c>
-      <c r="D599" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E599" s="77" t="s">
-        <v>393</v>
-      </c>
-      <c r="F599" s="77" t="s">
-        <v>394</v>
-      </c>
-      <c r="G599" s="78">
-        <v>41.047339999999998</v>
-      </c>
-      <c r="H599" s="78">
-        <v>42.161349999999999</v>
-      </c>
-      <c r="J599" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="600" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="D599" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="E599" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="F599" s="73" t="s">
+        <v>377</v>
+      </c>
+      <c r="G599" s="74">
+        <v>41.051569999999998</v>
+      </c>
+      <c r="H599" s="74">
+        <v>42.172460000000001</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A600" s="47">
-        <v>624</v>
-      </c>
-      <c r="B600" s="71">
-        <v>462</v>
-      </c>
-      <c r="C600" s="72">
+        <v>625</v>
+      </c>
+      <c r="B600" s="75">
+        <v>463</v>
+      </c>
+      <c r="C600" s="76">
         <v>46275</v>
       </c>
-      <c r="D600" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="E600" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="F600" s="73" t="s">
-        <v>377</v>
-      </c>
-      <c r="G600" s="74">
-        <v>41.051569999999998</v>
-      </c>
-      <c r="H600" s="74">
-        <v>42.172460000000001</v>
-      </c>
-    </row>
-    <row r="601" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="D600" s="75" t="s">
+        <v>111</v>
+      </c>
+      <c r="E600" s="77" t="s">
+        <v>329</v>
+      </c>
+      <c r="F600" s="77" t="s">
+        <v>368</v>
+      </c>
+      <c r="G600" s="78">
+        <v>41.06015</v>
+      </c>
+      <c r="H600" s="78">
+        <v>42.176189999999998</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A601" s="47">
-        <v>625</v>
-      </c>
-      <c r="B601" s="75">
-        <v>463</v>
-      </c>
-      <c r="C601" s="76">
+        <v>626</v>
+      </c>
+      <c r="B601" s="71">
+        <v>464</v>
+      </c>
+      <c r="C601" s="72">
         <v>46275</v>
       </c>
-      <c r="D601" s="75" t="s">
-        <v>111</v>
-      </c>
-      <c r="E601" s="77" t="s">
-        <v>329</v>
-      </c>
-      <c r="F601" s="77" t="s">
-        <v>368</v>
-      </c>
-      <c r="G601" s="78">
-        <v>41.06015</v>
-      </c>
-      <c r="H601" s="78">
-        <v>42.176189999999998</v>
-      </c>
-    </row>
-    <row r="602" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="D601" s="71" t="s">
+        <v>366</v>
+      </c>
+      <c r="E601" s="73" t="s">
+        <v>367</v>
+      </c>
+      <c r="F601" s="73" t="s">
+        <v>369</v>
+      </c>
+      <c r="G601" s="74">
+        <v>41.081600000000002</v>
+      </c>
+      <c r="H601" s="74">
+        <v>42.142980000000001</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A602" s="47">
-        <v>626</v>
-      </c>
-      <c r="B602" s="71">
-        <v>464</v>
-      </c>
-      <c r="C602" s="72">
+        <v>627</v>
+      </c>
+      <c r="B602" s="75">
+        <v>465</v>
+      </c>
+      <c r="C602" s="76">
         <v>46275</v>
       </c>
-      <c r="D602" s="71" t="s">
-        <v>366</v>
-      </c>
-      <c r="E602" s="73" t="s">
-        <v>367</v>
-      </c>
-      <c r="F602" s="73" t="s">
-        <v>369</v>
-      </c>
-      <c r="G602" s="74">
-        <v>41.081600000000002</v>
-      </c>
-      <c r="H602" s="74">
-        <v>42.142980000000001</v>
-      </c>
-    </row>
-    <row r="603" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="D602" s="75" t="s">
+        <v>334</v>
+      </c>
+      <c r="E602" s="77" t="s">
+        <v>335</v>
+      </c>
+      <c r="F602" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="G602" s="78">
+        <v>41.09966</v>
+      </c>
+      <c r="H602" s="78">
+        <v>42.107289999999999</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A603" s="47">
-        <v>627</v>
-      </c>
-      <c r="B603" s="75">
-        <v>465</v>
-      </c>
-      <c r="C603" s="76">
+        <v>628</v>
+      </c>
+      <c r="B603" s="71">
+        <v>466</v>
+      </c>
+      <c r="C603" s="72">
         <v>46275</v>
       </c>
-      <c r="D603" s="75" t="s">
-        <v>334</v>
-      </c>
-      <c r="E603" s="77" t="s">
-        <v>335</v>
-      </c>
-      <c r="F603" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="G603" s="78">
-        <v>41.09966</v>
-      </c>
-      <c r="H603" s="78">
-        <v>42.107289999999999</v>
-      </c>
-    </row>
-    <row r="604" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="D603" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E603" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="F603" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="G603" s="74">
+        <v>41.144710000000003</v>
+      </c>
+      <c r="H603" s="74">
+        <v>42.139490000000002</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A604" s="47">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B604" s="71">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C604" s="72">
         <v>46275</v>
       </c>
       <c r="D604" s="71" t="s">
-        <v>112</v>
+        <v>323</v>
       </c>
       <c r="E604" s="73" t="s">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="F604" s="73" t="s">
-        <v>114</v>
+        <v>325</v>
       </c>
       <c r="G604" s="74">
         <v>41.144710000000003</v>
@@ -19578,24 +19572,24 @@
         <v>42.139490000000002</v>
       </c>
     </row>
-    <row r="605" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A605" s="47">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B605" s="75">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C605" s="76">
         <v>46275</v>
       </c>
       <c r="D605" s="75" t="s">
-        <v>392</v>
+        <v>326</v>
       </c>
       <c r="E605" s="77" t="s">
-        <v>393</v>
+        <v>327</v>
       </c>
       <c r="F605" s="77" t="s">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="G605" s="78">
         <v>41.144710000000003</v>
@@ -19603,28 +19597,25 @@
       <c r="H605" s="78">
         <v>42.139490000000002</v>
       </c>
-      <c r="J605" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="606" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="606" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A606" s="47">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B606" s="71">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C606" s="72">
         <v>46275</v>
       </c>
       <c r="D606" s="71" t="s">
-        <v>323</v>
+        <v>115</v>
       </c>
       <c r="E606" s="73" t="s">
-        <v>324</v>
+        <v>116</v>
       </c>
       <c r="F606" s="73" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="G606" s="74">
         <v>41.144710000000003</v>
@@ -19633,24 +19624,24 @@
         <v>42.139490000000002</v>
       </c>
     </row>
-    <row r="607" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A607" s="47">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B607" s="75">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C607" s="76">
         <v>46275</v>
       </c>
       <c r="D607" s="75" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E607" s="77" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F607" s="77" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G607" s="78">
         <v>41.144710000000003</v>
@@ -19659,24 +19650,24 @@
         <v>42.139490000000002</v>
       </c>
     </row>
-    <row r="608" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A608" s="47">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B608" s="71">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C608" s="72">
         <v>46275</v>
       </c>
       <c r="D608" s="71" t="s">
-        <v>115</v>
+        <v>319</v>
       </c>
       <c r="E608" s="73" t="s">
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="F608" s="73" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="G608" s="74">
         <v>41.144710000000003</v>
@@ -19687,22 +19678,22 @@
     </row>
     <row r="609" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A609" s="47">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B609" s="75">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C609" s="76">
         <v>46275</v>
       </c>
       <c r="D609" s="75" t="s">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="E609" s="77" t="s">
-        <v>331</v>
+        <v>109</v>
       </c>
       <c r="F609" s="77" t="s">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="G609" s="78">
         <v>41.144710000000003</v>
@@ -19713,221 +19704,224 @@
     </row>
     <row r="610" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A610" s="47">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B610" s="71">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C610" s="72">
         <v>46275</v>
       </c>
       <c r="D610" s="71" t="s">
-        <v>319</v>
+        <v>2</v>
       </c>
       <c r="E610" s="73" t="s">
-        <v>386</v>
+        <v>13</v>
       </c>
       <c r="F610" s="73" t="s">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="G610" s="74">
-        <v>41.144710000000003</v>
+        <v>41.132269999999998</v>
       </c>
       <c r="H610" s="74">
-        <v>42.139490000000002</v>
+        <v>42.146459999999998</v>
       </c>
     </row>
     <row r="611" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A611" s="47">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B611" s="75">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C611" s="76">
         <v>46275</v>
       </c>
       <c r="D611" s="75" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="E611" s="77" t="s">
-        <v>109</v>
+        <v>324</v>
       </c>
       <c r="F611" s="77" t="s">
-        <v>110</v>
+        <v>325</v>
       </c>
       <c r="G611" s="78">
-        <v>41.144710000000003</v>
+        <v>41.132269999999998</v>
       </c>
       <c r="H611" s="78">
-        <v>42.139490000000002</v>
+        <v>42.146459999999998</v>
       </c>
     </row>
     <row r="612" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A612" s="47">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B612" s="71">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C612" s="72">
         <v>46275</v>
       </c>
       <c r="D612" s="71" t="s">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="E612" s="73" t="s">
-        <v>13</v>
+        <v>380</v>
       </c>
       <c r="F612" s="73" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="G612" s="74">
-        <v>41.132269999999998</v>
+        <v>41.139060000000001</v>
       </c>
       <c r="H612" s="74">
-        <v>42.146459999999998</v>
+        <v>42.161200000000001</v>
       </c>
     </row>
     <row r="613" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A613" s="47">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B613" s="75">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C613" s="76">
         <v>46275</v>
       </c>
       <c r="D613" s="75" t="s">
-        <v>323</v>
+        <v>392</v>
       </c>
       <c r="E613" s="77" t="s">
-        <v>324</v>
-      </c>
-      <c r="F613" s="77" t="s">
-        <v>325</v>
+        <v>393</v>
+      </c>
+      <c r="F613" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G613" s="78">
-        <v>41.132269999999998</v>
+        <v>41.139060000000001</v>
       </c>
       <c r="H613" s="78">
-        <v>42.146459999999998</v>
-      </c>
-    </row>
-    <row r="614" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+        <v>42.161200000000001</v>
+      </c>
+      <c r="J613" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A614" s="47">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B614" s="71">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C614" s="72">
         <v>46275</v>
       </c>
       <c r="D614" s="71" t="s">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="E614" s="73" t="s">
-        <v>380</v>
+        <v>107</v>
       </c>
       <c r="F614" s="73" t="s">
-        <v>120</v>
+        <v>377</v>
       </c>
       <c r="G614" s="74">
-        <v>41.139060000000001</v>
+        <v>41.13109</v>
       </c>
       <c r="H614" s="74">
-        <v>42.161200000000001</v>
+        <v>42.13026</v>
       </c>
     </row>
     <row r="615" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A615" s="47">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B615" s="75">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C615" s="76">
         <v>46275</v>
       </c>
       <c r="D615" s="75" t="s">
-        <v>392</v>
+        <v>111</v>
       </c>
       <c r="E615" s="77" t="s">
-        <v>393</v>
+        <v>329</v>
       </c>
       <c r="F615" s="77" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="G615" s="78">
         <v>41.139060000000001</v>
       </c>
       <c r="H615" s="78">
-        <v>42.161200000000001</v>
-      </c>
-      <c r="J615" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="616" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+        <v>42.128100000000003</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A616" s="47">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B616" s="71">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C616" s="72">
         <v>46275</v>
       </c>
       <c r="D616" s="71" t="s">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="E616" s="73" t="s">
-        <v>107</v>
+        <v>408</v>
       </c>
       <c r="F616" s="73" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="G616" s="74">
-        <v>41.13109</v>
+        <v>41.126199999999997</v>
       </c>
       <c r="H616" s="74">
-        <v>42.13026</v>
+        <v>42.109119999999997</v>
+      </c>
+      <c r="J616" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="617" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A617" s="47">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B617" s="75">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C617" s="76">
         <v>46275</v>
       </c>
       <c r="D617" s="75" t="s">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="E617" s="77" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="F617" s="77" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G617" s="78">
-        <v>41.139060000000001</v>
+        <v>41.126199999999997</v>
       </c>
       <c r="H617" s="78">
-        <v>42.128100000000003</v>
+        <v>42.109119999999997</v>
       </c>
     </row>
     <row r="618" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A618" s="47">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B618" s="71">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C618" s="72">
         <v>46275</v>
@@ -19936,120 +19930,117 @@
         <v>391</v>
       </c>
       <c r="E618" s="73" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F618" s="73" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G618" s="74">
-        <v>41.126199999999997</v>
+        <v>41.125599999999999</v>
       </c>
       <c r="H618" s="74">
-        <v>42.109119999999997</v>
+        <v>42.108969999999999</v>
       </c>
       <c r="J618" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="619" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A619" s="47">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B619" s="75">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C619" s="76">
         <v>46275</v>
       </c>
       <c r="D619" s="75" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="E619" s="77" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="F619" s="77" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="G619" s="78">
-        <v>41.126199999999997</v>
+        <v>41.124099999999999</v>
       </c>
       <c r="H619" s="78">
-        <v>42.109119999999997</v>
-      </c>
-    </row>
-    <row r="620" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+        <v>42.075049999999997</v>
+      </c>
+    </row>
+    <row r="620" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A620" s="47">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B620" s="71">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C620" s="72">
         <v>46275</v>
       </c>
       <c r="D620" s="71" t="s">
-        <v>391</v>
+        <v>1</v>
       </c>
       <c r="E620" s="73" t="s">
-        <v>407</v>
+        <v>107</v>
       </c>
       <c r="F620" s="73" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="G620" s="74">
-        <v>41.125599999999999</v>
+        <v>41.125360000000001</v>
       </c>
       <c r="H620" s="74">
-        <v>42.108969999999999</v>
-      </c>
-      <c r="J620" t="s">
-        <v>405</v>
+        <v>41.977890000000002</v>
       </c>
     </row>
     <row r="621" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A621" s="47">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B621" s="75">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C621" s="76">
         <v>46275</v>
       </c>
       <c r="D621" s="75" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="E621" s="77" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="F621" s="77" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="G621" s="78">
-        <v>41.124099999999999</v>
+        <v>41.125360000000001</v>
       </c>
       <c r="H621" s="78">
-        <v>42.075049999999997</v>
+        <v>41.977890000000002</v>
       </c>
     </row>
     <row r="622" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A622" s="47">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B622" s="71">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C622" s="72">
         <v>46275</v>
       </c>
       <c r="D622" s="71" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="E622" s="73" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F622" s="73" t="s">
-        <v>377</v>
+        <v>110</v>
       </c>
       <c r="G622" s="74">
         <v>41.125360000000001</v>
@@ -20060,22 +20051,22 @@
     </row>
     <row r="623" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A623" s="47">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B623" s="75">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C623" s="76">
         <v>46275</v>
       </c>
       <c r="D623" s="75" t="s">
-        <v>319</v>
+        <v>392</v>
       </c>
       <c r="E623" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F623" s="77" t="s">
-        <v>320</v>
+        <v>393</v>
+      </c>
+      <c r="F623" s="18" t="s">
+        <v>443</v>
       </c>
       <c r="G623" s="78">
         <v>41.125360000000001</v>
@@ -20083,615 +20074,615 @@
       <c r="H623" s="78">
         <v>41.977890000000002</v>
       </c>
+      <c r="J623" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="624" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A624" s="47">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B624" s="71">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C624" s="72">
         <v>46275</v>
       </c>
       <c r="D624" s="71" t="s">
-        <v>108</v>
+        <v>323</v>
       </c>
       <c r="E624" s="73" t="s">
-        <v>109</v>
+        <v>324</v>
       </c>
       <c r="F624" s="73" t="s">
-        <v>110</v>
+        <v>325</v>
       </c>
       <c r="G624" s="74">
-        <v>41.125360000000001</v>
+        <v>41.128439999999998</v>
       </c>
       <c r="H624" s="74">
-        <v>41.977890000000002</v>
+        <v>41.97916</v>
       </c>
     </row>
     <row r="625" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A625" s="47">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B625" s="75">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C625" s="76">
         <v>46275</v>
       </c>
       <c r="D625" s="75" t="s">
-        <v>392</v>
+        <v>326</v>
       </c>
       <c r="E625" s="77" t="s">
-        <v>393</v>
+        <v>327</v>
       </c>
       <c r="F625" s="77" t="s">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="G625" s="78">
-        <v>41.125360000000001</v>
+        <v>41.127890000000001</v>
       </c>
       <c r="H625" s="78">
-        <v>41.977890000000002</v>
-      </c>
-      <c r="J625" t="s">
-        <v>411</v>
+        <v>41.976900000000001</v>
       </c>
     </row>
     <row r="626" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A626" s="47">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B626" s="71">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C626" s="72">
         <v>46275</v>
       </c>
       <c r="D626" s="71" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E626" s="73" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F626" s="73" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="G626" s="74">
-        <v>41.128439999999998</v>
+        <v>41.127890000000001</v>
       </c>
       <c r="H626" s="74">
-        <v>41.97916</v>
+        <v>41.976900000000001</v>
       </c>
     </row>
     <row r="627" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A627" s="47">
-        <v>651</v>
-      </c>
-      <c r="B627" s="75">
-        <v>489</v>
-      </c>
-      <c r="C627" s="76">
+        <v>654</v>
+      </c>
+      <c r="B627" s="71">
+        <v>492</v>
+      </c>
+      <c r="C627" s="72">
         <v>46275</v>
       </c>
-      <c r="D627" s="75" t="s">
-        <v>326</v>
-      </c>
-      <c r="E627" s="77" t="s">
-        <v>327</v>
-      </c>
-      <c r="F627" s="77" t="s">
-        <v>328</v>
-      </c>
-      <c r="G627" s="78">
+      <c r="D627" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="E627" s="73" t="s">
+        <v>329</v>
+      </c>
+      <c r="F627" s="73" t="s">
+        <v>368</v>
+      </c>
+      <c r="G627" s="74">
         <v>41.127890000000001</v>
       </c>
-      <c r="H627" s="78">
+      <c r="H627" s="74">
         <v>41.976900000000001</v>
       </c>
     </row>
     <row r="628" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A628" s="47">
-        <v>652</v>
-      </c>
-      <c r="B628" s="71">
-        <v>490</v>
-      </c>
-      <c r="C628" s="72">
+        <v>655</v>
+      </c>
+      <c r="B628" s="75">
+        <v>493</v>
+      </c>
+      <c r="C628" s="76">
         <v>46275</v>
       </c>
-      <c r="D628" s="71" t="s">
-        <v>330</v>
-      </c>
-      <c r="E628" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="F628" s="73" t="s">
-        <v>332</v>
-      </c>
-      <c r="G628" s="74">
+      <c r="D628" s="75" t="s">
+        <v>366</v>
+      </c>
+      <c r="E628" s="77" t="s">
+        <v>367</v>
+      </c>
+      <c r="F628" s="77" t="s">
+        <v>369</v>
+      </c>
+      <c r="G628" s="78">
         <v>41.127890000000001</v>
       </c>
-      <c r="H628" s="74">
+      <c r="H628" s="78">
         <v>41.976900000000001</v>
       </c>
     </row>
     <row r="629" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A629" s="47">
-        <v>653</v>
-      </c>
-      <c r="B629" s="75">
-        <v>491</v>
-      </c>
-      <c r="C629" s="76">
+        <v>656</v>
+      </c>
+      <c r="B629" s="71">
+        <v>494</v>
+      </c>
+      <c r="C629" s="72">
         <v>46275</v>
       </c>
-      <c r="D629" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E629" s="77" t="s">
-        <v>393</v>
-      </c>
-      <c r="F629" s="77" t="s">
-        <v>394</v>
-      </c>
-      <c r="G629" s="78">
-        <v>41.127890000000001</v>
-      </c>
-      <c r="H629" s="78">
-        <v>41.976900000000001</v>
-      </c>
-      <c r="J629" t="s">
-        <v>410</v>
+      <c r="D629" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="E629" s="73" t="s">
+        <v>335</v>
+      </c>
+      <c r="F629" s="73" t="s">
+        <v>336</v>
+      </c>
+      <c r="G629" s="74">
+        <v>41.140180000000001</v>
+      </c>
+      <c r="H629" s="74">
+        <v>42.013689999999997</v>
       </c>
     </row>
     <row r="630" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A630" s="47">
-        <v>654</v>
-      </c>
-      <c r="B630" s="71">
-        <v>492</v>
-      </c>
-      <c r="C630" s="72">
-        <v>46275</v>
-      </c>
-      <c r="D630" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="E630" s="73" t="s">
-        <v>329</v>
-      </c>
-      <c r="F630" s="73" t="s">
-        <v>368</v>
-      </c>
-      <c r="G630" s="74">
-        <v>41.127890000000001</v>
-      </c>
-      <c r="H630" s="74">
-        <v>41.976900000000001</v>
+        <v>657</v>
+      </c>
+      <c r="B630" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="C630" s="29" t="s">
+        <v>395</v>
+      </c>
+      <c r="D630" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="E630" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="F630" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="G630" s="87">
+        <v>41.106499999999997</v>
+      </c>
+      <c r="H630" s="87">
+        <v>42.111778000000001</v>
       </c>
     </row>
     <row r="631" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A631" s="47">
-        <v>655</v>
-      </c>
-      <c r="B631" s="75">
-        <v>493</v>
-      </c>
-      <c r="C631" s="76">
-        <v>46275</v>
-      </c>
-      <c r="D631" s="75" t="s">
-        <v>366</v>
-      </c>
-      <c r="E631" s="77" t="s">
-        <v>367</v>
-      </c>
-      <c r="F631" s="77" t="s">
-        <v>369</v>
-      </c>
-      <c r="G631" s="78">
-        <v>41.127890000000001</v>
-      </c>
-      <c r="H631" s="78">
-        <v>41.976900000000001</v>
+        <v>658</v>
+      </c>
+      <c r="B631" s="38" t="s">
+        <v>396</v>
+      </c>
+      <c r="C631" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="D631" s="38" t="s">
+        <v>388</v>
+      </c>
+      <c r="E631" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F631" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="G631" s="88">
+        <v>41.09375</v>
+      </c>
+      <c r="H631" s="88">
+        <v>41.44585</v>
       </c>
     </row>
     <row r="632" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A632" s="47">
-        <v>656</v>
-      </c>
-      <c r="B632" s="71">
-        <v>494</v>
-      </c>
-      <c r="C632" s="72">
-        <v>46275</v>
-      </c>
-      <c r="D632" s="71" t="s">
-        <v>334</v>
-      </c>
-      <c r="E632" s="73" t="s">
-        <v>335</v>
-      </c>
-      <c r="F632" s="73" t="s">
-        <v>336</v>
-      </c>
-      <c r="G632" s="74">
-        <v>41.140180000000001</v>
-      </c>
-      <c r="H632" s="74">
-        <v>42.013689999999997</v>
-      </c>
-    </row>
-    <row r="633" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+      <c r="B632" s="29" t="s">
+        <v>398</v>
+      </c>
+      <c r="C632" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="D632" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E632" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="F632" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="G632" s="87">
+        <v>41.025759999999998</v>
+      </c>
+      <c r="H632" s="87">
+        <v>41.42315</v>
+      </c>
+    </row>
+    <row r="633" spans="1:10" ht="32" x14ac:dyDescent="0.35">
       <c r="A633" s="47">
-        <v>657</v>
-      </c>
-      <c r="B633" s="29" t="s">
-        <v>395</v>
-      </c>
-      <c r="C633" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="D633" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="E633" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="F633" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="G633" s="87">
-        <v>41.106499999999997</v>
-      </c>
-      <c r="H633" s="87">
-        <v>42.111778000000001</v>
+        <v>660</v>
+      </c>
+      <c r="B633" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="C633" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="D633" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="E633" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="F633" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="G633" s="88">
+        <v>40.98921</v>
+      </c>
+      <c r="H633" s="88">
+        <v>41.447049999999997</v>
+      </c>
+      <c r="J633" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="634" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A634" s="47">
-        <v>658</v>
-      </c>
-      <c r="B634" s="38" t="s">
+        <v>661</v>
+      </c>
+      <c r="B634" s="29" t="s">
+        <v>400</v>
+      </c>
+      <c r="C634" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="C634" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="D634" s="38" t="s">
-        <v>388</v>
-      </c>
-      <c r="E634" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="F634" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="G634" s="88">
-        <v>41.09375</v>
-      </c>
-      <c r="H634" s="88">
-        <v>41.44585</v>
+      <c r="D634" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E634" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="F634" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="G634" s="87">
+        <v>40.98921</v>
+      </c>
+      <c r="H634" s="87">
+        <v>41.447049999999997</v>
       </c>
     </row>
     <row r="635" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A635" s="47">
-        <v>659</v>
-      </c>
-      <c r="B635" s="29" t="s">
-        <v>399</v>
-      </c>
-      <c r="C635" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="D635" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="E635" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="F635" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="G635" s="87">
-        <v>41.025759999999998</v>
-      </c>
-      <c r="H635" s="87">
-        <v>41.42315</v>
+        <v>662</v>
+      </c>
+      <c r="B635" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C635" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="D635" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="E635" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="F635" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="G635" s="88">
+        <v>40.975119999999997</v>
+      </c>
+      <c r="H635" s="88">
+        <v>41.475189999999998</v>
       </c>
     </row>
     <row r="636" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A636" s="47">
-        <v>660</v>
-      </c>
-      <c r="B636" s="38" t="s">
-        <v>400</v>
-      </c>
-      <c r="C636" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="D636" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="E636" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="F636" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="G636" s="88">
-        <v>40.98921</v>
-      </c>
-      <c r="H636" s="88">
-        <v>41.447049999999997</v>
-      </c>
-      <c r="J636" t="s">
-        <v>406</v>
+        <v>663</v>
+      </c>
+      <c r="B636" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="C636" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="D636" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="E636" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="F636" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="G636" s="87">
+        <v>40.921259999999997</v>
+      </c>
+      <c r="H636" s="87">
+        <v>41.51314</v>
       </c>
     </row>
     <row r="637" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A637" s="47">
-        <v>661</v>
-      </c>
-      <c r="B637" s="29" t="s">
-        <v>401</v>
-      </c>
-      <c r="C637" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="D637" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E637" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="F637" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="G637" s="87">
-        <v>40.98921</v>
-      </c>
-      <c r="H637" s="87">
-        <v>41.447049999999997</v>
+        <v>664</v>
+      </c>
+      <c r="B637" s="13">
+        <v>502</v>
+      </c>
+      <c r="C637" s="94">
+        <v>46281</v>
+      </c>
+      <c r="D637" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E637" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F637" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G637" s="96">
+        <v>40.944442000000002</v>
+      </c>
+      <c r="H637" s="96">
+        <v>41.465207999999997</v>
       </c>
     </row>
     <row r="638" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A638" s="47">
-        <v>662</v>
-      </c>
-      <c r="B638" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="C638" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="D638" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="E638" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F638" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="G638" s="88">
-        <v>40.975119999999997</v>
-      </c>
-      <c r="H638" s="88">
-        <v>41.475189999999998</v>
+        <v>665</v>
+      </c>
+      <c r="B638" s="97">
+        <v>503</v>
+      </c>
+      <c r="C638" s="98">
+        <v>46281</v>
+      </c>
+      <c r="D638" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E638" s="99" t="s">
+        <v>408</v>
+      </c>
+      <c r="F638" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="G638" s="100">
+        <v>40.940688999999999</v>
+      </c>
+      <c r="H638" s="100">
+        <v>41.457130999999997</v>
+      </c>
+      <c r="J638" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="639" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A639" s="47">
-        <v>663</v>
-      </c>
-      <c r="B639" s="29" t="s">
-        <v>403</v>
-      </c>
-      <c r="C639" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="D639" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="E639" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="F639" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="G639" s="87">
-        <v>40.921259999999997</v>
-      </c>
-      <c r="H639" s="87">
-        <v>41.51314</v>
+        <v>666</v>
+      </c>
+      <c r="B639" s="13">
+        <v>504</v>
+      </c>
+      <c r="C639" s="94">
+        <v>46281</v>
+      </c>
+      <c r="D639" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E639" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F639" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G639" s="96">
+        <v>40.937133000000003</v>
+      </c>
+      <c r="H639" s="96">
+        <v>41.457833000000001</v>
       </c>
     </row>
     <row r="640" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A640" s="47">
-        <v>664</v>
-      </c>
-      <c r="B640" s="13">
-        <v>502</v>
-      </c>
-      <c r="C640" s="94">
+        <v>667</v>
+      </c>
+      <c r="B640" s="16">
+        <v>505</v>
+      </c>
+      <c r="C640" s="101">
         <v>46281</v>
       </c>
-      <c r="D640" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="E640" s="95" t="s">
-        <v>331</v>
-      </c>
-      <c r="F640" s="95" t="s">
-        <v>332</v>
-      </c>
-      <c r="G640" s="96">
-        <v>40.944442000000002</v>
-      </c>
-      <c r="H640" s="96">
-        <v>41.465207999999997</v>
+      <c r="D640" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E640" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F640" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G640" s="103">
+        <v>41.162950000000002</v>
+      </c>
+      <c r="H640" s="103">
+        <v>41.946640000000002</v>
       </c>
     </row>
     <row r="641" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A641" s="47">
-        <v>665</v>
-      </c>
-      <c r="B641" s="97">
-        <v>503</v>
-      </c>
-      <c r="C641" s="98">
+        <v>668</v>
+      </c>
+      <c r="B641" s="13">
+        <v>506</v>
+      </c>
+      <c r="C641" s="94">
         <v>46281</v>
       </c>
-      <c r="D641" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E641" s="99" t="s">
-        <v>409</v>
-      </c>
-      <c r="F641" s="99" t="s">
-        <v>406</v>
-      </c>
-      <c r="G641" s="100">
-        <v>40.940688999999999</v>
-      </c>
-      <c r="H641" s="100">
-        <v>41.457130999999997</v>
-      </c>
-      <c r="J641" t="s">
-        <v>406</v>
+      <c r="D641" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E641" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="F641" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="G641" s="96">
+        <v>41.162950000000002</v>
+      </c>
+      <c r="H641" s="96">
+        <v>41.946640000000002</v>
       </c>
     </row>
     <row r="642" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A642" s="47">
-        <v>666</v>
-      </c>
-      <c r="B642" s="13">
-        <v>504</v>
-      </c>
-      <c r="C642" s="94">
+        <v>669</v>
+      </c>
+      <c r="B642" s="97">
+        <v>507</v>
+      </c>
+      <c r="C642" s="98">
         <v>46281</v>
       </c>
-      <c r="D642" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E642" s="95" t="s">
-        <v>324</v>
-      </c>
-      <c r="F642" s="95" t="s">
-        <v>325</v>
-      </c>
-      <c r="G642" s="96">
-        <v>40.937133000000003</v>
-      </c>
-      <c r="H642" s="96">
-        <v>41.457833000000001</v>
+      <c r="D642" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="E642" s="99" t="s">
+        <v>335</v>
+      </c>
+      <c r="F642" s="99" t="s">
+        <v>336</v>
+      </c>
+      <c r="G642" s="100">
+        <v>41.164360000000002</v>
+      </c>
+      <c r="H642" s="100">
+        <v>41.943739999999998</v>
       </c>
     </row>
     <row r="643" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A643" s="47">
-        <v>667</v>
-      </c>
-      <c r="B643" s="16">
-        <v>505</v>
-      </c>
-      <c r="C643" s="101">
+        <v>670</v>
+      </c>
+      <c r="B643" s="13">
+        <v>508</v>
+      </c>
+      <c r="C643" s="94">
         <v>46281</v>
       </c>
-      <c r="D643" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E643" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="F643" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="G643" s="103">
-        <v>41.162950000000002</v>
-      </c>
-      <c r="H643" s="103">
-        <v>41.946640000000002</v>
+      <c r="D643" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E643" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F643" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G643" s="96">
+        <v>41.19706</v>
+      </c>
+      <c r="H643" s="96">
+        <v>41.87209</v>
+      </c>
+      <c r="J643" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="644" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A644" s="47">
-        <v>668</v>
-      </c>
-      <c r="B644" s="13">
-        <v>506</v>
-      </c>
-      <c r="C644" s="94">
-        <v>46281</v>
-      </c>
-      <c r="D644" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="E644" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="F644" s="95" t="s">
-        <v>328</v>
-      </c>
-      <c r="G644" s="96">
-        <v>41.162950000000002</v>
-      </c>
-      <c r="H644" s="96">
-        <v>41.946640000000002</v>
+        <v>671</v>
+      </c>
+      <c r="B644" s="16">
+        <v>509</v>
+      </c>
+      <c r="C644" s="101">
+        <v>46283</v>
+      </c>
+      <c r="D644" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E644" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="F644" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="G644" s="103">
+        <v>41.517969999999998</v>
+      </c>
+      <c r="H644" s="103">
+        <v>41.553170000000001</v>
       </c>
     </row>
     <row r="645" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A645" s="47">
-        <v>669</v>
-      </c>
-      <c r="B645" s="97">
-        <v>507</v>
-      </c>
-      <c r="C645" s="98">
-        <v>46281</v>
-      </c>
-      <c r="D645" s="97" t="s">
-        <v>334</v>
-      </c>
-      <c r="E645" s="99" t="s">
-        <v>335</v>
-      </c>
-      <c r="F645" s="99" t="s">
-        <v>336</v>
-      </c>
-      <c r="G645" s="100">
-        <v>41.164360000000002</v>
-      </c>
-      <c r="H645" s="100">
-        <v>41.943739999999998</v>
+        <v>672</v>
+      </c>
+      <c r="B645" s="13">
+        <v>510</v>
+      </c>
+      <c r="C645" s="94">
+        <v>46283</v>
+      </c>
+      <c r="D645" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E645" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F645" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G645" s="96">
+        <v>41.517969999999998</v>
+      </c>
+      <c r="H645" s="96">
+        <v>41.553170000000001</v>
       </c>
     </row>
     <row r="646" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A646" s="47">
-        <v>670</v>
-      </c>
-      <c r="B646" s="13">
-        <v>508</v>
-      </c>
-      <c r="C646" s="94">
-        <v>46281</v>
-      </c>
-      <c r="D646" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="B646" s="16">
+        <v>511</v>
+      </c>
+      <c r="C646" s="101">
+        <v>46283</v>
+      </c>
+      <c r="D646" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="E646" s="95" t="s">
-        <v>407</v>
-      </c>
-      <c r="F646" s="95" t="s">
+      <c r="E646" s="102" t="s">
         <v>408</v>
       </c>
-      <c r="G646" s="96">
-        <v>41.19706</v>
-      </c>
-      <c r="H646" s="96">
-        <v>41.87209</v>
+      <c r="F646" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G646" s="103">
+        <v>41.517969999999998</v>
+      </c>
+      <c r="H646" s="103">
+        <v>41.553170000000001</v>
       </c>
       <c r="J646" t="s">
         <v>405</v>
@@ -20699,2840 +20690,2759 @@
     </row>
     <row r="647" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A647" s="47">
-        <v>671</v>
-      </c>
-      <c r="B647" s="16">
-        <v>509</v>
-      </c>
-      <c r="C647" s="101">
+        <v>674</v>
+      </c>
+      <c r="B647" s="13">
+        <v>512</v>
+      </c>
+      <c r="C647" s="94">
         <v>46283</v>
       </c>
-      <c r="D647" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E647" s="102" t="s">
-        <v>367</v>
-      </c>
-      <c r="F647" s="102" t="s">
-        <v>369</v>
-      </c>
-      <c r="G647" s="103">
-        <v>41.517969999999998</v>
-      </c>
-      <c r="H647" s="103">
-        <v>41.553170000000001</v>
+      <c r="D647" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E647" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F647" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G647" s="96">
+        <v>41.514947999999997</v>
+      </c>
+      <c r="H647" s="96">
+        <v>41.547136999999999</v>
+      </c>
+      <c r="J647" t="s">
+        <v>404</v>
+      </c>
+      <c r="M647" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="648" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A648" s="47">
-        <v>672</v>
-      </c>
-      <c r="B648" s="13">
-        <v>510</v>
-      </c>
-      <c r="C648" s="94">
+        <v>675</v>
+      </c>
+      <c r="B648" s="16">
+        <v>513</v>
+      </c>
+      <c r="C648" s="101">
         <v>46283</v>
       </c>
-      <c r="D648" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E648" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="F648" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="G648" s="96">
-        <v>41.517969999999998</v>
-      </c>
-      <c r="H648" s="96">
-        <v>41.553170000000001</v>
+      <c r="D648" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E648" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F648" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G648" s="103">
+        <v>41.470950000000002</v>
+      </c>
+      <c r="H648" s="103">
+        <v>41.559060000000002</v>
       </c>
     </row>
     <row r="649" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A649" s="47">
-        <v>673</v>
-      </c>
-      <c r="B649" s="16">
-        <v>511</v>
-      </c>
-      <c r="C649" s="101">
+        <v>676</v>
+      </c>
+      <c r="B649" s="13">
+        <v>514</v>
+      </c>
+      <c r="C649" s="94">
         <v>46283</v>
       </c>
-      <c r="D649" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E649" s="102" t="s">
-        <v>409</v>
-      </c>
-      <c r="F649" s="102" t="s">
-        <v>406</v>
-      </c>
-      <c r="G649" s="103">
-        <v>41.517969999999998</v>
-      </c>
-      <c r="H649" s="103">
-        <v>41.553170000000001</v>
-      </c>
-      <c r="J649" t="s">
-        <v>406</v>
+      <c r="D649" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E649" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F649" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G649" s="96">
+        <v>41.427410000000002</v>
+      </c>
+      <c r="H649" s="96">
+        <v>41.452559999999998</v>
       </c>
     </row>
     <row r="650" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A650" s="47">
-        <v>674</v>
-      </c>
-      <c r="B650" s="13">
-        <v>512</v>
-      </c>
-      <c r="C650" s="94">
+        <v>677</v>
+      </c>
+      <c r="B650" s="16">
+        <v>515</v>
+      </c>
+      <c r="C650" s="101">
         <v>46283</v>
       </c>
-      <c r="D650" s="13" t="s">
+      <c r="D650" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="E650" s="95" t="s">
+      <c r="E650" s="102" t="s">
+        <v>406</v>
+      </c>
+      <c r="F650" s="102" t="s">
         <v>407</v>
       </c>
-      <c r="F650" s="95" t="s">
-        <v>408</v>
-      </c>
-      <c r="G650" s="96">
-        <v>41.514947999999997</v>
-      </c>
-      <c r="H650" s="96">
-        <v>41.547136999999999</v>
+      <c r="G650" s="103">
+        <v>41.426200000000001</v>
+      </c>
+      <c r="H650" s="103">
+        <v>41.450650000000003</v>
       </c>
       <c r="J650" t="s">
-        <v>405</v>
-      </c>
-      <c r="M650" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
     </row>
     <row r="651" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A651" s="47">
-        <v>675</v>
-      </c>
-      <c r="B651" s="16">
-        <v>513</v>
-      </c>
-      <c r="C651" s="101">
+        <v>678</v>
+      </c>
+      <c r="B651" s="13">
+        <v>516</v>
+      </c>
+      <c r="C651" s="94">
         <v>46283</v>
       </c>
-      <c r="D651" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E651" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F651" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G651" s="103">
-        <v>41.470950000000002</v>
-      </c>
-      <c r="H651" s="103">
-        <v>41.559060000000002</v>
+      <c r="D651" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E651" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="F651" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="G651" s="96">
+        <v>41.426200000000001</v>
+      </c>
+      <c r="H651" s="96">
+        <v>41.450650000000003</v>
       </c>
     </row>
     <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A652" s="47">
-        <v>676</v>
-      </c>
-      <c r="B652" s="13">
-        <v>514</v>
-      </c>
-      <c r="C652" s="94">
+        <v>679</v>
+      </c>
+      <c r="B652" s="16">
+        <v>517</v>
+      </c>
+      <c r="C652" s="101">
         <v>46283</v>
       </c>
-      <c r="D652" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E652" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="F652" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="G652" s="96">
-        <v>41.427410000000002</v>
-      </c>
-      <c r="H652" s="96">
-        <v>41.452559999999998</v>
+      <c r="D652" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E652" s="102" t="s">
+        <v>408</v>
+      </c>
+      <c r="F652" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G652" s="103">
+        <v>41.418019999999999</v>
+      </c>
+      <c r="H652" s="103">
+        <v>41.444569999999999</v>
+      </c>
+      <c r="J652" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="653" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A653" s="47">
-        <v>677</v>
-      </c>
-      <c r="B653" s="16">
-        <v>515</v>
-      </c>
-      <c r="C653" s="101">
+        <v>680</v>
+      </c>
+      <c r="B653" s="13">
+        <v>518</v>
+      </c>
+      <c r="C653" s="94">
         <v>46283</v>
       </c>
-      <c r="D653" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E653" s="102" t="s">
-        <v>407</v>
-      </c>
-      <c r="F653" s="102" t="s">
-        <v>408</v>
-      </c>
-      <c r="G653" s="103">
-        <v>41.426200000000001</v>
-      </c>
-      <c r="H653" s="103">
-        <v>41.450650000000003</v>
-      </c>
-      <c r="J653" t="s">
-        <v>405</v>
+      <c r="D653" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E653" s="95" t="s">
+        <v>335</v>
+      </c>
+      <c r="F653" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="G653" s="96">
+        <v>41.407879999999999</v>
+      </c>
+      <c r="H653" s="96">
+        <v>41.439819999999997</v>
       </c>
     </row>
     <row r="654" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A654" s="47">
-        <v>678</v>
-      </c>
-      <c r="B654" s="13">
-        <v>516</v>
-      </c>
-      <c r="C654" s="94">
+        <v>681</v>
+      </c>
+      <c r="B654" s="16">
+        <v>519</v>
+      </c>
+      <c r="C654" s="101">
         <v>46283</v>
       </c>
-      <c r="D654" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E654" s="95" t="s">
-        <v>367</v>
-      </c>
-      <c r="F654" s="95" t="s">
-        <v>369</v>
-      </c>
-      <c r="G654" s="96">
-        <v>41.426200000000001</v>
-      </c>
-      <c r="H654" s="96">
-        <v>41.450650000000003</v>
+      <c r="D654" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E654" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F654" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G654" s="103">
+        <v>41.414790000000004</v>
+      </c>
+      <c r="H654" s="103">
+        <v>41.491160000000001</v>
       </c>
     </row>
     <row r="655" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A655" s="47">
-        <v>679</v>
-      </c>
-      <c r="B655" s="16">
-        <v>517</v>
-      </c>
-      <c r="C655" s="101">
+        <v>682</v>
+      </c>
+      <c r="B655" s="13">
+        <v>520</v>
+      </c>
+      <c r="C655" s="94">
         <v>46283</v>
       </c>
-      <c r="D655" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E655" s="102" t="s">
-        <v>409</v>
-      </c>
-      <c r="F655" s="102" t="s">
-        <v>406</v>
-      </c>
-      <c r="G655" s="103">
-        <v>41.418019999999999</v>
-      </c>
-      <c r="H655" s="103">
-        <v>41.444569999999999</v>
-      </c>
-      <c r="J655" t="s">
-        <v>406</v>
+      <c r="D655" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E655" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F655" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G655" s="96">
+        <v>41.414790000000004</v>
+      </c>
+      <c r="H655" s="96">
+        <v>41.491160000000001</v>
       </c>
     </row>
     <row r="656" spans="1:13" ht="16" x14ac:dyDescent="0.35">
       <c r="A656" s="47">
-        <v>680</v>
-      </c>
-      <c r="B656" s="13">
-        <v>518</v>
-      </c>
-      <c r="C656" s="94">
+        <v>683</v>
+      </c>
+      <c r="B656" s="16">
+        <v>521</v>
+      </c>
+      <c r="C656" s="101">
         <v>46283</v>
       </c>
-      <c r="D656" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="E656" s="95" t="s">
-        <v>335</v>
-      </c>
-      <c r="F656" s="95" t="s">
-        <v>336</v>
-      </c>
-      <c r="G656" s="96">
-        <v>41.407879999999999</v>
-      </c>
-      <c r="H656" s="96">
-        <v>41.439819999999997</v>
+      <c r="D656" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E656" s="102" t="s">
+        <v>331</v>
+      </c>
+      <c r="F656" s="102" t="s">
+        <v>332</v>
+      </c>
+      <c r="G656" s="103">
+        <v>41.413739999999997</v>
+      </c>
+      <c r="H656" s="103">
+        <v>41.49203</v>
       </c>
     </row>
     <row r="657" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A657" s="47">
-        <v>681</v>
-      </c>
-      <c r="B657" s="16">
-        <v>519</v>
-      </c>
-      <c r="C657" s="101">
+        <v>684</v>
+      </c>
+      <c r="B657" s="13">
+        <v>522</v>
+      </c>
+      <c r="C657" s="94">
         <v>46283</v>
       </c>
-      <c r="D657" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E657" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F657" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G657" s="103">
-        <v>41.414790000000004</v>
-      </c>
-      <c r="H657" s="103">
-        <v>41.491160000000001</v>
+      <c r="D657" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E657" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F657" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G657" s="96">
+        <v>41.415010000000002</v>
+      </c>
+      <c r="H657" s="96">
+        <v>41.489609999999999</v>
+      </c>
+      <c r="J657" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="658" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A658" s="47">
-        <v>682</v>
-      </c>
-      <c r="B658" s="13">
-        <v>520</v>
-      </c>
-      <c r="C658" s="94">
+        <v>685</v>
+      </c>
+      <c r="B658" s="116">
+        <v>523</v>
+      </c>
+      <c r="C658" s="117">
         <v>46283</v>
       </c>
-      <c r="D658" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E658" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="F658" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="G658" s="96">
-        <v>41.414790000000004</v>
-      </c>
-      <c r="H658" s="96">
-        <v>41.491160000000001</v>
+      <c r="D658" s="116" t="s">
+        <v>366</v>
+      </c>
+      <c r="E658" s="118" t="s">
+        <v>367</v>
+      </c>
+      <c r="F658" s="118" t="s">
+        <v>369</v>
+      </c>
+      <c r="G658" s="103">
+        <v>41.409849999999999</v>
+      </c>
+      <c r="H658" s="103">
+        <v>41.487349999999999</v>
       </c>
     </row>
     <row r="659" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A659" s="47">
-        <v>683</v>
-      </c>
-      <c r="B659" s="16">
-        <v>521</v>
-      </c>
-      <c r="C659" s="101">
-        <v>46283</v>
-      </c>
-      <c r="D659" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="B659" s="13">
+        <v>524</v>
+      </c>
+      <c r="C659" s="94">
+        <v>46290</v>
+      </c>
+      <c r="D659" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="E659" s="102" t="s">
+      <c r="E659" s="95" t="s">
         <v>331</v>
       </c>
-      <c r="F659" s="102" t="s">
+      <c r="F659" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="G659" s="103">
-        <v>41.413739999999997</v>
-      </c>
-      <c r="H659" s="103">
-        <v>41.49203</v>
+      <c r="G659" s="96">
+        <v>41.393459999999997</v>
+      </c>
+      <c r="H659" s="96">
+        <v>41.696550000000002</v>
       </c>
     </row>
     <row r="660" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A660" s="47">
-        <v>684</v>
-      </c>
-      <c r="B660" s="13">
-        <v>522</v>
-      </c>
-      <c r="C660" s="94">
-        <v>46283</v>
-      </c>
-      <c r="D660" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E660" s="95" t="s">
-        <v>407</v>
-      </c>
-      <c r="F660" s="95" t="s">
-        <v>408</v>
-      </c>
-      <c r="G660" s="96">
-        <v>41.415010000000002</v>
-      </c>
-      <c r="H660" s="96">
-        <v>41.489609999999999</v>
-      </c>
-      <c r="J660" t="s">
-        <v>405</v>
+        <v>687</v>
+      </c>
+      <c r="B660" s="16">
+        <v>525</v>
+      </c>
+      <c r="C660" s="101">
+        <v>46290</v>
+      </c>
+      <c r="D660" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E660" s="102" t="s">
+        <v>389</v>
+      </c>
+      <c r="F660" s="102" t="s">
+        <v>390</v>
+      </c>
+      <c r="G660" s="103">
+        <v>41.41478</v>
+      </c>
+      <c r="H660" s="103">
+        <v>41.845590000000001</v>
       </c>
     </row>
     <row r="661" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A661" s="47">
-        <v>685</v>
-      </c>
-      <c r="B661" s="116">
-        <v>523</v>
-      </c>
-      <c r="C661" s="117">
-        <v>46283</v>
-      </c>
-      <c r="D661" s="116" t="s">
-        <v>366</v>
-      </c>
-      <c r="E661" s="118" t="s">
-        <v>367</v>
-      </c>
-      <c r="F661" s="118" t="s">
-        <v>369</v>
-      </c>
-      <c r="G661" s="103">
-        <v>41.409849999999999</v>
-      </c>
-      <c r="H661" s="103">
-        <v>41.487349999999999</v>
+        <v>688</v>
+      </c>
+      <c r="B661" s="13">
+        <v>526</v>
+      </c>
+      <c r="C661" s="94">
+        <v>46290</v>
+      </c>
+      <c r="D661" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E661" s="95" t="s">
+        <v>376</v>
+      </c>
+      <c r="F661" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="G661" s="96">
+        <v>41.41621</v>
+      </c>
+      <c r="H661" s="96">
+        <v>41.853029999999997</v>
       </c>
     </row>
     <row r="662" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A662" s="47">
-        <v>686</v>
-      </c>
-      <c r="B662" s="13">
-        <v>524</v>
-      </c>
-      <c r="C662" s="94">
+        <v>689</v>
+      </c>
+      <c r="B662" s="16">
+        <v>527</v>
+      </c>
+      <c r="C662" s="101">
         <v>46290</v>
       </c>
-      <c r="D662" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="E662" s="95" t="s">
-        <v>331</v>
-      </c>
-      <c r="F662" s="95" t="s">
-        <v>332</v>
-      </c>
-      <c r="G662" s="96">
-        <v>41.393459999999997</v>
-      </c>
-      <c r="H662" s="96">
-        <v>41.696550000000002</v>
+      <c r="D662" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E662" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F662" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G662" s="103">
+        <v>41.408540000000002</v>
+      </c>
+      <c r="H662" s="103">
+        <v>41.80997</v>
       </c>
     </row>
     <row r="663" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A663" s="47">
-        <v>687</v>
-      </c>
-      <c r="B663" s="16">
-        <v>525</v>
-      </c>
-      <c r="C663" s="101">
+        <v>690</v>
+      </c>
+      <c r="B663" s="13">
+        <v>528</v>
+      </c>
+      <c r="C663" s="94">
         <v>46290</v>
       </c>
-      <c r="D663" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E663" s="102" t="s">
-        <v>389</v>
-      </c>
-      <c r="F663" s="102" t="s">
-        <v>390</v>
-      </c>
-      <c r="G663" s="103">
-        <v>41.41478</v>
-      </c>
-      <c r="H663" s="103">
-        <v>41.845590000000001</v>
+      <c r="D663" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E663" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F663" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G663" s="96">
+        <v>41.408540000000002</v>
+      </c>
+      <c r="H663" s="96">
+        <v>41.80997</v>
       </c>
     </row>
     <row r="664" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A664" s="47">
-        <v>688</v>
-      </c>
-      <c r="B664" s="13">
-        <v>526</v>
-      </c>
-      <c r="C664" s="94">
+        <v>691</v>
+      </c>
+      <c r="B664" s="113">
+        <v>529</v>
+      </c>
+      <c r="C664" s="114">
         <v>46290</v>
       </c>
-      <c r="D664" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="E664" s="95" t="s">
-        <v>376</v>
-      </c>
-      <c r="F664" s="95" t="s">
-        <v>370</v>
-      </c>
-      <c r="G664" s="96">
-        <v>41.41621</v>
-      </c>
-      <c r="H664" s="96">
-        <v>41.853029999999997</v>
+      <c r="D664" s="113" t="s">
+        <v>366</v>
+      </c>
+      <c r="E664" s="115" t="s">
+        <v>367</v>
+      </c>
+      <c r="F664" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="G664" s="103">
+        <v>41.404290000000003</v>
+      </c>
+      <c r="H664" s="103">
+        <v>41.781759999999998</v>
       </c>
     </row>
     <row r="665" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A665" s="47">
-        <v>689</v>
-      </c>
-      <c r="B665" s="16">
-        <v>527</v>
-      </c>
-      <c r="C665" s="101">
+        <v>692</v>
+      </c>
+      <c r="B665" s="13">
+        <v>530</v>
+      </c>
+      <c r="C665" s="94">
         <v>46290</v>
       </c>
-      <c r="D665" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E665" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F665" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G665" s="103">
-        <v>41.408540000000002</v>
-      </c>
-      <c r="H665" s="103">
-        <v>41.80997</v>
+      <c r="D665" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E665" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F665" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="G665" s="96">
+        <v>41.404269999999997</v>
+      </c>
+      <c r="H665" s="96">
+        <v>41.781759999999998</v>
       </c>
     </row>
     <row r="666" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A666" s="47">
-        <v>690</v>
-      </c>
-      <c r="B666" s="13">
-        <v>528</v>
-      </c>
-      <c r="C666" s="94">
+        <v>693</v>
+      </c>
+      <c r="B666" s="16">
+        <v>531</v>
+      </c>
+      <c r="C666" s="101">
         <v>46290</v>
       </c>
-      <c r="D666" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E666" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="F666" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="G666" s="96">
-        <v>41.408540000000002</v>
-      </c>
-      <c r="H666" s="96">
-        <v>41.80997</v>
+      <c r="D666" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E666" s="102" t="s">
+        <v>408</v>
+      </c>
+      <c r="F666" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G666" s="103">
+        <v>41.396590000000003</v>
+      </c>
+      <c r="H666" s="103">
+        <v>41.75976</v>
+      </c>
+      <c r="J666" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="667" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A667" s="47">
-        <v>691</v>
-      </c>
-      <c r="B667" s="113">
-        <v>529</v>
-      </c>
-      <c r="C667" s="114">
+        <v>694</v>
+      </c>
+      <c r="B667" s="13">
+        <v>532</v>
+      </c>
+      <c r="C667" s="94">
         <v>46290</v>
       </c>
-      <c r="D667" s="113" t="s">
-        <v>366</v>
-      </c>
-      <c r="E667" s="115" t="s">
-        <v>367</v>
-      </c>
-      <c r="F667" s="115" t="s">
-        <v>369</v>
-      </c>
-      <c r="G667" s="103">
-        <v>41.404290000000003</v>
-      </c>
-      <c r="H667" s="103">
-        <v>41.781759999999998</v>
+      <c r="D667" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E667" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F667" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G667" s="96">
+        <v>41.395850000000003</v>
+      </c>
+      <c r="H667" s="96">
+        <v>41.748049999999999</v>
+      </c>
+      <c r="J667" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="668" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A668" s="47">
-        <v>692</v>
-      </c>
-      <c r="B668" s="13">
-        <v>530</v>
-      </c>
-      <c r="C668" s="94">
+        <v>695</v>
+      </c>
+      <c r="B668" s="113">
+        <v>533</v>
+      </c>
+      <c r="C668" s="114">
         <v>46290</v>
       </c>
-      <c r="D668" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E668" s="95" t="s">
-        <v>116</v>
-      </c>
-      <c r="F668" s="95" t="s">
-        <v>333</v>
-      </c>
-      <c r="G668" s="96">
-        <v>41.404269999999997</v>
-      </c>
-      <c r="H668" s="96">
-        <v>41.781759999999998</v>
+      <c r="D668" s="113" t="s">
+        <v>366</v>
+      </c>
+      <c r="E668" s="115" t="s">
+        <v>367</v>
+      </c>
+      <c r="F668" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="G668" s="103">
+        <v>41.467080000000003</v>
+      </c>
+      <c r="H668" s="103">
+        <v>41.710709999999999</v>
       </c>
     </row>
     <row r="669" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A669" s="47">
-        <v>693</v>
-      </c>
-      <c r="B669" s="16">
-        <v>531</v>
-      </c>
-      <c r="C669" s="101">
+        <v>696</v>
+      </c>
+      <c r="B669" s="13">
+        <v>534</v>
+      </c>
+      <c r="C669" s="94">
         <v>46290</v>
       </c>
-      <c r="D669" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E669" s="102" t="s">
-        <v>409</v>
-      </c>
-      <c r="F669" s="102" t="s">
-        <v>406</v>
-      </c>
-      <c r="G669" s="103">
-        <v>41.396590000000003</v>
-      </c>
-      <c r="H669" s="103">
-        <v>41.75976</v>
-      </c>
-      <c r="J669" t="s">
-        <v>406</v>
+      <c r="D669" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E669" s="95" t="s">
+        <v>376</v>
+      </c>
+      <c r="F669" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="G669" s="96">
+        <v>41.458889999999997</v>
+      </c>
+      <c r="H669" s="96">
+        <v>41.715710000000001</v>
       </c>
     </row>
     <row r="670" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A670" s="47">
-        <v>694</v>
-      </c>
-      <c r="B670" s="13">
-        <v>532</v>
-      </c>
-      <c r="C670" s="94">
+        <v>697</v>
+      </c>
+      <c r="B670" s="16">
+        <v>535</v>
+      </c>
+      <c r="C670" s="101">
         <v>46290</v>
       </c>
-      <c r="D670" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E670" s="95" t="s">
-        <v>407</v>
-      </c>
-      <c r="F670" s="95" t="s">
-        <v>408</v>
-      </c>
-      <c r="G670" s="96">
-        <v>41.395850000000003</v>
-      </c>
-      <c r="H670" s="96">
-        <v>41.748049999999999</v>
-      </c>
-      <c r="J670" t="s">
-        <v>405</v>
+      <c r="D670" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E670" s="102" t="s">
+        <v>317</v>
+      </c>
+      <c r="F670" s="102" t="s">
+        <v>318</v>
+      </c>
+      <c r="G670" s="103">
+        <v>41.458889999999997</v>
+      </c>
+      <c r="H670" s="103">
+        <v>41.715710000000001</v>
       </c>
     </row>
     <row r="671" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A671" s="47">
-        <v>695</v>
-      </c>
-      <c r="B671" s="113">
-        <v>533</v>
-      </c>
-      <c r="C671" s="114">
+        <v>698</v>
+      </c>
+      <c r="B671" s="13">
+        <v>536</v>
+      </c>
+      <c r="C671" s="94">
         <v>46290</v>
       </c>
-      <c r="D671" s="113" t="s">
-        <v>366</v>
-      </c>
-      <c r="E671" s="115" t="s">
-        <v>367</v>
-      </c>
-      <c r="F671" s="115" t="s">
-        <v>369</v>
-      </c>
-      <c r="G671" s="103">
-        <v>41.467080000000003</v>
-      </c>
-      <c r="H671" s="103">
-        <v>41.710709999999999</v>
+      <c r="D671" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E671" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="F671" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="G671" s="96">
+        <v>41.458889999999997</v>
+      </c>
+      <c r="H671" s="96">
+        <v>41.715710000000001</v>
       </c>
     </row>
     <row r="672" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A672" s="47">
-        <v>696</v>
-      </c>
-      <c r="B672" s="13">
-        <v>534</v>
-      </c>
-      <c r="C672" s="94">
+        <v>699</v>
+      </c>
+      <c r="B672" s="16">
+        <v>537</v>
+      </c>
+      <c r="C672" s="101">
         <v>46290</v>
       </c>
-      <c r="D672" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="E672" s="95" t="s">
-        <v>376</v>
-      </c>
-      <c r="F672" s="95" t="s">
-        <v>370</v>
-      </c>
-      <c r="G672" s="96">
+      <c r="D672" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E672" s="102" t="s">
+        <v>329</v>
+      </c>
+      <c r="F672" s="102" t="s">
+        <v>368</v>
+      </c>
+      <c r="G672" s="103">
         <v>41.458889999999997</v>
       </c>
-      <c r="H672" s="96">
+      <c r="H672" s="103">
         <v>41.715710000000001</v>
       </c>
     </row>
     <row r="673" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A673" s="47">
-        <v>697</v>
-      </c>
-      <c r="B673" s="16">
-        <v>535</v>
-      </c>
-      <c r="C673" s="101">
+        <v>700</v>
+      </c>
+      <c r="B673" s="13">
+        <v>538</v>
+      </c>
+      <c r="C673" s="94">
         <v>46290</v>
       </c>
-      <c r="D673" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="E673" s="102" t="s">
-        <v>317</v>
-      </c>
-      <c r="F673" s="102" t="s">
-        <v>318</v>
-      </c>
-      <c r="G673" s="103">
-        <v>41.458889999999997</v>
-      </c>
-      <c r="H673" s="103">
-        <v>41.715710000000001</v>
+      <c r="D673" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E673" s="95" t="s">
+        <v>408</v>
+      </c>
+      <c r="F673" s="95" t="s">
+        <v>405</v>
+      </c>
+      <c r="G673" s="96">
+        <v>41.456409999999998</v>
+      </c>
+      <c r="H673" s="96">
+        <v>41.720269999999999</v>
+      </c>
+      <c r="J673" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="674" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A674" s="47">
-        <v>698</v>
-      </c>
-      <c r="B674" s="13">
-        <v>536</v>
-      </c>
-      <c r="C674" s="94">
+        <v>701</v>
+      </c>
+      <c r="B674" s="16">
+        <v>539</v>
+      </c>
+      <c r="C674" s="101">
         <v>46290</v>
       </c>
-      <c r="D674" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="E674" s="95" t="s">
-        <v>386</v>
-      </c>
-      <c r="F674" s="95" t="s">
-        <v>320</v>
-      </c>
-      <c r="G674" s="96">
-        <v>41.458889999999997</v>
-      </c>
-      <c r="H674" s="96">
-        <v>41.715710000000001</v>
+      <c r="D674" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E674" s="102" t="s">
+        <v>331</v>
+      </c>
+      <c r="F674" s="102" t="s">
+        <v>332</v>
+      </c>
+      <c r="G674" s="103">
+        <v>41.447479999999999</v>
+      </c>
+      <c r="H674" s="103">
+        <v>41.703539999999997</v>
       </c>
     </row>
     <row r="675" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A675" s="47">
-        <v>699</v>
-      </c>
-      <c r="B675" s="16">
-        <v>537</v>
-      </c>
-      <c r="C675" s="101">
+        <v>702</v>
+      </c>
+      <c r="B675" s="13">
+        <v>540</v>
+      </c>
+      <c r="C675" s="94">
         <v>46290</v>
       </c>
-      <c r="D675" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E675" s="102" t="s">
-        <v>329</v>
-      </c>
-      <c r="F675" s="102" t="s">
-        <v>368</v>
-      </c>
-      <c r="G675" s="103">
-        <v>41.458889999999997</v>
-      </c>
-      <c r="H675" s="103">
-        <v>41.715710000000001</v>
+      <c r="D675" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E675" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F675" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G675" s="96">
+        <v>41.446260000000002</v>
+      </c>
+      <c r="H675" s="96">
+        <v>41.702629999999999</v>
+      </c>
+      <c r="J675" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="676" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A676" s="47">
-        <v>700</v>
-      </c>
-      <c r="B676" s="13">
-        <v>538</v>
-      </c>
-      <c r="C676" s="94">
+        <v>703</v>
+      </c>
+      <c r="B676" s="16">
+        <v>541</v>
+      </c>
+      <c r="C676" s="101">
         <v>46290</v>
       </c>
-      <c r="D676" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E676" s="95" t="s">
-        <v>409</v>
-      </c>
-      <c r="F676" s="95" t="s">
-        <v>406</v>
-      </c>
-      <c r="G676" s="96">
-        <v>41.456409999999998</v>
-      </c>
-      <c r="H676" s="96">
-        <v>41.720269999999999</v>
-      </c>
-      <c r="J676" t="s">
-        <v>406</v>
+      <c r="D676" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E676" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F676" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G676" s="103">
+        <v>41.420459999999999</v>
+      </c>
+      <c r="H676" s="103">
+        <v>41.703130000000002</v>
       </c>
     </row>
     <row r="677" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A677" s="47">
-        <v>701</v>
-      </c>
-      <c r="B677" s="16">
-        <v>539</v>
-      </c>
-      <c r="C677" s="101">
+        <v>704</v>
+      </c>
+      <c r="B677" s="13">
+        <v>542</v>
+      </c>
+      <c r="C677" s="94">
         <v>46290</v>
       </c>
-      <c r="D677" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E677" s="102" t="s">
-        <v>331</v>
-      </c>
-      <c r="F677" s="102" t="s">
-        <v>332</v>
-      </c>
-      <c r="G677" s="103">
-        <v>41.447479999999999</v>
-      </c>
-      <c r="H677" s="103">
-        <v>41.703539999999997</v>
+      <c r="D677" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E677" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F677" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="G677" s="96">
+        <v>41.420459999999999</v>
+      </c>
+      <c r="H677" s="96">
+        <v>41.703130000000002</v>
       </c>
     </row>
     <row r="678" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A678" s="47">
-        <v>702</v>
-      </c>
-      <c r="B678" s="13">
-        <v>540</v>
-      </c>
-      <c r="C678" s="94">
+        <v>705</v>
+      </c>
+      <c r="B678" s="113">
+        <v>543</v>
+      </c>
+      <c r="C678" s="114">
         <v>46290</v>
       </c>
-      <c r="D678" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E678" s="95" t="s">
-        <v>407</v>
-      </c>
-      <c r="F678" s="95" t="s">
-        <v>408</v>
-      </c>
-      <c r="G678" s="96">
-        <v>41.446260000000002</v>
-      </c>
-      <c r="H678" s="96">
-        <v>41.702629999999999</v>
-      </c>
-      <c r="J678" t="s">
-        <v>405</v>
+      <c r="D678" s="113" t="s">
+        <v>366</v>
+      </c>
+      <c r="E678" s="115" t="s">
+        <v>367</v>
+      </c>
+      <c r="F678" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="G678" s="103">
+        <v>41.352829999999997</v>
+      </c>
+      <c r="H678" s="103">
+        <v>41.735729999999997</v>
       </c>
     </row>
     <row r="679" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A679" s="47">
-        <v>703</v>
-      </c>
-      <c r="B679" s="16">
-        <v>541</v>
-      </c>
-      <c r="C679" s="101">
+        <v>706</v>
+      </c>
+      <c r="B679" s="97">
+        <v>544</v>
+      </c>
+      <c r="C679" s="98">
         <v>46290</v>
       </c>
-      <c r="D679" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E679" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F679" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G679" s="103">
-        <v>41.420459999999999</v>
-      </c>
-      <c r="H679" s="103">
-        <v>41.703130000000002</v>
+      <c r="D679" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E679" s="99" t="s">
+        <v>406</v>
+      </c>
+      <c r="F679" s="99" t="s">
+        <v>407</v>
+      </c>
+      <c r="G679" s="100">
+        <v>41.35284</v>
+      </c>
+      <c r="H679" s="100">
+        <v>41.73574</v>
+      </c>
+      <c r="J679" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="680" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A680" s="47">
-        <v>704</v>
-      </c>
-      <c r="B680" s="13">
-        <v>542</v>
-      </c>
-      <c r="C680" s="94">
+        <v>707</v>
+      </c>
+      <c r="B680" s="16">
+        <v>545</v>
+      </c>
+      <c r="C680" s="101">
         <v>46290</v>
       </c>
-      <c r="D680" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E680" s="95" t="s">
-        <v>116</v>
-      </c>
-      <c r="F680" s="95" t="s">
-        <v>333</v>
-      </c>
-      <c r="G680" s="96">
-        <v>41.420459999999999</v>
-      </c>
-      <c r="H680" s="96">
-        <v>41.703130000000002</v>
+      <c r="D680" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E680" s="102" t="s">
+        <v>329</v>
+      </c>
+      <c r="F680" s="102" t="s">
+        <v>368</v>
+      </c>
+      <c r="G680" s="103">
+        <v>41.35284</v>
+      </c>
+      <c r="H680" s="103">
+        <v>41.73574</v>
       </c>
     </row>
     <row r="681" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A681" s="47">
-        <v>705</v>
-      </c>
-      <c r="B681" s="113">
-        <v>543</v>
-      </c>
-      <c r="C681" s="114">
+        <v>708</v>
+      </c>
+      <c r="B681" s="97">
+        <v>546</v>
+      </c>
+      <c r="C681" s="98">
         <v>46290</v>
       </c>
-      <c r="D681" s="113" t="s">
-        <v>366</v>
-      </c>
-      <c r="E681" s="115" t="s">
-        <v>367</v>
-      </c>
-      <c r="F681" s="115" t="s">
-        <v>369</v>
-      </c>
-      <c r="G681" s="103">
-        <v>41.352829999999997</v>
-      </c>
-      <c r="H681" s="103">
-        <v>41.735729999999997</v>
+      <c r="D681" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E681" s="99" t="s">
+        <v>408</v>
+      </c>
+      <c r="F681" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="G681" s="100">
+        <v>41.375500000000002</v>
+      </c>
+      <c r="H681" s="100">
+        <v>41.882100000000001</v>
+      </c>
+      <c r="J681" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="682" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A682" s="47">
-        <v>706</v>
-      </c>
-      <c r="B682" s="97">
-        <v>544</v>
-      </c>
-      <c r="C682" s="98">
+        <v>709</v>
+      </c>
+      <c r="B682" s="16">
+        <v>547</v>
+      </c>
+      <c r="C682" s="101">
         <v>46290</v>
       </c>
-      <c r="D682" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E682" s="99" t="s">
-        <v>407</v>
-      </c>
-      <c r="F682" s="99" t="s">
-        <v>408</v>
-      </c>
-      <c r="G682" s="100">
-        <v>41.35284</v>
-      </c>
-      <c r="H682" s="100">
-        <v>41.73574</v>
-      </c>
-      <c r="J682" t="s">
-        <v>405</v>
+      <c r="D682" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E682" s="102" t="s">
+        <v>376</v>
+      </c>
+      <c r="F682" s="102" t="s">
+        <v>370</v>
+      </c>
+      <c r="G682" s="103">
+        <v>41.352469999999997</v>
+      </c>
+      <c r="H682" s="103">
+        <v>41.733600000000003</v>
       </c>
     </row>
     <row r="683" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A683" s="47">
-        <v>707</v>
-      </c>
-      <c r="B683" s="16">
-        <v>545</v>
-      </c>
-      <c r="C683" s="101">
+        <v>710</v>
+      </c>
+      <c r="B683" s="13">
+        <v>548</v>
+      </c>
+      <c r="C683" s="94">
         <v>46290</v>
       </c>
-      <c r="D683" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E683" s="102" t="s">
-        <v>329</v>
-      </c>
-      <c r="F683" s="102" t="s">
-        <v>368</v>
-      </c>
-      <c r="G683" s="103">
-        <v>41.35284</v>
-      </c>
-      <c r="H683" s="103">
-        <v>41.73574</v>
+      <c r="D683" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E683" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F683" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G683" s="96">
+        <v>41.352409999999999</v>
+      </c>
+      <c r="H683" s="96">
+        <v>41.73386</v>
       </c>
     </row>
     <row r="684" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A684" s="47">
-        <v>708</v>
-      </c>
-      <c r="B684" s="97">
-        <v>546</v>
-      </c>
-      <c r="C684" s="98">
+        <v>711</v>
+      </c>
+      <c r="B684" s="16">
+        <v>549</v>
+      </c>
+      <c r="C684" s="101">
         <v>46290</v>
       </c>
-      <c r="D684" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E684" s="99" t="s">
-        <v>409</v>
-      </c>
-      <c r="F684" s="99" t="s">
-        <v>406</v>
-      </c>
-      <c r="G684" s="100">
-        <v>41.375500000000002</v>
-      </c>
-      <c r="H684" s="100">
-        <v>41.882100000000001</v>
-      </c>
-      <c r="J684" t="s">
-        <v>406</v>
+      <c r="D684" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E684" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F684" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G684" s="103">
+        <v>41.350999999999999</v>
+      </c>
+      <c r="H684" s="103">
+        <v>41.735199999999999</v>
       </c>
     </row>
     <row r="685" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A685" s="47">
-        <v>709</v>
-      </c>
-      <c r="B685" s="16">
-        <v>547</v>
-      </c>
-      <c r="C685" s="101">
+        <v>712</v>
+      </c>
+      <c r="B685" s="13">
+        <v>550</v>
+      </c>
+      <c r="C685" s="94">
         <v>46290</v>
       </c>
-      <c r="D685" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="E685" s="102" t="s">
-        <v>376</v>
-      </c>
-      <c r="F685" s="102" t="s">
-        <v>370</v>
-      </c>
-      <c r="G685" s="103">
-        <v>41.352469999999997</v>
-      </c>
-      <c r="H685" s="103">
-        <v>41.733600000000003</v>
+      <c r="D685" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E685" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F685" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="G685" s="96">
+        <v>41.3491</v>
+      </c>
+      <c r="H685" s="96">
+        <v>41.734070000000003</v>
       </c>
     </row>
     <row r="686" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A686" s="47">
-        <v>710</v>
-      </c>
-      <c r="B686" s="13">
-        <v>548</v>
-      </c>
-      <c r="C686" s="94">
+      <c r="A686" s="104">
+        <v>713</v>
+      </c>
+      <c r="B686" s="38">
+        <v>551</v>
+      </c>
+      <c r="C686" s="105">
         <v>46290</v>
       </c>
       <c r="D686" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E686" s="108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F686" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="G686" s="88">
+        <v>41.269660000000002</v>
+      </c>
+      <c r="H686" s="88">
+        <v>41.359920000000002</v>
+      </c>
+    </row>
+    <row r="687" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A687" s="104">
+        <v>714</v>
+      </c>
+      <c r="B687" s="29">
+        <v>552</v>
+      </c>
+      <c r="C687" s="107">
+        <v>46290</v>
+      </c>
+      <c r="D687" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="E686" s="95" t="s">
+      <c r="E687" s="106" t="s">
         <v>331</v>
       </c>
-      <c r="F686" s="95" t="s">
+      <c r="F687" s="106" t="s">
         <v>332</v>
       </c>
-      <c r="G686" s="96">
-        <v>41.352409999999999</v>
-      </c>
-      <c r="H686" s="96">
-        <v>41.73386</v>
-      </c>
-    </row>
-    <row r="687" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A687" s="47">
-        <v>711</v>
-      </c>
-      <c r="B687" s="16">
-        <v>549</v>
-      </c>
-      <c r="C687" s="101">
+      <c r="G687" s="87">
+        <v>41.269660000000002</v>
+      </c>
+      <c r="H687" s="87">
+        <v>41.359920000000002</v>
+      </c>
+    </row>
+    <row r="688" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A688" s="104">
+        <v>715</v>
+      </c>
+      <c r="B688" s="38">
+        <v>553</v>
+      </c>
+      <c r="C688" s="105">
         <v>46290</v>
       </c>
-      <c r="D687" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E687" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F687" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G687" s="103">
-        <v>41.350999999999999</v>
-      </c>
-      <c r="H687" s="103">
-        <v>41.735199999999999</v>
-      </c>
-    </row>
-    <row r="688" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A688" s="47">
-        <v>712</v>
-      </c>
-      <c r="B688" s="13">
-        <v>550</v>
-      </c>
-      <c r="C688" s="94">
-        <v>46290</v>
-      </c>
       <c r="D688" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E688" s="95" t="s">
-        <v>13</v>
-      </c>
-      <c r="F688" s="95" t="s">
-        <v>101</v>
-      </c>
-      <c r="G688" s="96">
-        <v>41.3491</v>
-      </c>
-      <c r="H688" s="96">
-        <v>41.734070000000003</v>
+        <v>391</v>
+      </c>
+      <c r="E688" s="108" t="s">
+        <v>408</v>
+      </c>
+      <c r="F688" s="108" t="s">
+        <v>405</v>
+      </c>
+      <c r="G688" s="88">
+        <v>41.269660000000002</v>
+      </c>
+      <c r="H688" s="88">
+        <v>41.359920000000002</v>
+      </c>
+      <c r="J688" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="689" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A689" s="104">
-        <v>713</v>
-      </c>
-      <c r="B689" s="38">
-        <v>551</v>
-      </c>
-      <c r="C689" s="105">
+        <v>716</v>
+      </c>
+      <c r="B689" s="29">
+        <v>554</v>
+      </c>
+      <c r="C689" s="107">
         <v>46290</v>
       </c>
-      <c r="D689" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E689" s="108" t="s">
-        <v>367</v>
-      </c>
-      <c r="F689" s="108" t="s">
-        <v>369</v>
-      </c>
-      <c r="G689" s="88">
+      <c r="D689" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E689" s="106" t="s">
+        <v>329</v>
+      </c>
+      <c r="F689" s="106" t="s">
+        <v>368</v>
+      </c>
+      <c r="G689" s="87">
         <v>41.269660000000002</v>
       </c>
-      <c r="H689" s="88">
+      <c r="H689" s="87">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="690" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A690" s="104">
-        <v>714</v>
-      </c>
-      <c r="B690" s="29">
-        <v>552</v>
-      </c>
-      <c r="C690" s="107">
+        <v>717</v>
+      </c>
+      <c r="B690" s="38">
+        <v>555</v>
+      </c>
+      <c r="C690" s="105">
         <v>46290</v>
       </c>
-      <c r="D690" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E690" s="106" t="s">
-        <v>331</v>
-      </c>
-      <c r="F690" s="106" t="s">
-        <v>332</v>
-      </c>
-      <c r="G690" s="87">
+      <c r="D690" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E690" s="108" t="s">
+        <v>327</v>
+      </c>
+      <c r="F690" s="108" t="s">
+        <v>328</v>
+      </c>
+      <c r="G690" s="88">
         <v>41.269660000000002</v>
       </c>
-      <c r="H690" s="87">
+      <c r="H690" s="88">
         <v>41.359920000000002</v>
       </c>
     </row>
     <row r="691" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A691" s="104">
-        <v>715</v>
-      </c>
-      <c r="B691" s="38">
-        <v>553</v>
-      </c>
-      <c r="C691" s="105">
+        <v>718</v>
+      </c>
+      <c r="B691" s="29">
+        <v>556</v>
+      </c>
+      <c r="C691" s="107">
         <v>46290</v>
       </c>
-      <c r="D691" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E691" s="108" t="s">
-        <v>409</v>
-      </c>
-      <c r="F691" s="108" t="s">
-        <v>406</v>
-      </c>
-      <c r="G691" s="88">
-        <v>41.269660000000002</v>
-      </c>
-      <c r="H691" s="88">
-        <v>41.359920000000002</v>
-      </c>
-      <c r="J691" t="s">
-        <v>406</v>
+      <c r="D691" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="E691" s="106" t="s">
+        <v>389</v>
+      </c>
+      <c r="F691" s="106" t="s">
+        <v>390</v>
+      </c>
+      <c r="G691" s="87">
+        <v>41.271999999999998</v>
+      </c>
+      <c r="H691" s="87">
+        <v>41.366070000000001</v>
       </c>
     </row>
     <row r="692" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A692" s="104">
-        <v>716</v>
-      </c>
-      <c r="B692" s="29">
-        <v>554</v>
-      </c>
-      <c r="C692" s="107">
+        <v>719</v>
+      </c>
+      <c r="B692" s="38">
+        <v>557</v>
+      </c>
+      <c r="C692" s="105">
         <v>46290</v>
       </c>
-      <c r="D692" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E692" s="106" t="s">
-        <v>329</v>
-      </c>
-      <c r="F692" s="106" t="s">
-        <v>368</v>
-      </c>
-      <c r="G692" s="87">
-        <v>41.269660000000002</v>
-      </c>
-      <c r="H692" s="87">
-        <v>41.359920000000002</v>
+      <c r="D692" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E692" s="108" t="s">
+        <v>408</v>
+      </c>
+      <c r="F692" s="108" t="s">
+        <v>405</v>
+      </c>
+      <c r="G692" s="88">
+        <v>41.271999999999998</v>
+      </c>
+      <c r="H692" s="88">
+        <v>41.366070000000001</v>
+      </c>
+      <c r="J692" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="693" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A693" s="104">
-        <v>717</v>
-      </c>
-      <c r="B693" s="38">
-        <v>555</v>
-      </c>
-      <c r="C693" s="105">
+        <v>720</v>
+      </c>
+      <c r="B693" s="109">
+        <v>558</v>
+      </c>
+      <c r="C693" s="110">
         <v>46290</v>
       </c>
-      <c r="D693" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="E693" s="108" t="s">
-        <v>327</v>
-      </c>
-      <c r="F693" s="108" t="s">
-        <v>328</v>
-      </c>
-      <c r="G693" s="88">
-        <v>41.269660000000002</v>
-      </c>
-      <c r="H693" s="88">
-        <v>41.359920000000002</v>
+      <c r="D693" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E693" s="111" t="s">
+        <v>408</v>
+      </c>
+      <c r="F693" s="111" t="s">
+        <v>405</v>
+      </c>
+      <c r="G693" s="112">
+        <v>41.312849999999997</v>
+      </c>
+      <c r="H693" s="112">
+        <v>41.295079999999999</v>
+      </c>
+      <c r="J693" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="694" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A694" s="104">
-        <v>718</v>
-      </c>
-      <c r="B694" s="29">
-        <v>556</v>
-      </c>
-      <c r="C694" s="107">
+        <v>721</v>
+      </c>
+      <c r="B694" s="38">
+        <v>559</v>
+      </c>
+      <c r="C694" s="105">
         <v>46290</v>
       </c>
-      <c r="D694" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E694" s="106" t="s">
-        <v>389</v>
-      </c>
-      <c r="F694" s="106" t="s">
-        <v>390</v>
-      </c>
-      <c r="G694" s="87">
-        <v>41.271999999999998</v>
-      </c>
-      <c r="H694" s="87">
-        <v>41.366070000000001</v>
+      <c r="D694" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E694" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="F694" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="G694" s="88">
+        <v>41.313079999999999</v>
+      </c>
+      <c r="H694" s="88">
+        <v>41.295029999999997</v>
       </c>
     </row>
     <row r="695" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A695" s="104">
-        <v>719</v>
-      </c>
-      <c r="B695" s="38">
-        <v>557</v>
-      </c>
-      <c r="C695" s="105">
+        <v>722</v>
+      </c>
+      <c r="B695" s="29">
+        <v>560</v>
+      </c>
+      <c r="C695" s="107">
         <v>46290</v>
       </c>
-      <c r="D695" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E695" s="108" t="s">
-        <v>409</v>
-      </c>
-      <c r="F695" s="108" t="s">
-        <v>406</v>
-      </c>
-      <c r="G695" s="88">
-        <v>41.271999999999998</v>
-      </c>
-      <c r="H695" s="88">
-        <v>41.366070000000001</v>
-      </c>
-      <c r="J695" t="s">
-        <v>406</v>
+      <c r="D695" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E695" s="106" t="s">
+        <v>367</v>
+      </c>
+      <c r="F695" s="106" t="s">
+        <v>369</v>
+      </c>
+      <c r="G695" s="87">
+        <v>41.313079999999999</v>
+      </c>
+      <c r="H695" s="87">
+        <v>41.295029999999997</v>
       </c>
     </row>
     <row r="696" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A696" s="104">
-        <v>720</v>
-      </c>
-      <c r="B696" s="109">
-        <v>558</v>
-      </c>
-      <c r="C696" s="110">
+        <v>723</v>
+      </c>
+      <c r="B696" s="38">
+        <v>561</v>
+      </c>
+      <c r="C696" s="105">
         <v>46290</v>
       </c>
-      <c r="D696" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E696" s="111" t="s">
-        <v>409</v>
-      </c>
-      <c r="F696" s="111" t="s">
-        <v>406</v>
-      </c>
-      <c r="G696" s="112">
-        <v>41.312849999999997</v>
-      </c>
-      <c r="H696" s="112">
-        <v>41.295079999999999</v>
-      </c>
-      <c r="J696" t="s">
-        <v>406</v>
+      <c r="D696" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E696" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="F696" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="G696" s="88">
+        <v>41.31521</v>
+      </c>
+      <c r="H696" s="88">
+        <v>41.300800000000002</v>
       </c>
     </row>
     <row r="697" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A697" s="104">
-        <v>721</v>
-      </c>
-      <c r="B697" s="38">
-        <v>559</v>
-      </c>
-      <c r="C697" s="105">
+        <v>724</v>
+      </c>
+      <c r="B697" s="109">
+        <v>562</v>
+      </c>
+      <c r="C697" s="110">
         <v>46290</v>
       </c>
-      <c r="D697" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E697" s="108" t="s">
-        <v>329</v>
-      </c>
-      <c r="F697" s="108" t="s">
-        <v>368</v>
-      </c>
-      <c r="G697" s="88">
-        <v>41.313079999999999</v>
-      </c>
-      <c r="H697" s="88">
-        <v>41.295029999999997</v>
+      <c r="D697" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="E697" s="111" t="s">
+        <v>331</v>
+      </c>
+      <c r="F697" s="111" t="s">
+        <v>332</v>
+      </c>
+      <c r="G697" s="112">
+        <v>41.314399999999999</v>
+      </c>
+      <c r="H697" s="112">
+        <v>41.383319999999998</v>
       </c>
     </row>
     <row r="698" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A698" s="104">
-        <v>722</v>
-      </c>
-      <c r="B698" s="29">
-        <v>560</v>
-      </c>
-      <c r="C698" s="107">
+        <v>725</v>
+      </c>
+      <c r="B698" s="38">
+        <v>563</v>
+      </c>
+      <c r="C698" s="105">
         <v>46290</v>
       </c>
-      <c r="D698" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E698" s="106" t="s">
-        <v>367</v>
-      </c>
-      <c r="F698" s="106" t="s">
-        <v>369</v>
-      </c>
-      <c r="G698" s="87">
-        <v>41.313079999999999</v>
-      </c>
-      <c r="H698" s="87">
-        <v>41.295029999999997</v>
+      <c r="D698" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E698" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="F698" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="G698" s="88">
+        <v>41.321469999999998</v>
+      </c>
+      <c r="H698" s="88">
+        <v>41.397590000000001</v>
       </c>
     </row>
     <row r="699" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A699" s="104">
-        <v>723</v>
-      </c>
-      <c r="B699" s="38">
-        <v>561</v>
-      </c>
-      <c r="C699" s="105">
+        <v>726</v>
+      </c>
+      <c r="B699" s="29">
+        <v>564</v>
+      </c>
+      <c r="C699" s="107">
         <v>46290</v>
       </c>
-      <c r="D699" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E699" s="108" t="s">
-        <v>116</v>
-      </c>
-      <c r="F699" s="108" t="s">
-        <v>333</v>
-      </c>
-      <c r="G699" s="88">
-        <v>41.31521</v>
-      </c>
-      <c r="H699" s="88">
-        <v>41.300800000000002</v>
+      <c r="D699" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E699" s="106" t="s">
+        <v>408</v>
+      </c>
+      <c r="F699" s="106" t="s">
+        <v>405</v>
+      </c>
+      <c r="G699" s="87">
+        <v>41.321469999999998</v>
+      </c>
+      <c r="H699" s="87">
+        <v>41.397590000000001</v>
+      </c>
+      <c r="J699" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="700" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A700" s="104">
-        <v>724</v>
-      </c>
-      <c r="B700" s="109">
-        <v>562</v>
-      </c>
-      <c r="C700" s="110">
+        <v>727</v>
+      </c>
+      <c r="B700" s="38">
+        <v>565</v>
+      </c>
+      <c r="C700" s="105">
         <v>46290</v>
       </c>
-      <c r="D700" s="97" t="s">
-        <v>330</v>
-      </c>
-      <c r="E700" s="111" t="s">
-        <v>331</v>
-      </c>
-      <c r="F700" s="111" t="s">
-        <v>332</v>
-      </c>
-      <c r="G700" s="112">
-        <v>41.314399999999999</v>
-      </c>
-      <c r="H700" s="112">
-        <v>41.383319999999998</v>
+      <c r="D700" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E700" s="108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F700" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="G700" s="88">
+        <v>41.32</v>
+      </c>
+      <c r="H700" s="88">
+        <v>41.395359999999997</v>
       </c>
     </row>
     <row r="701" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A701" s="104">
-        <v>725</v>
-      </c>
-      <c r="B701" s="38">
-        <v>563</v>
-      </c>
-      <c r="C701" s="105">
+        <v>728</v>
+      </c>
+      <c r="B701" s="29">
+        <v>566</v>
+      </c>
+      <c r="C701" s="107">
         <v>46290</v>
       </c>
-      <c r="D701" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E701" s="108" t="s">
-        <v>329</v>
-      </c>
-      <c r="F701" s="108" t="s">
-        <v>368</v>
-      </c>
-      <c r="G701" s="88">
-        <v>41.321469999999998</v>
-      </c>
-      <c r="H701" s="88">
-        <v>41.397590000000001</v>
+      <c r="D701" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E701" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="F701" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="G701" s="87">
+        <v>41.32</v>
+      </c>
+      <c r="H701" s="87">
+        <v>41.395359999999997</v>
       </c>
     </row>
     <row r="702" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A702" s="104">
-        <v>726</v>
-      </c>
-      <c r="B702" s="29">
-        <v>564</v>
-      </c>
-      <c r="C702" s="107">
+        <v>729</v>
+      </c>
+      <c r="B702" s="38">
+        <v>567</v>
+      </c>
+      <c r="C702" s="105">
         <v>46290</v>
       </c>
-      <c r="D702" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E702" s="106" t="s">
-        <v>409</v>
-      </c>
-      <c r="F702" s="106" t="s">
-        <v>406</v>
-      </c>
-      <c r="G702" s="87">
-        <v>41.321469999999998</v>
-      </c>
-      <c r="H702" s="87">
-        <v>41.397590000000001</v>
-      </c>
-      <c r="J702" t="s">
-        <v>406</v>
+      <c r="D702" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E702" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="F702" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="G702" s="88">
+        <v>41.345910000000003</v>
+      </c>
+      <c r="H702" s="88">
+        <v>41.308459999999997</v>
       </c>
     </row>
     <row r="703" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A703" s="104">
-        <v>727</v>
-      </c>
-      <c r="B703" s="38">
-        <v>565</v>
-      </c>
-      <c r="C703" s="105">
+        <v>730</v>
+      </c>
+      <c r="B703" s="29">
+        <v>568</v>
+      </c>
+      <c r="C703" s="107">
         <v>46290</v>
       </c>
-      <c r="D703" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E703" s="108" t="s">
-        <v>367</v>
-      </c>
-      <c r="F703" s="108" t="s">
-        <v>369</v>
-      </c>
-      <c r="G703" s="88">
-        <v>41.32</v>
-      </c>
-      <c r="H703" s="88">
-        <v>41.395359999999997</v>
+      <c r="D703" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E703" s="106" t="s">
+        <v>331</v>
+      </c>
+      <c r="F703" s="106" t="s">
+        <v>332</v>
+      </c>
+      <c r="G703" s="87">
+        <v>41.345910000000003</v>
+      </c>
+      <c r="H703" s="87">
+        <v>41.308459999999997</v>
       </c>
     </row>
     <row r="704" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A704" s="104">
-        <v>728</v>
-      </c>
-      <c r="B704" s="29">
-        <v>566</v>
-      </c>
-      <c r="C704" s="107">
+        <v>731</v>
+      </c>
+      <c r="B704" s="38">
+        <v>569</v>
+      </c>
+      <c r="C704" s="105">
         <v>46290</v>
       </c>
-      <c r="D704" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E704" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="F704" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="G704" s="87">
-        <v>41.32</v>
-      </c>
-      <c r="H704" s="87">
-        <v>41.395359999999997</v>
+      <c r="D704" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E704" s="108" t="s">
+        <v>408</v>
+      </c>
+      <c r="F704" s="108" t="s">
+        <v>405</v>
+      </c>
+      <c r="G704" s="88">
+        <v>41.365650000000002</v>
+      </c>
+      <c r="H704" s="88">
+        <v>41.3367</v>
+      </c>
+      <c r="J704" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="705" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A705" s="104">
-        <v>729</v>
-      </c>
-      <c r="B705" s="38">
-        <v>567</v>
-      </c>
-      <c r="C705" s="105">
+        <v>732</v>
+      </c>
+      <c r="B705" s="29">
+        <v>570</v>
+      </c>
+      <c r="C705" s="107">
         <v>46290</v>
       </c>
-      <c r="D705" s="13" t="s">
+      <c r="D705" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E705" s="108" t="s">
+      <c r="E705" s="106" t="s">
         <v>116</v>
       </c>
-      <c r="F705" s="108" t="s">
+      <c r="F705" s="106" t="s">
         <v>333</v>
       </c>
-      <c r="G705" s="88">
-        <v>41.345910000000003</v>
-      </c>
-      <c r="H705" s="88">
-        <v>41.308459999999997</v>
+      <c r="G705" s="87">
+        <v>41.365650000000002</v>
+      </c>
+      <c r="H705" s="87">
+        <v>41.3367</v>
       </c>
     </row>
     <row r="706" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A706" s="104">
-        <v>730</v>
-      </c>
-      <c r="B706" s="29">
-        <v>568</v>
-      </c>
-      <c r="C706" s="107">
+        <v>733</v>
+      </c>
+      <c r="B706" s="38">
+        <v>571</v>
+      </c>
+      <c r="C706" s="105">
         <v>46290</v>
       </c>
-      <c r="D706" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E706" s="106" t="s">
-        <v>331</v>
-      </c>
-      <c r="F706" s="106" t="s">
-        <v>332</v>
-      </c>
-      <c r="G706" s="87">
-        <v>41.345910000000003</v>
-      </c>
-      <c r="H706" s="87">
-        <v>41.308459999999997</v>
+      <c r="D706" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E706" s="108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F706" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="G706" s="88">
+        <v>41.365650000000002</v>
+      </c>
+      <c r="H706" s="88">
+        <v>41.3367</v>
       </c>
     </row>
     <row r="707" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A707" s="104">
-        <v>731</v>
-      </c>
-      <c r="B707" s="38">
-        <v>569</v>
-      </c>
-      <c r="C707" s="105">
+        <v>734</v>
+      </c>
+      <c r="B707" s="29">
+        <v>572</v>
+      </c>
+      <c r="C707" s="107">
         <v>46290</v>
       </c>
-      <c r="D707" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E707" s="108" t="s">
-        <v>409</v>
-      </c>
-      <c r="F707" s="108" t="s">
-        <v>406</v>
-      </c>
-      <c r="G707" s="88">
+      <c r="D707" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E707" s="106" t="s">
+        <v>329</v>
+      </c>
+      <c r="F707" s="106" t="s">
+        <v>368</v>
+      </c>
+      <c r="G707" s="87">
         <v>41.365650000000002</v>
       </c>
-      <c r="H707" s="88">
+      <c r="H707" s="87">
         <v>41.3367</v>
-      </c>
-      <c r="J707" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="708" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A708" s="104">
-        <v>732</v>
-      </c>
-      <c r="B708" s="29">
-        <v>570</v>
-      </c>
-      <c r="C708" s="107">
+        <v>735</v>
+      </c>
+      <c r="B708" s="38">
+        <v>573</v>
+      </c>
+      <c r="C708" s="105">
         <v>46290</v>
       </c>
-      <c r="D708" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E708" s="106" t="s">
-        <v>116</v>
-      </c>
-      <c r="F708" s="106" t="s">
-        <v>333</v>
-      </c>
-      <c r="G708" s="87">
-        <v>41.365650000000002</v>
-      </c>
-      <c r="H708" s="87">
-        <v>41.3367</v>
+      <c r="D708" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E708" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="F708" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="G708" s="88">
+        <v>41.361899999999999</v>
+      </c>
+      <c r="H708" s="88">
+        <v>41.397300000000001</v>
       </c>
     </row>
     <row r="709" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A709" s="104">
-        <v>733</v>
-      </c>
-      <c r="B709" s="38">
-        <v>571</v>
-      </c>
-      <c r="C709" s="105">
+        <v>736</v>
+      </c>
+      <c r="B709" s="109">
+        <v>574</v>
+      </c>
+      <c r="C709" s="110">
         <v>46290</v>
       </c>
-      <c r="D709" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E709" s="108" t="s">
-        <v>367</v>
-      </c>
-      <c r="F709" s="108" t="s">
-        <v>369</v>
-      </c>
-      <c r="G709" s="88">
-        <v>41.365650000000002</v>
-      </c>
-      <c r="H709" s="88">
-        <v>41.3367</v>
+      <c r="D709" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E709" s="111" t="s">
+        <v>408</v>
+      </c>
+      <c r="F709" s="111" t="s">
+        <v>405</v>
+      </c>
+      <c r="G709" s="112">
+        <v>41.36036</v>
+      </c>
+      <c r="H709" s="112">
+        <v>41.397559999999999</v>
+      </c>
+      <c r="J709" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="710" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A710" s="104">
-        <v>734</v>
-      </c>
-      <c r="B710" s="29">
-        <v>572</v>
-      </c>
-      <c r="C710" s="107">
+        <v>737</v>
+      </c>
+      <c r="B710" s="109">
+        <v>575</v>
+      </c>
+      <c r="C710" s="110">
         <v>46290</v>
       </c>
-      <c r="D710" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E710" s="106" t="s">
-        <v>329</v>
-      </c>
-      <c r="F710" s="106" t="s">
-        <v>368</v>
-      </c>
-      <c r="G710" s="87">
-        <v>41.365650000000002</v>
-      </c>
-      <c r="H710" s="87">
-        <v>41.3367</v>
+      <c r="D710" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E710" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="F710" s="111" t="s">
+        <v>407</v>
+      </c>
+      <c r="G710" s="112">
+        <v>41.345950000000002</v>
+      </c>
+      <c r="H710" s="112">
+        <v>41.323419999999999</v>
+      </c>
+      <c r="J710" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="711" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A711" s="104">
-        <v>735</v>
-      </c>
-      <c r="B711" s="38">
-        <v>573</v>
-      </c>
-      <c r="C711" s="105">
+        <v>738</v>
+      </c>
+      <c r="B711" s="29">
+        <v>576</v>
+      </c>
+      <c r="C711" s="107">
         <v>46290</v>
       </c>
-      <c r="D711" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E711" s="108" t="s">
-        <v>329</v>
-      </c>
-      <c r="F711" s="108" t="s">
-        <v>368</v>
-      </c>
-      <c r="G711" s="88">
-        <v>41.361899999999999</v>
-      </c>
-      <c r="H711" s="88">
-        <v>41.397300000000001</v>
+      <c r="D711" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E711" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="F711" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G711" s="87">
+        <v>41.357779999999998</v>
+      </c>
+      <c r="H711" s="87">
+        <v>41.400300000000001</v>
       </c>
     </row>
     <row r="712" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A712" s="104">
-        <v>736</v>
-      </c>
-      <c r="B712" s="109">
-        <v>574</v>
-      </c>
-      <c r="C712" s="110">
+        <v>739</v>
+      </c>
+      <c r="B712" s="38">
+        <v>577</v>
+      </c>
+      <c r="C712" s="105">
         <v>46290</v>
       </c>
-      <c r="D712" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E712" s="111" t="s">
-        <v>409</v>
-      </c>
-      <c r="F712" s="111" t="s">
-        <v>406</v>
-      </c>
-      <c r="G712" s="112">
-        <v>41.36036</v>
-      </c>
-      <c r="H712" s="112">
-        <v>41.397559999999999</v>
-      </c>
-      <c r="J712" t="s">
-        <v>406</v>
+      <c r="D712" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E712" s="108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F712" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="G712" s="88">
+        <v>41.357089999999999</v>
+      </c>
+      <c r="H712" s="88">
+        <v>41.400820000000003</v>
       </c>
     </row>
     <row r="713" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A713" s="104">
-        <v>737</v>
-      </c>
-      <c r="B713" s="109">
-        <v>575</v>
-      </c>
-      <c r="C713" s="110">
+        <v>740</v>
+      </c>
+      <c r="B713" s="29">
+        <v>578</v>
+      </c>
+      <c r="C713" s="107">
         <v>46290</v>
       </c>
-      <c r="D713" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E713" s="111" t="s">
-        <v>407</v>
-      </c>
-      <c r="F713" s="111" t="s">
-        <v>408</v>
-      </c>
-      <c r="G713" s="112">
-        <v>41.345950000000002</v>
-      </c>
-      <c r="H713" s="112">
-        <v>41.323419999999999</v>
-      </c>
-      <c r="J713" t="s">
-        <v>405</v>
+      <c r="D713" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E713" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="F713" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="G713" s="87">
+        <v>41.380409999999998</v>
+      </c>
+      <c r="H713" s="87">
+        <v>41.401510000000002</v>
       </c>
     </row>
     <row r="714" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A714" s="104">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B714" s="29">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C714" s="107">
         <v>46290</v>
       </c>
-      <c r="D714" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E714" s="106" t="s">
-        <v>116</v>
-      </c>
-      <c r="F714" s="106" t="s">
-        <v>333</v>
-      </c>
-      <c r="G714" s="87">
-        <v>41.357779999999998</v>
-      </c>
-      <c r="H714" s="87">
-        <v>41.400300000000001</v>
+      <c r="D714" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E714" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="F714" s="111" t="s">
+        <v>407</v>
+      </c>
+      <c r="G714" s="112">
+        <v>41.324402900000003</v>
+      </c>
+      <c r="H714" s="112">
+        <v>41.396081299999999</v>
+      </c>
+      <c r="J714" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="715" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A715" s="104">
-        <v>739</v>
-      </c>
-      <c r="B715" s="38">
-        <v>577</v>
-      </c>
-      <c r="C715" s="105">
-        <v>46290</v>
+        <v>742</v>
+      </c>
+      <c r="B715" s="13">
+        <v>580</v>
+      </c>
+      <c r="C715" s="94">
+        <v>46300</v>
       </c>
       <c r="D715" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E715" s="108" t="s">
-        <v>367</v>
-      </c>
-      <c r="F715" s="108" t="s">
-        <v>369</v>
-      </c>
-      <c r="G715" s="88">
-        <v>41.357089999999999</v>
-      </c>
-      <c r="H715" s="88">
-        <v>41.400820000000003</v>
+        <v>326</v>
+      </c>
+      <c r="E715" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="F715" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="G715" s="96">
+        <v>41.253059999999998</v>
+      </c>
+      <c r="H715" s="96">
+        <v>41.586469999999998</v>
       </c>
     </row>
     <row r="716" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A716" s="104">
-        <v>740</v>
-      </c>
-      <c r="B716" s="29">
-        <v>578</v>
-      </c>
-      <c r="C716" s="107">
-        <v>46290</v>
+        <v>743</v>
+      </c>
+      <c r="B716" s="16">
+        <v>581</v>
+      </c>
+      <c r="C716" s="101">
+        <v>46300</v>
       </c>
       <c r="D716" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E716" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="F716" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="G716" s="87">
-        <v>41.380409999999998</v>
-      </c>
-      <c r="H716" s="87">
-        <v>41.401510000000002</v>
+        <v>366</v>
+      </c>
+      <c r="E716" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="F716" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="G716" s="103">
+        <v>41.252519999999997</v>
+      </c>
+      <c r="H716" s="103">
+        <v>41.585479999999997</v>
       </c>
     </row>
     <row r="717" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A717" s="104">
-        <v>741</v>
-      </c>
-      <c r="B717" s="29">
-        <v>579</v>
-      </c>
-      <c r="C717" s="107">
-        <v>46290</v>
-      </c>
-      <c r="D717" s="97" t="s">
-        <v>391</v>
-      </c>
-      <c r="E717" s="111" t="s">
-        <v>407</v>
-      </c>
-      <c r="F717" s="111" t="s">
-        <v>408</v>
-      </c>
-      <c r="G717" s="112">
-        <v>41.324402900000003</v>
-      </c>
-      <c r="H717" s="112">
-        <v>41.396081299999999</v>
-      </c>
-      <c r="J717" t="s">
-        <v>405</v>
+        <v>744</v>
+      </c>
+      <c r="B717" s="13">
+        <v>582</v>
+      </c>
+      <c r="C717" s="94">
+        <v>46300</v>
+      </c>
+      <c r="D717" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E717" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="F717" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="G717" s="96">
+        <v>41.253059999999998</v>
+      </c>
+      <c r="H717" s="96">
+        <v>41.586469999999998</v>
       </c>
     </row>
     <row r="718" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A718" s="104">
-        <v>742</v>
-      </c>
-      <c r="B718" s="13">
-        <v>580</v>
-      </c>
-      <c r="C718" s="94">
+        <v>745</v>
+      </c>
+      <c r="B718" s="16">
+        <v>583</v>
+      </c>
+      <c r="C718" s="101">
         <v>46300</v>
       </c>
-      <c r="D718" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="E718" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="F718" s="95" t="s">
-        <v>328</v>
-      </c>
-      <c r="G718" s="96">
-        <v>41.253059999999998</v>
-      </c>
-      <c r="H718" s="96">
-        <v>41.586469999999998</v>
+      <c r="D718" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E718" s="102" t="s">
+        <v>331</v>
+      </c>
+      <c r="F718" s="102" t="s">
+        <v>332</v>
+      </c>
+      <c r="G718" s="103">
+        <v>41.257829999999998</v>
+      </c>
+      <c r="H718" s="103">
+        <v>41.586599999999997</v>
       </c>
     </row>
     <row r="719" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A719" s="104">
-        <v>743</v>
-      </c>
-      <c r="B719" s="16">
-        <v>581</v>
-      </c>
-      <c r="C719" s="101">
+        <v>746</v>
+      </c>
+      <c r="B719" s="97">
+        <v>584</v>
+      </c>
+      <c r="C719" s="98">
         <v>46300</v>
       </c>
-      <c r="D719" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E719" s="102" t="s">
-        <v>367</v>
-      </c>
-      <c r="F719" s="102" t="s">
-        <v>369</v>
-      </c>
-      <c r="G719" s="103">
-        <v>41.252519999999997</v>
-      </c>
-      <c r="H719" s="103">
-        <v>41.585479999999997</v>
+      <c r="D719" s="97" t="s">
+        <v>323</v>
+      </c>
+      <c r="E719" s="99" t="s">
+        <v>324</v>
+      </c>
+      <c r="F719" s="99" t="s">
+        <v>325</v>
+      </c>
+      <c r="G719" s="100">
+        <v>41.256659999999997</v>
+      </c>
+      <c r="H719" s="100">
+        <v>41.588830000000002</v>
       </c>
     </row>
     <row r="720" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A720" s="104">
-        <v>744</v>
-      </c>
-      <c r="B720" s="13">
-        <v>582</v>
-      </c>
-      <c r="C720" s="94">
+        <v>747</v>
+      </c>
+      <c r="B720" s="16">
+        <v>585</v>
+      </c>
+      <c r="C720" s="101">
         <v>46300</v>
       </c>
-      <c r="D720" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="E720" s="95" t="s">
-        <v>386</v>
-      </c>
-      <c r="F720" s="95" t="s">
-        <v>320</v>
-      </c>
-      <c r="G720" s="96">
-        <v>41.253059999999998</v>
-      </c>
-      <c r="H720" s="96">
-        <v>41.586469999999998</v>
+      <c r="D720" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E720" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="F720" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="G720" s="103">
+        <v>41.256659999999997</v>
+      </c>
+      <c r="H720" s="103">
+        <v>41.588830000000002</v>
       </c>
     </row>
     <row r="721" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A721" s="104">
-        <v>745</v>
-      </c>
-      <c r="B721" s="16">
-        <v>583</v>
-      </c>
-      <c r="C721" s="101">
+        <v>748</v>
+      </c>
+      <c r="B721" s="97">
+        <v>586</v>
+      </c>
+      <c r="C721" s="98">
         <v>46300</v>
       </c>
-      <c r="D721" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E721" s="102" t="s">
-        <v>331</v>
-      </c>
-      <c r="F721" s="102" t="s">
-        <v>332</v>
-      </c>
-      <c r="G721" s="103">
-        <v>41.257829999999998</v>
-      </c>
-      <c r="H721" s="103">
-        <v>41.586599999999997</v>
+      <c r="D721" s="97" t="s">
+        <v>321</v>
+      </c>
+      <c r="E721" s="99" t="s">
+        <v>322</v>
+      </c>
+      <c r="F721" s="99" t="s">
+        <v>387</v>
+      </c>
+      <c r="G721" s="100">
+        <v>41.257460000000002</v>
+      </c>
+      <c r="H721" s="100">
+        <v>41.592829999999999</v>
       </c>
     </row>
     <row r="722" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A722" s="104">
-        <v>746</v>
-      </c>
-      <c r="B722" s="97">
-        <v>584</v>
-      </c>
-      <c r="C722" s="98">
+        <v>749</v>
+      </c>
+      <c r="B722" s="16">
+        <v>587</v>
+      </c>
+      <c r="C722" s="101">
         <v>46300</v>
       </c>
-      <c r="D722" s="97" t="s">
-        <v>323</v>
-      </c>
-      <c r="E722" s="99" t="s">
-        <v>324</v>
-      </c>
-      <c r="F722" s="99" t="s">
-        <v>325</v>
-      </c>
-      <c r="G722" s="100">
-        <v>41.256659999999997</v>
-      </c>
-      <c r="H722" s="100">
-        <v>41.588830000000002</v>
+      <c r="D722" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="E722" s="102" t="s">
+        <v>393</v>
+      </c>
+      <c r="F722" s="136" t="s">
+        <v>443</v>
+      </c>
+      <c r="G722" s="103">
+        <v>41.257460000000002</v>
+      </c>
+      <c r="H722" s="103">
+        <v>41.592829999999999</v>
+      </c>
+      <c r="J722" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="723" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A723" s="104">
-        <v>747</v>
-      </c>
-      <c r="B723" s="16">
-        <v>585</v>
-      </c>
-      <c r="C723" s="101">
+        <v>750</v>
+      </c>
+      <c r="B723" s="97">
+        <v>588</v>
+      </c>
+      <c r="C723" s="98">
         <v>46300</v>
       </c>
-      <c r="D723" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E723" s="102" t="s">
-        <v>335</v>
-      </c>
-      <c r="F723" s="102" t="s">
-        <v>336</v>
-      </c>
-      <c r="G723" s="103">
-        <v>41.256659999999997</v>
-      </c>
-      <c r="H723" s="103">
-        <v>41.588830000000002</v>
+      <c r="D723" s="97" t="s">
+        <v>388</v>
+      </c>
+      <c r="E723" s="99" t="s">
+        <v>389</v>
+      </c>
+      <c r="F723" s="99" t="s">
+        <v>390</v>
+      </c>
+      <c r="G723" s="100">
+        <v>41.25423</v>
+      </c>
+      <c r="H723" s="100">
+        <v>41.56662</v>
       </c>
     </row>
     <row r="724" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A724" s="104">
-        <v>748</v>
-      </c>
-      <c r="B724" s="97">
-        <v>586</v>
-      </c>
-      <c r="C724" s="98">
+        <v>751</v>
+      </c>
+      <c r="B724" s="16">
+        <v>589</v>
+      </c>
+      <c r="C724" s="101">
         <v>46300</v>
       </c>
-      <c r="D724" s="97" t="s">
-        <v>321</v>
-      </c>
-      <c r="E724" s="99" t="s">
-        <v>322</v>
-      </c>
-      <c r="F724" s="99" t="s">
-        <v>387</v>
-      </c>
-      <c r="G724" s="100">
-        <v>41.257460000000002</v>
-      </c>
-      <c r="H724" s="100">
-        <v>41.592829999999999</v>
+      <c r="D724" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E724" s="102" t="s">
+        <v>406</v>
+      </c>
+      <c r="F724" s="102" t="s">
+        <v>407</v>
+      </c>
+      <c r="G724" s="103">
+        <v>41.298110000000001</v>
+      </c>
+      <c r="H724" s="103">
+        <v>41.539209999999997</v>
+      </c>
+      <c r="J724" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="725" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A725" s="104">
-        <v>749</v>
-      </c>
-      <c r="B725" s="16">
-        <v>587</v>
-      </c>
-      <c r="C725" s="101">
+        <v>752</v>
+      </c>
+      <c r="B725" s="13">
+        <v>590</v>
+      </c>
+      <c r="C725" s="94">
         <v>46300</v>
       </c>
-      <c r="D725" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="E725" s="102" t="s">
-        <v>393</v>
-      </c>
-      <c r="F725" s="102" t="s">
-        <v>394</v>
-      </c>
-      <c r="G725" s="103">
-        <v>41.257460000000002</v>
-      </c>
-      <c r="H725" s="103">
-        <v>41.592829999999999</v>
-      </c>
-      <c r="J725" t="s">
-        <v>411</v>
+      <c r="D725" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E725" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F725" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G725" s="96">
+        <v>41.29768</v>
+      </c>
+      <c r="H725" s="96">
+        <v>41.538629999999998</v>
       </c>
     </row>
     <row r="726" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A726" s="104">
-        <v>750</v>
-      </c>
-      <c r="B726" s="97">
-        <v>588</v>
-      </c>
-      <c r="C726" s="98">
+        <v>753</v>
+      </c>
+      <c r="B726" s="16">
+        <v>591</v>
+      </c>
+      <c r="C726" s="101">
         <v>46300</v>
       </c>
-      <c r="D726" s="97" t="s">
-        <v>388</v>
-      </c>
-      <c r="E726" s="99" t="s">
-        <v>389</v>
-      </c>
-      <c r="F726" s="99" t="s">
-        <v>390</v>
-      </c>
-      <c r="G726" s="100">
-        <v>41.25423</v>
-      </c>
-      <c r="H726" s="100">
-        <v>41.56662</v>
+      <c r="D726" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E726" s="102" t="s">
+        <v>386</v>
+      </c>
+      <c r="F726" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="G726" s="103">
+        <v>41.296669999999999</v>
+      </c>
+      <c r="H726" s="103">
+        <v>41.537660000000002</v>
       </c>
     </row>
     <row r="727" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A727" s="104">
-        <v>751</v>
-      </c>
-      <c r="B727" s="16">
-        <v>589</v>
-      </c>
-      <c r="C727" s="101">
+        <v>754</v>
+      </c>
+      <c r="B727" s="97">
+        <v>592</v>
+      </c>
+      <c r="C727" s="98">
         <v>46300</v>
       </c>
-      <c r="D727" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="E727" s="102" t="s">
-        <v>407</v>
-      </c>
-      <c r="F727" s="102" t="s">
-        <v>408</v>
-      </c>
-      <c r="G727" s="103">
-        <v>41.298110000000001</v>
-      </c>
-      <c r="H727" s="103">
-        <v>41.539209999999997</v>
-      </c>
-      <c r="J727" t="s">
-        <v>405</v>
+      <c r="D727" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="E727" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="F727" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="G727" s="100">
+        <v>41.296599999999998</v>
+      </c>
+      <c r="H727" s="100">
+        <v>41.537649999999999</v>
       </c>
     </row>
     <row r="728" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A728" s="104">
-        <v>752</v>
-      </c>
-      <c r="B728" s="13">
-        <v>590</v>
-      </c>
-      <c r="C728" s="94">
+        <v>755</v>
+      </c>
+      <c r="B728" s="16">
+        <v>593</v>
+      </c>
+      <c r="C728" s="101">
         <v>46300</v>
       </c>
-      <c r="D728" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E728" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="F728" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="G728" s="96">
-        <v>41.29768</v>
-      </c>
-      <c r="H728" s="96">
-        <v>41.538629999999998</v>
+      <c r="D728" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E728" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F728" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G728" s="103">
+        <v>41.295099999999998</v>
+      </c>
+      <c r="H728" s="103">
+        <v>41.537939999999999</v>
       </c>
     </row>
     <row r="729" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A729" s="104">
-        <v>753</v>
-      </c>
-      <c r="B729" s="16">
-        <v>591</v>
-      </c>
-      <c r="C729" s="101">
+        <v>756</v>
+      </c>
+      <c r="B729" s="13">
+        <v>594</v>
+      </c>
+      <c r="C729" s="94">
         <v>46300</v>
       </c>
-      <c r="D729" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="E729" s="102" t="s">
-        <v>386</v>
-      </c>
-      <c r="F729" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="G729" s="103">
-        <v>41.296669999999999</v>
-      </c>
-      <c r="H729" s="103">
-        <v>41.537660000000002</v>
+      <c r="D729" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="E729" s="95" t="s">
+        <v>408</v>
+      </c>
+      <c r="F729" s="95" t="s">
+        <v>405</v>
+      </c>
+      <c r="G729" s="96">
+        <v>41.296909999999997</v>
+      </c>
+      <c r="H729" s="96">
+        <v>41.559269999999998</v>
+      </c>
+      <c r="J729" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="730" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A730" s="104">
-        <v>754</v>
-      </c>
-      <c r="B730" s="97">
-        <v>592</v>
-      </c>
-      <c r="C730" s="98">
+        <v>757</v>
+      </c>
+      <c r="B730" s="16">
+        <v>595</v>
+      </c>
+      <c r="C730" s="101">
         <v>46300</v>
       </c>
-      <c r="D730" s="97" t="s">
-        <v>330</v>
-      </c>
-      <c r="E730" s="99" t="s">
-        <v>331</v>
-      </c>
-      <c r="F730" s="99" t="s">
-        <v>332</v>
-      </c>
-      <c r="G730" s="100">
-        <v>41.296599999999998</v>
-      </c>
-      <c r="H730" s="100">
-        <v>41.537649999999999</v>
+      <c r="D730" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E730" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="F730" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="G730" s="103">
+        <v>41.294460000000001</v>
+      </c>
+      <c r="H730" s="103">
+        <v>41.56662</v>
       </c>
     </row>
     <row r="731" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A731" s="104">
-        <v>755</v>
-      </c>
-      <c r="B731" s="16">
-        <v>593</v>
-      </c>
-      <c r="C731" s="101">
+        <v>758</v>
+      </c>
+      <c r="B731" s="13">
+        <v>596</v>
+      </c>
+      <c r="C731" s="94">
         <v>46300</v>
       </c>
-      <c r="D731" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E731" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F731" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G731" s="103">
-        <v>41.295099999999998</v>
-      </c>
-      <c r="H731" s="103">
-        <v>41.537939999999999</v>
+      <c r="D731" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E731" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="F731" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="G731" s="96">
+        <v>41.26099</v>
+      </c>
+      <c r="H731" s="96">
+        <v>41.545209999999997</v>
       </c>
     </row>
     <row r="732" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A732" s="104">
-        <v>756</v>
-      </c>
-      <c r="B732" s="13">
-        <v>594</v>
-      </c>
-      <c r="C732" s="94">
+        <v>759</v>
+      </c>
+      <c r="B732" s="16">
+        <v>597</v>
+      </c>
+      <c r="C732" s="101">
         <v>46300</v>
       </c>
-      <c r="D732" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E732" s="95" t="s">
-        <v>409</v>
-      </c>
-      <c r="F732" s="95" t="s">
-        <v>406</v>
-      </c>
-      <c r="G732" s="96">
-        <v>41.296909999999997</v>
-      </c>
-      <c r="H732" s="96">
-        <v>41.559269999999998</v>
-      </c>
-      <c r="J732" t="s">
-        <v>406</v>
+      <c r="D732" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E732" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="F732" s="102" t="s">
+        <v>333</v>
+      </c>
+      <c r="G732" s="103">
+        <v>41.26099</v>
+      </c>
+      <c r="H732" s="103">
+        <v>41.545209999999997</v>
       </c>
     </row>
     <row r="733" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A733" s="104">
-        <v>757</v>
-      </c>
-      <c r="B733" s="16">
-        <v>595</v>
-      </c>
-      <c r="C733" s="101">
+        <v>760</v>
+      </c>
+      <c r="B733" s="13">
+        <v>598</v>
+      </c>
+      <c r="C733" s="94">
         <v>46300</v>
       </c>
-      <c r="D733" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E733" s="102" t="s">
-        <v>367</v>
-      </c>
-      <c r="F733" s="102" t="s">
-        <v>369</v>
-      </c>
-      <c r="G733" s="103">
-        <v>41.294460000000001</v>
-      </c>
-      <c r="H733" s="103">
-        <v>41.56662</v>
+      <c r="D733" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E733" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F733" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G733" s="96">
+        <v>41.26099</v>
+      </c>
+      <c r="H733" s="96">
+        <v>41.545209999999997</v>
       </c>
     </row>
     <row r="734" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A734" s="104">
-        <v>758</v>
-      </c>
-      <c r="B734" s="13">
-        <v>596</v>
-      </c>
-      <c r="C734" s="94">
+        <v>761</v>
+      </c>
+      <c r="B734" s="16">
+        <v>599</v>
+      </c>
+      <c r="C734" s="101">
         <v>46300</v>
       </c>
-      <c r="D734" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="E734" s="95" t="s">
-        <v>367</v>
-      </c>
-      <c r="F734" s="95" t="s">
-        <v>369</v>
-      </c>
-      <c r="G734" s="96">
+      <c r="D734" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E734" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F734" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G734" s="103">
         <v>41.26099</v>
       </c>
-      <c r="H734" s="96">
+      <c r="H734" s="103">
         <v>41.545209999999997</v>
       </c>
     </row>
     <row r="735" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A735" s="104">
-        <v>759</v>
-      </c>
-      <c r="B735" s="16">
-        <v>597</v>
-      </c>
-      <c r="C735" s="101">
+        <v>762</v>
+      </c>
+      <c r="B735" s="13">
+        <v>600</v>
+      </c>
+      <c r="C735" s="94">
         <v>46300</v>
       </c>
-      <c r="D735" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E735" s="102" t="s">
-        <v>116</v>
-      </c>
-      <c r="F735" s="102" t="s">
-        <v>333</v>
-      </c>
-      <c r="G735" s="103">
+      <c r="D735" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E735" s="95" t="s">
+        <v>322</v>
+      </c>
+      <c r="F735" s="95" t="s">
+        <v>387</v>
+      </c>
+      <c r="G735" s="96">
         <v>41.26099</v>
       </c>
-      <c r="H735" s="103">
+      <c r="H735" s="96">
         <v>41.545209999999997</v>
       </c>
     </row>
     <row r="736" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A736" s="104">
-        <v>760</v>
-      </c>
-      <c r="B736" s="13">
-        <v>598</v>
-      </c>
-      <c r="C736" s="94">
+        <v>763</v>
+      </c>
+      <c r="B736" s="16">
+        <v>601</v>
+      </c>
+      <c r="C736" s="101">
         <v>46300</v>
       </c>
-      <c r="D736" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E736" s="95" t="s">
-        <v>329</v>
-      </c>
-      <c r="F736" s="95" t="s">
-        <v>368</v>
-      </c>
-      <c r="G736" s="96">
-        <v>41.26099</v>
-      </c>
-      <c r="H736" s="96">
-        <v>41.545209999999997</v>
+      <c r="D736" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E736" s="102" t="s">
+        <v>386</v>
+      </c>
+      <c r="F736" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="G736" s="103">
+        <v>41.263240000000003</v>
+      </c>
+      <c r="H736" s="103">
+        <v>41.54468</v>
       </c>
     </row>
     <row r="737" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A737" s="104">
-        <v>761</v>
-      </c>
-      <c r="B737" s="16">
-        <v>599</v>
-      </c>
-      <c r="C737" s="101">
+        <v>764</v>
+      </c>
+      <c r="B737" s="13">
+        <v>602</v>
+      </c>
+      <c r="C737" s="94">
         <v>46300</v>
       </c>
-      <c r="D737" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E737" s="102" t="s">
-        <v>327</v>
-      </c>
-      <c r="F737" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G737" s="103">
-        <v>41.26099</v>
-      </c>
-      <c r="H737" s="103">
-        <v>41.545209999999997</v>
+      <c r="D737" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E737" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F737" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G737" s="96">
+        <v>41.263240000000003</v>
+      </c>
+      <c r="H737" s="96">
+        <v>41.54468</v>
       </c>
     </row>
     <row r="738" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A738" s="104">
-        <v>762</v>
-      </c>
-      <c r="B738" s="13">
-        <v>600</v>
-      </c>
-      <c r="C738" s="94">
+        <v>765</v>
+      </c>
+      <c r="B738" s="97">
+        <v>603</v>
+      </c>
+      <c r="C738" s="98">
         <v>46300</v>
       </c>
-      <c r="D738" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="E738" s="95" t="s">
-        <v>322</v>
-      </c>
-      <c r="F738" s="95" t="s">
-        <v>387</v>
-      </c>
-      <c r="G738" s="96">
-        <v>41.26099</v>
-      </c>
-      <c r="H738" s="96">
-        <v>41.545209999999997</v>
+      <c r="D738" s="97" t="s">
+        <v>391</v>
+      </c>
+      <c r="E738" s="99" t="s">
+        <v>408</v>
+      </c>
+      <c r="F738" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="G738" s="100">
+        <v>41.26793</v>
+      </c>
+      <c r="H738" s="100">
+        <v>41.548389999999998</v>
+      </c>
+      <c r="J738" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="739" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A739" s="104">
-        <v>763</v>
-      </c>
-      <c r="B739" s="16">
-        <v>601</v>
-      </c>
-      <c r="C739" s="101">
+        <v>766</v>
+      </c>
+      <c r="B739" s="13">
+        <v>604</v>
+      </c>
+      <c r="C739" s="94">
         <v>46300</v>
       </c>
-      <c r="D739" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="E739" s="102" t="s">
-        <v>386</v>
-      </c>
-      <c r="F739" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="G739" s="103">
-        <v>41.263240000000003</v>
-      </c>
-      <c r="H739" s="103">
-        <v>41.54468</v>
+      <c r="D739" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E739" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F739" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G739" s="96">
+        <v>41.26793</v>
+      </c>
+      <c r="H739" s="96">
+        <v>41.548389999999998</v>
       </c>
     </row>
     <row r="740" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A740" s="104">
-        <v>764</v>
-      </c>
-      <c r="B740" s="13">
-        <v>602</v>
-      </c>
-      <c r="C740" s="94">
+        <v>767</v>
+      </c>
+      <c r="B740" s="16">
+        <v>605</v>
+      </c>
+      <c r="C740" s="101">
         <v>46300</v>
       </c>
-      <c r="D740" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E740" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="F740" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="G740" s="96">
-        <v>41.263240000000003</v>
-      </c>
-      <c r="H740" s="96">
-        <v>41.54468</v>
+      <c r="D740" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E740" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F740" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G740" s="103">
+        <v>41.27948</v>
+      </c>
+      <c r="H740" s="103">
+        <v>41.55856</v>
       </c>
     </row>
     <row r="741" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A741" s="104">
-        <v>765</v>
-      </c>
-      <c r="B741" s="97">
-        <v>603</v>
-      </c>
-      <c r="C741" s="98">
+        <v>768</v>
+      </c>
+      <c r="B741" s="13">
+        <v>606</v>
+      </c>
+      <c r="C741" s="94">
         <v>46300</v>
       </c>
-      <c r="D741" s="97" t="s">
+      <c r="D741" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="E741" s="99" t="s">
-        <v>409</v>
-      </c>
-      <c r="F741" s="99" t="s">
+      <c r="E741" s="95" t="s">
         <v>406</v>
       </c>
-      <c r="G741" s="100">
-        <v>41.26793</v>
-      </c>
-      <c r="H741" s="100">
-        <v>41.548389999999998</v>
+      <c r="F741" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G741" s="96">
+        <v>41.27948</v>
+      </c>
+      <c r="H741" s="96">
+        <v>41.55856</v>
       </c>
       <c r="J741" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="742" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A742" s="104">
-        <v>766</v>
-      </c>
-      <c r="B742" s="13">
-        <v>604</v>
-      </c>
-      <c r="C742" s="94">
+        <v>769</v>
+      </c>
+      <c r="B742" s="16">
+        <v>607</v>
+      </c>
+      <c r="C742" s="101">
         <v>46300</v>
       </c>
-      <c r="D742" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="E742" s="95" t="s">
-        <v>331</v>
-      </c>
-      <c r="F742" s="95" t="s">
-        <v>332</v>
-      </c>
-      <c r="G742" s="96">
-        <v>41.26793</v>
-      </c>
-      <c r="H742" s="96">
-        <v>41.548389999999998</v>
+      <c r="D742" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E742" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="F742" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="G742" s="103">
+        <v>41.280389999999997</v>
+      </c>
+      <c r="H742" s="103">
+        <v>41.561770000000003</v>
       </c>
     </row>
     <row r="743" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A743" s="104">
-        <v>767</v>
-      </c>
-      <c r="B743" s="16">
-        <v>605</v>
-      </c>
-      <c r="C743" s="101">
-        <v>46300</v>
-      </c>
-      <c r="D743" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E743" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="F743" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="G743" s="103">
-        <v>41.27948</v>
-      </c>
-      <c r="H743" s="103">
-        <v>41.55856</v>
+        <v>770</v>
+      </c>
+      <c r="B743" s="29">
+        <v>608</v>
+      </c>
+      <c r="C743" s="107">
+        <v>46302</v>
+      </c>
+      <c r="D743" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="E743" s="108" t="s">
+        <v>331</v>
+      </c>
+      <c r="F743" s="108" t="s">
+        <v>332</v>
+      </c>
+      <c r="G743" s="87">
+        <v>41.181894999999997</v>
+      </c>
+      <c r="H743" s="87">
+        <v>41.828584999999997</v>
       </c>
     </row>
     <row r="744" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A744" s="104">
-        <v>768</v>
-      </c>
-      <c r="B744" s="13">
-        <v>606</v>
-      </c>
-      <c r="C744" s="94">
-        <v>46300</v>
-      </c>
-      <c r="D744" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="E744" s="95" t="s">
-        <v>407</v>
-      </c>
-      <c r="F744" s="95" t="s">
-        <v>408</v>
-      </c>
-      <c r="G744" s="96">
-        <v>41.27948</v>
-      </c>
-      <c r="H744" s="96">
-        <v>41.55856</v>
-      </c>
-      <c r="J744" t="s">
-        <v>405</v>
+        <v>771</v>
+      </c>
+      <c r="B744" s="38">
+        <v>609</v>
+      </c>
+      <c r="C744" s="105">
+        <v>46302</v>
+      </c>
+      <c r="D744" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E744" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="F744" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="G744" s="88">
+        <v>41.182499999999997</v>
+      </c>
+      <c r="H744" s="88">
+        <v>41.832070000000002</v>
       </c>
     </row>
     <row r="745" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A745" s="104">
-        <v>769</v>
-      </c>
-      <c r="B745" s="16">
-        <v>607</v>
-      </c>
-      <c r="C745" s="101">
-        <v>46300</v>
-      </c>
-      <c r="D745" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E745" s="102" t="s">
-        <v>335</v>
-      </c>
-      <c r="F745" s="102" t="s">
-        <v>336</v>
-      </c>
-      <c r="G745" s="103">
-        <v>41.280389999999997</v>
-      </c>
-      <c r="H745" s="103">
-        <v>41.561770000000003</v>
+        <v>772</v>
+      </c>
+      <c r="B745" s="29">
+        <v>610</v>
+      </c>
+      <c r="C745" s="107">
+        <v>46302</v>
+      </c>
+      <c r="D745" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="E745" s="108" t="s">
+        <v>406</v>
+      </c>
+      <c r="F745" s="108" t="s">
+        <v>407</v>
+      </c>
+      <c r="G745" s="87">
+        <v>41.182499999999997</v>
+      </c>
+      <c r="H745" s="87">
+        <v>41.832070000000002</v>
+      </c>
+      <c r="J745" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="746" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A746" s="104">
-        <v>770</v>
-      </c>
-      <c r="B746" s="29">
-        <v>608</v>
-      </c>
-      <c r="C746" s="107">
+        <v>773</v>
+      </c>
+      <c r="B746" s="38">
+        <v>611</v>
+      </c>
+      <c r="C746" s="105">
         <v>46302</v>
       </c>
-      <c r="D746" s="29" t="s">
-        <v>330</v>
-      </c>
-      <c r="E746" s="108" t="s">
-        <v>331</v>
-      </c>
-      <c r="F746" s="108" t="s">
-        <v>332</v>
-      </c>
-      <c r="G746" s="87">
-        <v>41.181894999999997</v>
-      </c>
-      <c r="H746" s="87">
-        <v>41.828584999999997</v>
+      <c r="D746" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="E746" s="106" t="s">
+        <v>335</v>
+      </c>
+      <c r="F746" s="106" t="s">
+        <v>336</v>
+      </c>
+      <c r="G746" s="88">
+        <v>41.182499999999997</v>
+      </c>
+      <c r="H746" s="88">
+        <v>41.832070000000002</v>
       </c>
     </row>
     <row r="747" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A747" s="104">
-        <v>771</v>
-      </c>
-      <c r="B747" s="38">
-        <v>609</v>
-      </c>
-      <c r="C747" s="105">
+        <v>774</v>
+      </c>
+      <c r="B747" s="29">
+        <v>612</v>
+      </c>
+      <c r="C747" s="107">
         <v>46302</v>
       </c>
-      <c r="D747" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="E747" s="106" t="s">
-        <v>327</v>
-      </c>
-      <c r="F747" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="G747" s="88">
+      <c r="D747" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E747" s="108" t="s">
+        <v>329</v>
+      </c>
+      <c r="F747" s="108" t="s">
+        <v>368</v>
+      </c>
+      <c r="G747" s="87">
         <v>41.182499999999997</v>
       </c>
-      <c r="H747" s="88">
+      <c r="H747" s="87">
         <v>41.832070000000002</v>
       </c>
     </row>
     <row r="748" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A748" s="104">
-        <v>772</v>
-      </c>
-      <c r="B748" s="29">
-        <v>610</v>
-      </c>
-      <c r="C748" s="107">
+        <v>775</v>
+      </c>
+      <c r="B748" s="38">
+        <v>613</v>
+      </c>
+      <c r="C748" s="105">
         <v>46302</v>
       </c>
-      <c r="D748" s="29" t="s">
-        <v>391</v>
-      </c>
-      <c r="E748" s="108" t="s">
-        <v>407</v>
-      </c>
-      <c r="F748" s="108" t="s">
-        <v>408</v>
-      </c>
-      <c r="G748" s="87">
-        <v>41.182499999999997</v>
-      </c>
-      <c r="H748" s="87">
-        <v>41.832070000000002</v>
-      </c>
-      <c r="J748" t="s">
-        <v>405</v>
+      <c r="D748" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E748" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="F748" s="106" t="s">
+        <v>333</v>
+      </c>
+      <c r="G748" s="88">
+        <v>41.210369999999998</v>
+      </c>
+      <c r="H748" s="88">
+        <v>41.85134</v>
       </c>
     </row>
     <row r="749" spans="1:10" ht="16" x14ac:dyDescent="0.35">
       <c r="A749" s="104">
-        <v>773</v>
-      </c>
-      <c r="B749" s="38">
-        <v>611</v>
-      </c>
-      <c r="C749" s="105">
+        <v>776</v>
+      </c>
+      <c r="B749" s="29">
+        <v>614</v>
+      </c>
+      <c r="C749" s="107">
         <v>46302</v>
       </c>
-      <c r="D749" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="E749" s="106" t="s">
-        <v>335</v>
-      </c>
-      <c r="F749" s="106" t="s">
-        <v>336</v>
-      </c>
-      <c r="G749" s="88">
-        <v>41.182499999999997</v>
-      </c>
-      <c r="H749" s="88">
-        <v>41.832070000000002</v>
-      </c>
-    </row>
-    <row r="750" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A750" s="104">
-        <v>774</v>
-      </c>
-      <c r="B750" s="29">
-        <v>612</v>
-      </c>
-      <c r="C750" s="107">
-        <v>46302</v>
-      </c>
-      <c r="D750" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E750" s="108" t="s">
-        <v>329</v>
-      </c>
-      <c r="F750" s="108" t="s">
-        <v>368</v>
-      </c>
-      <c r="G750" s="87">
-        <v>41.182499999999997</v>
-      </c>
-      <c r="H750" s="87">
-        <v>41.832070000000002</v>
-      </c>
-    </row>
-    <row r="751" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A751" s="104">
-        <v>775</v>
-      </c>
-      <c r="B751" s="38">
-        <v>613</v>
-      </c>
-      <c r="C751" s="105">
-        <v>46302</v>
-      </c>
-      <c r="D751" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="E751" s="106" t="s">
-        <v>116</v>
-      </c>
-      <c r="F751" s="106" t="s">
-        <v>333</v>
-      </c>
-      <c r="G751" s="88">
-        <v>41.210369999999998</v>
-      </c>
-      <c r="H751" s="88">
-        <v>41.85134</v>
-      </c>
-    </row>
-    <row r="752" spans="1:10" ht="16" x14ac:dyDescent="0.35">
-      <c r="A752" s="104">
-        <v>776</v>
-      </c>
-      <c r="B752" s="29">
-        <v>614</v>
-      </c>
-      <c r="C752" s="107">
-        <v>46302</v>
-      </c>
-      <c r="D752" s="29" t="s">
+      <c r="D749" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="E752" s="108" t="s">
+      <c r="E749" s="108" t="s">
         <v>367</v>
       </c>
-      <c r="F752" s="108" t="s">
+      <c r="F749" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="G752" s="87">
+      <c r="G749" s="87">
         <v>41.181894999999997</v>
       </c>
-      <c r="H752" s="87">
+      <c r="H749" s="87">
         <v>41.828584999999997</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H752" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H749" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23551,38 +23461,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="131" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="134"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="131" t="s">
+      <c r="C1" s="131"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="128" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="132" t="s">
+      <c r="F1" s="128"/>
+      <c r="G1" s="129" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
-      <c r="M1" s="127" t="s">
+      <c r="M1" s="120" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="55" t="s">
         <v>260</v>
       </c>
       <c r="D2" s="56"/>
-      <c r="E2" s="125" t="s">
+      <c r="E2" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="126"/>
+      <c r="F2" s="127"/>
       <c r="G2" s="60" t="s">
         <v>240</v>
       </c>
@@ -23605,15 +23515,15 @@
       <c r="L3" s="59"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="122" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="125" t="s">
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="126"/>
+      <c r="F4" s="127"/>
       <c r="G4" s="60" t="s">
         <v>242</v>
       </c>
@@ -23712,11 +23622,11 @@
       <c r="L11" s="59"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="120" t="s">
+      <c r="B12" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="120"/>
-      <c r="D12" s="121"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="123"/>
       <c r="G12" s="60" t="s">
         <v>248</v>
       </c>
@@ -23736,11 +23646,11 @@
       <c r="L13" s="59"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="122" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="121"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="123"/>
       <c r="G14" s="60" t="s">
         <v>249</v>
       </c>
@@ -23760,15 +23670,15 @@
       <c r="L15" s="59"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="120" t="s">
+      <c r="B16" s="122" t="s">
         <v>265</v>
       </c>
-      <c r="C16" s="120"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="129" t="s">
+      <c r="C16" s="122"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="130"/>
+      <c r="F16" s="125"/>
       <c r="G16" s="60" t="s">
         <v>251</v>
       </c>
@@ -23791,19 +23701,19 @@
       <c r="L17" s="59"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="120" t="s">
+      <c r="B18" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="120"/>
-      <c r="D18" s="121"/>
-      <c r="G18" s="122" t="s">
+      <c r="C18" s="122"/>
+      <c r="D18" s="123"/>
+      <c r="G18" s="133" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="124"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="135"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="56"/>
@@ -23815,23 +23725,23 @@
       <c r="L19" s="59"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="122" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="125" t="s">
+      <c r="C20" s="122"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="126" t="s">
         <v>254</v>
       </c>
-      <c r="F20" s="126"/>
-      <c r="G20" s="122" t="s">
+      <c r="F20" s="127"/>
+      <c r="G20" s="133" t="s">
         <v>253</v>
       </c>
-      <c r="H20" s="123"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="124"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="135"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="56"/>
@@ -23843,11 +23753,11 @@
       <c r="L21" s="59"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="120" t="s">
+      <c r="B22" s="122" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="120"/>
-      <c r="D22" s="121"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="123"/>
       <c r="G22" s="60" t="s">
         <v>255</v>
       </c>
@@ -23867,11 +23777,11 @@
       <c r="L23" s="59"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="123"/>
       <c r="G24" s="60"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
@@ -23883,11 +23793,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="120" t="s">
+      <c r="B25" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="121"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="123"/>
       <c r="G25" s="60"/>
       <c r="H25" s="59"/>
       <c r="I25" s="59"/>
@@ -23973,6 +23883,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B14:D14"/>
@@ -23984,14 +23902,6 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/istasyonlar.xlsx
+++ b/data/istasyonlar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\(DOÇENTLİK ve SONRASI)\PROJELER\BAP10-Aromatik\SAHA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F5680F-6767-41A0-B25F-C91017354263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8597259-0D71-445B-957C-4EE02C9BEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1010" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="1730" windowWidth="22040" windowHeight="14270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2719" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="449">
   <si>
     <t>CCR</t>
   </si>
@@ -1760,6 +1760,12 @@
   </si>
   <si>
     <t>Hypericum montbretii</t>
+  </si>
+  <si>
+    <t>DKA</t>
+  </si>
+  <si>
+    <t>DLO</t>
   </si>
 </sst>
 </file>
@@ -2522,11 +2528,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2534,17 +2537,32 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2560,18 +2578,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2892,15 +2898,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M749"/>
+  <dimension ref="A1:M812"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
     <col min="2" max="2" width="9.7265625" customWidth="1"/>
     <col min="3" max="3" width="13.1796875" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" customWidth="1"/>
-    <col min="5" max="5" width="19.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="23.08984375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" customWidth="1"/>
     <col min="10" max="10" width="21.90625" customWidth="1"/>
@@ -17182,7 +17188,7 @@
         <v>41.771599999999999</v>
       </c>
     </row>
-    <row r="517" spans="1:13" ht="32" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="47">
         <v>541</v>
       </c>
@@ -22711,7 +22717,7 @@
       <c r="E722" s="102" t="s">
         <v>393</v>
       </c>
-      <c r="F722" s="136" t="s">
+      <c r="F722" s="120" t="s">
         <v>443</v>
       </c>
       <c r="G722" s="103">
@@ -23439,6 +23445,1644 @@
       </c>
       <c r="H749" s="87">
         <v>41.828584999999997</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A750" s="104">
+        <v>777</v>
+      </c>
+      <c r="B750" s="13">
+        <v>615</v>
+      </c>
+      <c r="C750" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D750" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E750" s="95" t="s">
+        <v>376</v>
+      </c>
+      <c r="F750" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="G750" s="96">
+        <v>41.239280000000001</v>
+      </c>
+      <c r="H750" s="96">
+        <v>42.426909999999999</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A751" s="104">
+        <v>778</v>
+      </c>
+      <c r="B751" s="16">
+        <v>616</v>
+      </c>
+      <c r="C751" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D751" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E751" s="102" t="s">
+        <v>109</v>
+      </c>
+      <c r="F751" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="G751" s="103">
+        <v>41.236800000000002</v>
+      </c>
+      <c r="H751" s="103">
+        <v>42.420340000000003</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" ht="16" x14ac:dyDescent="0.35">
+      <c r="A752" s="104">
+        <v>779</v>
+      </c>
+      <c r="B752" s="13">
+        <v>617</v>
+      </c>
+      <c r="C752" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D752" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E752" s="95" t="s">
+        <v>113</v>
+      </c>
+      <c r="F752" s="95" t="s">
+        <v>114</v>
+      </c>
+      <c r="G752" s="96">
+        <v>41.23659</v>
+      </c>
+      <c r="H752" s="96">
+        <v>42.414290000000001</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A753" s="104">
+        <v>780</v>
+      </c>
+      <c r="B753" s="13">
+        <v>619</v>
+      </c>
+      <c r="C753" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D753" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E753" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F753" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G753" s="96">
+        <v>41.224609999999998</v>
+      </c>
+      <c r="H753" s="96">
+        <v>42.389919999999996</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A754" s="104">
+        <v>781</v>
+      </c>
+      <c r="B754" s="16">
+        <v>620</v>
+      </c>
+      <c r="C754" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D754" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E754" s="102" t="s">
+        <v>376</v>
+      </c>
+      <c r="F754" s="102" t="s">
+        <v>370</v>
+      </c>
+      <c r="G754" s="103">
+        <v>41.22213</v>
+      </c>
+      <c r="H754" s="103">
+        <v>42.385590000000001</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A755" s="104">
+        <v>782</v>
+      </c>
+      <c r="B755" s="13">
+        <v>621</v>
+      </c>
+      <c r="C755" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D755" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E755" s="95" t="s">
+        <v>380</v>
+      </c>
+      <c r="F755" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="G755" s="96">
+        <v>41.22213</v>
+      </c>
+      <c r="H755" s="96">
+        <v>42.385590000000001</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A756" s="104">
+        <v>783</v>
+      </c>
+      <c r="B756" s="97">
+        <v>622</v>
+      </c>
+      <c r="C756" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D756" s="97" t="s">
+        <v>108</v>
+      </c>
+      <c r="E756" s="99" t="s">
+        <v>109</v>
+      </c>
+      <c r="F756" s="99" t="s">
+        <v>110</v>
+      </c>
+      <c r="G756" s="100">
+        <v>41.22045</v>
+      </c>
+      <c r="H756" s="100">
+        <v>42.375480000000003</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A757" s="104">
+        <v>784</v>
+      </c>
+      <c r="B757" s="13">
+        <v>623</v>
+      </c>
+      <c r="C757" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D757" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E757" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="F757" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="G757" s="96">
+        <v>41.219940000000001</v>
+      </c>
+      <c r="H757" s="96">
+        <v>42.37538</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A758" s="104">
+        <v>785</v>
+      </c>
+      <c r="B758" s="13">
+        <v>625</v>
+      </c>
+      <c r="C758" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D758" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E758" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F758" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G758" s="96">
+        <v>41.215479999999999</v>
+      </c>
+      <c r="H758" s="96">
+        <v>42.376980000000003</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A759" s="104">
+        <v>786</v>
+      </c>
+      <c r="B759" s="16">
+        <v>626</v>
+      </c>
+      <c r="C759" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D759" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E759" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="F759" s="102" t="s">
+        <v>333</v>
+      </c>
+      <c r="G759" s="103">
+        <v>41.214419999999997</v>
+      </c>
+      <c r="H759" s="103">
+        <v>42.371789999999997</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A760" s="104">
+        <v>787</v>
+      </c>
+      <c r="B760" s="97">
+        <v>627</v>
+      </c>
+      <c r="C760" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D760" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="E760" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="F760" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="G760" s="100">
+        <v>41.229419999999998</v>
+      </c>
+      <c r="H760" s="100">
+        <v>42.374980000000001</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A761" s="104">
+        <v>788</v>
+      </c>
+      <c r="B761" s="16">
+        <v>628</v>
+      </c>
+      <c r="C761" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D761" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="E761" s="102" t="s">
+        <v>376</v>
+      </c>
+      <c r="F761" s="102" t="s">
+        <v>370</v>
+      </c>
+      <c r="G761" s="103">
+        <v>41.236649999999997</v>
+      </c>
+      <c r="H761" s="103">
+        <v>42.369610000000002</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A762" s="104">
+        <v>789</v>
+      </c>
+      <c r="B762" s="13">
+        <v>629</v>
+      </c>
+      <c r="C762" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D762" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E762" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F762" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="G762" s="96">
+        <v>41.236649999999997</v>
+      </c>
+      <c r="H762" s="96">
+        <v>42.369610000000002</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A763" s="104">
+        <v>790</v>
+      </c>
+      <c r="B763" s="16">
+        <v>630</v>
+      </c>
+      <c r="C763" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D763" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E763" s="102" t="s">
+        <v>380</v>
+      </c>
+      <c r="F763" s="102" t="s">
+        <v>120</v>
+      </c>
+      <c r="G763" s="103">
+        <v>41.236649999999997</v>
+      </c>
+      <c r="H763" s="103">
+        <v>42.369610000000002</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A764" s="104">
+        <v>791</v>
+      </c>
+      <c r="B764" s="13">
+        <v>631</v>
+      </c>
+      <c r="C764" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D764" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E764" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F764" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G764" s="96">
+        <v>41.236649999999997</v>
+      </c>
+      <c r="H764" s="96">
+        <v>42.369610000000002</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A765" s="104">
+        <v>792</v>
+      </c>
+      <c r="B765" s="16">
+        <v>632</v>
+      </c>
+      <c r="C765" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D765" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E765" s="102" t="s">
+        <v>408</v>
+      </c>
+      <c r="F765" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G765" s="103">
+        <v>41.256799999999998</v>
+      </c>
+      <c r="H765" s="103">
+        <v>42.338099999999997</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A766" s="104">
+        <v>793</v>
+      </c>
+      <c r="B766" s="13">
+        <v>633</v>
+      </c>
+      <c r="C766" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D766" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E766" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="F766" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="G766" s="96">
+        <v>41.256799999999998</v>
+      </c>
+      <c r="H766" s="96">
+        <v>42.338099999999997</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A767" s="104">
+        <v>794</v>
+      </c>
+      <c r="B767" s="97">
+        <v>634</v>
+      </c>
+      <c r="C767" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D767" s="97" t="s">
+        <v>448</v>
+      </c>
+      <c r="E767" s="99" t="s">
+        <v>406</v>
+      </c>
+      <c r="F767" s="99" t="s">
+        <v>407</v>
+      </c>
+      <c r="G767" s="100">
+        <v>41.25759</v>
+      </c>
+      <c r="H767" s="100">
+        <v>42.313890000000001</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A768" s="104">
+        <v>795</v>
+      </c>
+      <c r="B768" s="13">
+        <v>635</v>
+      </c>
+      <c r="C768" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D768" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E768" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F768" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G768" s="96">
+        <v>41.25759</v>
+      </c>
+      <c r="H768" s="96">
+        <v>42.313890000000001</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A769" s="104">
+        <v>796</v>
+      </c>
+      <c r="B769" s="97">
+        <v>636</v>
+      </c>
+      <c r="C769" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D769" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="E769" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="F769" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="G769" s="100">
+        <v>41.259140000000002</v>
+      </c>
+      <c r="H769" s="100">
+        <v>42.30782</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A770" s="104">
+        <v>797</v>
+      </c>
+      <c r="B770" s="97">
+        <v>637</v>
+      </c>
+      <c r="C770" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D770" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="E770" s="99" t="s">
+        <v>376</v>
+      </c>
+      <c r="F770" s="99" t="s">
+        <v>370</v>
+      </c>
+      <c r="G770" s="100">
+        <v>41.261960000000002</v>
+      </c>
+      <c r="H770" s="100">
+        <v>42.299979999999998</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A771" s="104">
+        <v>798</v>
+      </c>
+      <c r="B771" s="16">
+        <v>638</v>
+      </c>
+      <c r="C771" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D771" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E771" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F771" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G771" s="103">
+        <v>41.271299999999997</v>
+      </c>
+      <c r="H771" s="103">
+        <v>42.266719999999999</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A772" s="104">
+        <v>799</v>
+      </c>
+      <c r="B772" s="13">
+        <v>639</v>
+      </c>
+      <c r="C772" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D772" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E772" s="95" t="s">
+        <v>335</v>
+      </c>
+      <c r="F772" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="G772" s="96">
+        <v>41.272210000000001</v>
+      </c>
+      <c r="H772" s="96">
+        <v>42.264209999999999</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A773" s="104">
+        <v>800</v>
+      </c>
+      <c r="B773" s="97">
+        <v>640</v>
+      </c>
+      <c r="C773" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D773" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="E773" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="F773" s="99" t="s">
+        <v>332</v>
+      </c>
+      <c r="G773" s="100">
+        <v>41.343000000000004</v>
+      </c>
+      <c r="H773" s="100">
+        <v>42.259729999999998</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A774" s="104">
+        <v>801</v>
+      </c>
+      <c r="B774" s="13">
+        <v>641</v>
+      </c>
+      <c r="C774" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D774" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E774" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F774" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G774" s="96">
+        <v>41.343000000000004</v>
+      </c>
+      <c r="H774" s="96">
+        <v>42.259729999999998</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A775" s="104">
+        <v>802</v>
+      </c>
+      <c r="B775" s="16">
+        <v>642</v>
+      </c>
+      <c r="C775" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D775" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E775" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="F775" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="G775" s="103">
+        <v>41.354259999999996</v>
+      </c>
+      <c r="H775" s="103">
+        <v>42.276400000000002</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A776" s="104">
+        <v>803</v>
+      </c>
+      <c r="B776" s="13">
+        <v>643</v>
+      </c>
+      <c r="C776" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D776" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E776" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="F776" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="G776" s="96">
+        <v>41.354259999999996</v>
+      </c>
+      <c r="H776" s="96">
+        <v>42.276400000000002</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A777" s="104">
+        <v>804</v>
+      </c>
+      <c r="B777" s="16">
+        <v>644</v>
+      </c>
+      <c r="C777" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D777" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="E777" s="102" t="s">
+        <v>406</v>
+      </c>
+      <c r="F777" s="102" t="s">
+        <v>407</v>
+      </c>
+      <c r="G777" s="103">
+        <v>41.395310000000002</v>
+      </c>
+      <c r="H777" s="103">
+        <v>42.286990000000003</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A778" s="104">
+        <v>805</v>
+      </c>
+      <c r="B778" s="13">
+        <v>645</v>
+      </c>
+      <c r="C778" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D778" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E778" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="F778" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="G778" s="96">
+        <v>41.390659999999997</v>
+      </c>
+      <c r="H778" s="96">
+        <v>42.285060000000001</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A779" s="104">
+        <v>806</v>
+      </c>
+      <c r="B779" s="16">
+        <v>646</v>
+      </c>
+      <c r="C779" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D779" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E779" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F779" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G779" s="103">
+        <v>41.381959999999999</v>
+      </c>
+      <c r="H779" s="103">
+        <v>42.286740000000002</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A780" s="104">
+        <v>807</v>
+      </c>
+      <c r="B780" s="13">
+        <v>647</v>
+      </c>
+      <c r="C780" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D780" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="E780" s="95" t="s">
+        <v>376</v>
+      </c>
+      <c r="F780" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="G780" s="96">
+        <v>41.37133</v>
+      </c>
+      <c r="H780" s="96">
+        <v>42.289349999999999</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A781" s="104">
+        <v>808</v>
+      </c>
+      <c r="B781" s="16">
+        <v>648</v>
+      </c>
+      <c r="C781" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D781" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E781" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F781" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G781" s="103">
+        <v>41.338549999999998</v>
+      </c>
+      <c r="H781" s="103">
+        <v>42.253720000000001</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A782" s="104">
+        <v>809</v>
+      </c>
+      <c r="B782" s="13">
+        <v>649</v>
+      </c>
+      <c r="C782" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D782" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E782" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F782" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G782" s="96">
+        <v>41.338549999999998</v>
+      </c>
+      <c r="H782" s="96">
+        <v>42.253720000000001</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A783" s="104">
+        <v>810</v>
+      </c>
+      <c r="B783" s="16">
+        <v>650</v>
+      </c>
+      <c r="C783" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D783" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E783" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="F783" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="G783" s="103">
+        <v>41.330649999999999</v>
+      </c>
+      <c r="H783" s="103">
+        <v>42.243189999999998</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A784" s="104">
+        <v>811</v>
+      </c>
+      <c r="B784" s="13">
+        <v>651</v>
+      </c>
+      <c r="C784" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D784" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E784" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="F784" s="95" t="s">
+        <v>368</v>
+      </c>
+      <c r="G784" s="96">
+        <v>41.326129999999999</v>
+      </c>
+      <c r="H784" s="96">
+        <v>42.237290000000002</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A785" s="104">
+        <v>812</v>
+      </c>
+      <c r="B785" s="16">
+        <v>652</v>
+      </c>
+      <c r="C785" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D785" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E785" s="102" t="s">
+        <v>408</v>
+      </c>
+      <c r="F785" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G785" s="103">
+        <v>41.326129999999999</v>
+      </c>
+      <c r="H785" s="103">
+        <v>42.237290000000002</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A786" s="104">
+        <v>813</v>
+      </c>
+      <c r="B786" s="13">
+        <v>653</v>
+      </c>
+      <c r="C786" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D786" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="E786" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F786" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G786" s="96">
+        <v>41.300539999999998</v>
+      </c>
+      <c r="H786" s="96">
+        <v>42.224780000000003</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A787" s="104">
+        <v>814</v>
+      </c>
+      <c r="B787" s="16">
+        <v>654</v>
+      </c>
+      <c r="C787" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D787" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E787" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F787" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G787" s="103">
+        <v>41.28519</v>
+      </c>
+      <c r="H787" s="103">
+        <v>42.231290000000001</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A788" s="104">
+        <v>815</v>
+      </c>
+      <c r="B788" s="13">
+        <v>655</v>
+      </c>
+      <c r="C788" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D788" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E788" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="F788" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="G788" s="96">
+        <v>41.28519</v>
+      </c>
+      <c r="H788" s="96">
+        <v>42.231290000000001</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A789" s="104">
+        <v>816</v>
+      </c>
+      <c r="B789" s="16">
+        <v>656</v>
+      </c>
+      <c r="C789" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D789" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="E789" s="102" t="s">
+        <v>406</v>
+      </c>
+      <c r="F789" s="102" t="s">
+        <v>407</v>
+      </c>
+      <c r="G789" s="103">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H789" s="103">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A790" s="104">
+        <v>817</v>
+      </c>
+      <c r="B790" s="13">
+        <v>657</v>
+      </c>
+      <c r="C790" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D790" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E790" s="95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F790" s="95" t="s">
+        <v>332</v>
+      </c>
+      <c r="G790" s="96">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H790" s="96">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A791" s="104">
+        <v>818</v>
+      </c>
+      <c r="B791" s="16">
+        <v>658</v>
+      </c>
+      <c r="C791" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D791" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E791" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F791" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G791" s="103">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H791" s="103">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A792" s="104">
+        <v>819</v>
+      </c>
+      <c r="B792" s="13">
+        <v>659</v>
+      </c>
+      <c r="C792" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D792" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E792" s="95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F792" s="95" t="s">
+        <v>325</v>
+      </c>
+      <c r="G792" s="96">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H792" s="96">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A793" s="104">
+        <v>820</v>
+      </c>
+      <c r="B793" s="16">
+        <v>660</v>
+      </c>
+      <c r="C793" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D793" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E793" s="102" t="s">
+        <v>367</v>
+      </c>
+      <c r="F793" s="102" t="s">
+        <v>369</v>
+      </c>
+      <c r="G793" s="103">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H793" s="103">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A794" s="104">
+        <v>821</v>
+      </c>
+      <c r="B794" s="13">
+        <v>661</v>
+      </c>
+      <c r="C794" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D794" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E794" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F794" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G794" s="96">
+        <v>40.785769999999999</v>
+      </c>
+      <c r="H794" s="96">
+        <v>41.746989999999997</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A795" s="104">
+        <v>822</v>
+      </c>
+      <c r="B795" s="16">
+        <v>662</v>
+      </c>
+      <c r="C795" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D795" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E795" s="102" t="s">
+        <v>408</v>
+      </c>
+      <c r="F795" s="102" t="s">
+        <v>405</v>
+      </c>
+      <c r="G795" s="103">
+        <v>40.788539999999998</v>
+      </c>
+      <c r="H795" s="103">
+        <v>41.745330000000003</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A796" s="104">
+        <v>823</v>
+      </c>
+      <c r="B796" s="13">
+        <v>663</v>
+      </c>
+      <c r="C796" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D796" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E796" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="F796" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="G796" s="96">
+        <v>40.798099999999998</v>
+      </c>
+      <c r="H796" s="96">
+        <v>41.742339999999999</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A797" s="104">
+        <v>824</v>
+      </c>
+      <c r="B797" s="16">
+        <v>664</v>
+      </c>
+      <c r="C797" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D797" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E797" s="102" t="s">
+        <v>329</v>
+      </c>
+      <c r="F797" s="102" t="s">
+        <v>368</v>
+      </c>
+      <c r="G797" s="103">
+        <v>40.798099999999998</v>
+      </c>
+      <c r="H797" s="103">
+        <v>41.742339999999999</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A798" s="104">
+        <v>825</v>
+      </c>
+      <c r="B798" s="97">
+        <v>665</v>
+      </c>
+      <c r="C798" s="98">
+        <v>46304</v>
+      </c>
+      <c r="D798" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="E798" s="99" t="s">
+        <v>335</v>
+      </c>
+      <c r="F798" s="99" t="s">
+        <v>336</v>
+      </c>
+      <c r="G798" s="100">
+        <v>40.786819999999999</v>
+      </c>
+      <c r="H798" s="100">
+        <v>41.743009999999998</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A799" s="104">
+        <v>826</v>
+      </c>
+      <c r="B799" s="16">
+        <v>666</v>
+      </c>
+      <c r="C799" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D799" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E799" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="F799" s="102" t="s">
+        <v>333</v>
+      </c>
+      <c r="G799" s="103">
+        <v>40.786380000000001</v>
+      </c>
+      <c r="H799" s="103">
+        <v>41.749020000000002</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A800" s="104">
+        <v>827</v>
+      </c>
+      <c r="B800" s="13">
+        <v>667</v>
+      </c>
+      <c r="C800" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D800" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E800" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="F800" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="G800" s="96">
+        <v>40.788229999999999</v>
+      </c>
+      <c r="H800" s="96">
+        <v>41.75488</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A801" s="104">
+        <v>828</v>
+      </c>
+      <c r="B801" s="16">
+        <v>668</v>
+      </c>
+      <c r="C801" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D801" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="E801" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="F801" s="102" t="s">
+        <v>325</v>
+      </c>
+      <c r="G801" s="103">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H801" s="103">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A802" s="104">
+        <v>829</v>
+      </c>
+      <c r="B802" s="13">
+        <v>669</v>
+      </c>
+      <c r="C802" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D802" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E802" s="95" t="s">
+        <v>367</v>
+      </c>
+      <c r="F802" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="G802" s="96">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H802" s="96">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A803" s="104">
+        <v>830</v>
+      </c>
+      <c r="B803" s="16">
+        <v>670</v>
+      </c>
+      <c r="C803" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D803" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E803" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="F803" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G803" s="103">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H803" s="103">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A804" s="104">
+        <v>831</v>
+      </c>
+      <c r="B804" s="13">
+        <v>671</v>
+      </c>
+      <c r="C804" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D804" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E804" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F804" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G804" s="96">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H804" s="96">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A805" s="104">
+        <v>832</v>
+      </c>
+      <c r="B805" s="16">
+        <v>672</v>
+      </c>
+      <c r="C805" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D805" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E805" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F805" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="G805" s="103">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H805" s="103">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A806" s="104">
+        <v>833</v>
+      </c>
+      <c r="B806" s="13">
+        <v>673</v>
+      </c>
+      <c r="C806" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D806" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="E806" s="95" t="s">
+        <v>408</v>
+      </c>
+      <c r="F806" s="95" t="s">
+        <v>405</v>
+      </c>
+      <c r="G806" s="96">
+        <v>40.887729999999998</v>
+      </c>
+      <c r="H806" s="96">
+        <v>41.743209999999998</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A807" s="104">
+        <v>834</v>
+      </c>
+      <c r="B807" s="16">
+        <v>674</v>
+      </c>
+      <c r="C807" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D807" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E807" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="F807" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="G807" s="103">
+        <v>40.887729999999998</v>
+      </c>
+      <c r="H807" s="103">
+        <v>41.743209999999998</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A808" s="104">
+        <v>835</v>
+      </c>
+      <c r="B808" s="13">
+        <v>675</v>
+      </c>
+      <c r="C808" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D808" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E808" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F808" s="95" t="s">
+        <v>333</v>
+      </c>
+      <c r="G808" s="96">
+        <v>40.886040000000001</v>
+      </c>
+      <c r="H808" s="96">
+        <v>41.742040000000003</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A809" s="104">
+        <v>836</v>
+      </c>
+      <c r="B809" s="16">
+        <v>676</v>
+      </c>
+      <c r="C809" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D809" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E809" s="102" t="s">
+        <v>331</v>
+      </c>
+      <c r="F809" s="102" t="s">
+        <v>332</v>
+      </c>
+      <c r="G809" s="103">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H809" s="103">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A810" s="104">
+        <v>837</v>
+      </c>
+      <c r="B810" s="13">
+        <v>677</v>
+      </c>
+      <c r="C810" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D810" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="E810" s="95" t="s">
+        <v>406</v>
+      </c>
+      <c r="F810" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="G810" s="96">
+        <v>40.884680000000003</v>
+      </c>
+      <c r="H810" s="96">
+        <v>41.740389999999998</v>
+      </c>
+    </row>
+    <row r="811" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A811" s="104">
+        <v>838</v>
+      </c>
+      <c r="B811" s="16">
+        <v>678</v>
+      </c>
+      <c r="C811" s="101">
+        <v>46304</v>
+      </c>
+      <c r="D811" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E811" s="102" t="s">
+        <v>329</v>
+      </c>
+      <c r="F811" s="102" t="s">
+        <v>368</v>
+      </c>
+      <c r="G811" s="103">
+        <v>40.885179999999998</v>
+      </c>
+      <c r="H811" s="103">
+        <v>41.739690000000003</v>
+      </c>
+    </row>
+    <row r="812" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A812" s="104">
+        <v>839</v>
+      </c>
+      <c r="B812" s="13">
+        <v>679</v>
+      </c>
+      <c r="C812" s="94">
+        <v>46304</v>
+      </c>
+      <c r="D812" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E812" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="F812" s="95" t="s">
+        <v>320</v>
+      </c>
+      <c r="G812" s="96">
+        <v>40.889270000000003</v>
+      </c>
+      <c r="H812" s="96">
+        <v>41.73498</v>
       </c>
     </row>
   </sheetData>
@@ -23461,28 +25105,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="131"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="128" t="s">
+      <c r="C1" s="135"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="132" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="129" t="s">
+      <c r="F1" s="132"/>
+      <c r="G1" s="133" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
       <c r="K1" s="61"/>
       <c r="L1" s="61"/>
-      <c r="M1" s="120" t="s">
+      <c r="M1" s="128" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="55" t="s">
@@ -23515,11 +25159,11 @@
       <c r="L3" s="59"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="121" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="123"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
       <c r="E4" s="126" t="s">
         <v>241</v>
       </c>
@@ -23622,11 +25266,11 @@
       <c r="L11" s="59"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="121" t="s">
         <v>264</v>
       </c>
-      <c r="C12" s="122"/>
-      <c r="D12" s="123"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="122"/>
       <c r="G12" s="60" t="s">
         <v>248</v>
       </c>
@@ -23646,11 +25290,11 @@
       <c r="L13" s="59"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="121" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="122"/>
-      <c r="D14" s="123"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="122"/>
       <c r="G14" s="60" t="s">
         <v>249</v>
       </c>
@@ -23670,15 +25314,15 @@
       <c r="L15" s="59"/>
     </row>
     <row r="16" spans="2:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="121" t="s">
         <v>265</v>
       </c>
-      <c r="C16" s="122"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124" t="s">
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="130" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="125"/>
+      <c r="F16" s="131"/>
       <c r="G16" s="60" t="s">
         <v>251</v>
       </c>
@@ -23701,19 +25345,19 @@
       <c r="L17" s="59"/>
     </row>
     <row r="18" spans="2:13" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="121" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="122"/>
-      <c r="D18" s="123"/>
-      <c r="G18" s="133" t="s">
+      <c r="C18" s="121"/>
+      <c r="D18" s="122"/>
+      <c r="G18" s="123" t="s">
         <v>252</v>
       </c>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="135"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="125"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D19" s="56"/>
@@ -23725,23 +25369,23 @@
       <c r="L19" s="59"/>
     </row>
     <row r="20" spans="2:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="121" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="122"/>
-      <c r="D20" s="123"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="122"/>
       <c r="E20" s="126" t="s">
         <v>254</v>
       </c>
       <c r="F20" s="127"/>
-      <c r="G20" s="133" t="s">
+      <c r="G20" s="123" t="s">
         <v>253</v>
       </c>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="135"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="125"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D21" s="56"/>
@@ -23753,11 +25397,11 @@
       <c r="L21" s="59"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="122"/>
-      <c r="D22" s="123"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="122"/>
       <c r="G22" s="60" t="s">
         <v>255</v>
       </c>
@@ -23777,11 +25421,11 @@
       <c r="L23" s="59"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="122"/>
-      <c r="D24" s="123"/>
+      <c r="C24" s="121"/>
+      <c r="D24" s="122"/>
       <c r="G24" s="60"/>
       <c r="H24" s="59"/>
       <c r="I24" s="59"/>
@@ -23793,11 +25437,11 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="122"/>
-      <c r="D25" s="123"/>
+      <c r="C25" s="121"/>
+      <c r="D25" s="122"/>
       <c r="G25" s="60"/>
       <c r="H25" s="59"/>
       <c r="I25" s="59"/>
@@ -23883,14 +25527,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B14:D14"/>
@@ -23902,6 +25538,14 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G20:L20"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
